--- a/my_project/templates/template_B.xlsx
+++ b/my_project/templates/template_B.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\OneDrive\바탕 화면\my_project\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -374,9 +374,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
-    <numFmt numFmtId="177" formatCode="0.0%"/>
-    <numFmt numFmtId="178" formatCode="\+0.0%;\-0.0%"/>
-    <numFmt numFmtId="185" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="0.0%"/>
+    <numFmt numFmtId="177" formatCode="\+0.0%;\-0.0%"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-_);_(@_)"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -797,16 +797,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="185" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="185" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="185" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -818,40 +818,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -861,7 +828,7 @@
     <xf numFmtId="3" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -870,7 +837,7 @@
     <xf numFmtId="3" fontId="13" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="13" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="13" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -882,7 +849,89 @@
     <xf numFmtId="3" fontId="12" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="12" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="12" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -891,139 +940,90 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="13" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="13" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="13" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1496,7 +1496,7 @@
                 <c:order val="3"/>
                 <c:tx>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>요약보고서!$B$31:$E$31</c15:sqref>
@@ -1544,7 +1544,7 @@
                 </c:marker>
                 <c:cat>
                   <c:strRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>요약보고서!$F$27:$O$27</c15:sqref>
@@ -1588,7 +1588,7 @@
                 </c:cat>
                 <c:val>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>요약보고서!$F$31:$O$31</c15:sqref>
@@ -1602,7 +1602,7 @@
                   </c:numRef>
                 </c:val>
                 <c:smooth val="0"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000003-3121-47EF-9BD8-88AF9FBCC688}"/>
                   </c:ext>
@@ -2602,553 +2602,547 @@
   <sheetData>
     <row r="1" spans="2:15" ht="12.75" customHeight="1"/>
     <row r="2" spans="2:15" ht="31.5" customHeight="1">
-      <c r="B2" s="65" t="s">
+      <c r="B2" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
-      <c r="M2" s="65"/>
-      <c r="N2" s="65"/>
-      <c r="O2" s="65"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="45"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="45"/>
+      <c r="O2" s="45"/>
     </row>
     <row r="3" spans="2:15" ht="13.5" customHeight="1"/>
     <row r="4" spans="2:15" ht="27.75" customHeight="1">
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
-      <c r="L4" s="62"/>
-      <c r="M4" s="62"/>
-      <c r="N4" s="62"/>
-      <c r="O4" s="62"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="47"/>
+      <c r="N4" s="47"/>
+      <c r="O4" s="47"/>
     </row>
     <row r="5" spans="2:15" ht="27.75" customHeight="1">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
+      <c r="K5" s="49"/>
+      <c r="L5" s="49"/>
+      <c r="M5" s="49"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
     </row>
     <row r="6" spans="2:15" ht="41.25" customHeight="1">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="9" t="s">
+      <c r="C6" s="51"/>
+      <c r="D6" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="10" t="s">
+      <c r="E6" s="51"/>
+      <c r="F6" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="G6" s="8"/>
+      <c r="G6" s="51"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="9" t="s">
+      <c r="K6" s="51"/>
+      <c r="L6" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="M6" s="8"/>
-      <c r="N6" s="10" t="s">
+      <c r="M6" s="51"/>
+      <c r="N6" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="O6" s="8"/>
+      <c r="O6" s="51"/>
     </row>
     <row r="7" spans="2:15" ht="30" customHeight="1">
-      <c r="B7" s="11"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="69"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="51"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="8"/>
+      <c r="J7" s="69"/>
+      <c r="K7" s="51"/>
+      <c r="L7" s="68"/>
+      <c r="M7" s="51"/>
+      <c r="N7" s="52"/>
+      <c r="O7" s="51"/>
     </row>
     <row r="8" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14"/>
-      <c r="N8" s="14"/>
-      <c r="O8" s="14"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
     </row>
     <row r="9" spans="2:15" ht="27.75" customHeight="1">
-      <c r="B9" s="63" t="s">
+      <c r="B9" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="64"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="60" t="s">
+      <c r="I9" s="4"/>
+      <c r="J9" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="15"/>
-      <c r="O9" s="16"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="72"/>
+      <c r="M9" s="72"/>
+      <c r="N9" s="72"/>
+      <c r="O9" s="31"/>
     </row>
     <row r="10" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="43"/>
-      <c r="D10" s="18" t="s">
+      <c r="C10" s="42"/>
+      <c r="D10" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="5" t="s">
         <v>56</v>
       </c>
       <c r="H10" s="2"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="18" t="s">
+      <c r="I10" s="4"/>
+      <c r="J10" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="K10" s="18" t="s">
+      <c r="K10" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="L10" s="18" t="s">
+      <c r="L10" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="M10" s="18" t="s">
+      <c r="M10" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="N10" s="18" t="s">
+      <c r="N10" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="O10" s="18" t="s">
+      <c r="O10" s="5" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="11" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B11" s="30" t="s">
+      <c r="B11" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="31"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="20" t="str">
-        <f>IF(E11=0,"-",F11/D11)</f>
+      <c r="C11" s="29"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="7" t="str">
+        <f t="shared" ref="G11:G16" si="0">IF(E11=0,"-",F11/D11)</f>
         <v>-</v>
       </c>
       <c r="H11" s="2"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="21" t="s">
+      <c r="I11" s="4"/>
+      <c r="J11" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="20" t="str">
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="7" t="str">
         <f>IF(K11=0,"-",L11/K11)</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="33"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="23" t="str">
-        <f>IF(E12=0,"-",F12/D12)</f>
+      <c r="C12" s="34"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="10" t="str">
+        <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H12" s="2"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="24" t="s">
+      <c r="I12" s="4"/>
+      <c r="J12" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="22"/>
-      <c r="O12" s="23" t="str">
-        <f t="shared" ref="O12:O17" si="0">IF(K12=0,"-",L12/K12)</f>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="10" t="str">
+        <f t="shared" ref="O12:O17" si="1">IF(K12=0,"-",L12/K12)</f>
         <v>-</v>
       </c>
     </row>
     <row r="13" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="20" t="str">
-        <f>IF(E13=0,"-",F13/D13)</f>
-        <v>-</v>
-      </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="20" t="str">
+      <c r="C13" s="29"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="7" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
+      <c r="H13" s="2"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
     </row>
     <row r="14" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="33"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="23" t="str">
-        <f>IF(E14=0,"-",F14/D14)</f>
-        <v>-</v>
-      </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="17"/>
-      <c r="J14" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="22"/>
-      <c r="O14" s="23" t="str">
+      <c r="C14" s="34"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="10" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
     </row>
     <row r="15" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="31"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="20" t="str">
-        <f>IF(E15=0,"-",F15/D15)</f>
-        <v>-</v>
-      </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
-      <c r="M15" s="19"/>
-      <c r="N15" s="19"/>
-      <c r="O15" s="20" t="str">
+      <c r="C15" s="29"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="7" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
+      <c r="H15" s="2"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="7" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
     </row>
     <row r="16" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B16" s="69" t="s">
+      <c r="B16" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="70"/>
-      <c r="D16" s="26">
+      <c r="C16" s="36"/>
+      <c r="D16" s="13">
         <f>SUM(D11:D15)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="13">
         <f>SUM(E11:E15)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="13">
         <f>SUM(F11:F15)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="27" t="str">
-        <f>IF(E16=0,"-",F16/D16)</f>
-        <v>-</v>
-      </c>
-      <c r="H16" s="2"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="22"/>
-      <c r="N16" s="22"/>
-      <c r="O16" s="23" t="str">
+      <c r="G16" s="14" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
+      <c r="H16" s="2"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>-</v>
+      </c>
     </row>
     <row r="17" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="25" t="s">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="K17" s="26">
+      <c r="K17" s="13">
         <f>SUM(K11:K16)</f>
         <v>0</v>
       </c>
-      <c r="L17" s="26">
+      <c r="L17" s="13">
         <f>SUM(L11:L16)</f>
         <v>0</v>
       </c>
-      <c r="M17" s="26">
+      <c r="M17" s="13">
         <f>SUM(M11:M16)</f>
         <v>0</v>
       </c>
-      <c r="N17" s="26">
+      <c r="N17" s="13">
         <f>SUM(N11:N16)</f>
         <v>0</v>
       </c>
-      <c r="O17" s="27" t="str">
-        <f t="shared" si="0"/>
+      <c r="O17" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
     </row>
     <row r="18" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="14"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
     </row>
     <row r="19" spans="2:15" ht="27.75" customHeight="1">
-      <c r="B19" s="66" t="s">
+      <c r="B19" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="67"/>
-      <c r="D19" s="67"/>
-      <c r="E19" s="67"/>
-      <c r="F19" s="67"/>
-      <c r="G19" s="68"/>
-      <c r="H19" s="14"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="3"/>
       <c r="I19" s="2"/>
-      <c r="J19" s="66" t="s">
+      <c r="J19" s="57" t="s">
         <v>61</v>
       </c>
-      <c r="K19" s="67"/>
-      <c r="L19" s="67"/>
-      <c r="M19" s="67"/>
-      <c r="N19" s="67"/>
-      <c r="O19" s="68"/>
+      <c r="K19" s="58"/>
+      <c r="L19" s="58"/>
+      <c r="M19" s="58"/>
+      <c r="N19" s="58"/>
+      <c r="O19" s="59"/>
     </row>
     <row r="20" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="29"/>
-      <c r="D20" s="34" t="s">
+      <c r="C20" s="44"/>
+      <c r="D20" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="16"/>
-      <c r="F20" s="34" t="s">
+      <c r="E20" s="31"/>
+      <c r="F20" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="G20" s="16"/>
-      <c r="H20" s="14"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="3"/>
       <c r="I20" s="2"/>
-      <c r="J20" s="28" t="s">
+      <c r="J20" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="K20" s="29"/>
-      <c r="L20" s="34" t="s">
+      <c r="K20" s="44"/>
+      <c r="L20" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="M20" s="16"/>
-      <c r="N20" s="34" t="s">
+      <c r="M20" s="31"/>
+      <c r="N20" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="O20" s="16"/>
+      <c r="O20" s="31"/>
     </row>
     <row r="21" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B21" s="30" t="s">
+      <c r="B21" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="C21" s="31"/>
-      <c r="D21" s="35">
-        <v>50</v>
-      </c>
-      <c r="E21" s="16"/>
-      <c r="F21" s="36">
+      <c r="C21" s="29"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="32" t="str">
         <f>IF(D24=0,"-",D21/D24)</f>
-        <v>0.54347826086956519</v>
-      </c>
-      <c r="G21" s="16"/>
-      <c r="H21" s="14"/>
+        <v>-</v>
+      </c>
+      <c r="G21" s="31"/>
+      <c r="H21" s="3"/>
       <c r="I21" s="2"/>
-      <c r="J21" s="30" t="s">
+      <c r="J21" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="K21" s="31"/>
-      <c r="L21" s="35"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="35"/>
-      <c r="O21" s="16"/>
+      <c r="K21" s="29"/>
+      <c r="L21" s="30"/>
+      <c r="M21" s="31"/>
+      <c r="N21" s="30"/>
+      <c r="O21" s="31"/>
     </row>
     <row r="22" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B22" s="32" t="s">
+      <c r="B22" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="C22" s="33"/>
-      <c r="D22" s="37">
-        <v>21</v>
-      </c>
-      <c r="E22" s="16"/>
-      <c r="F22" s="38">
+      <c r="C22" s="34"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="73" t="str">
         <f>IF(D24=0,"-",D22/D24)</f>
-        <v>0.22826086956521738</v>
-      </c>
-      <c r="G22" s="16"/>
-      <c r="H22" s="14"/>
+        <v>-</v>
+      </c>
+      <c r="G22" s="31"/>
+      <c r="H22" s="3"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="32" t="s">
+      <c r="J22" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="K22" s="33"/>
-      <c r="L22" s="37"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="37"/>
-      <c r="O22" s="16"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="70"/>
+      <c r="M22" s="31"/>
+      <c r="N22" s="70"/>
+      <c r="O22" s="31"/>
     </row>
     <row r="23" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B23" s="30" t="s">
+      <c r="B23" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="31"/>
-      <c r="D23" s="35">
-        <v>21</v>
-      </c>
-      <c r="E23" s="16"/>
-      <c r="F23" s="36">
+      <c r="C23" s="29"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="32" t="str">
         <f>IF(D24=0,"-",D23/D24)</f>
-        <v>0.22826086956521738</v>
-      </c>
-      <c r="G23" s="16"/>
-      <c r="H23" s="14"/>
+        <v>-</v>
+      </c>
+      <c r="G23" s="31"/>
+      <c r="H23" s="3"/>
       <c r="I23" s="2"/>
-      <c r="J23" s="30" t="s">
+      <c r="J23" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="K23" s="31"/>
-      <c r="L23" s="35"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="35"/>
-      <c r="O23" s="16"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="31"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="31"/>
     </row>
     <row r="24" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B24" s="39" t="s">
+      <c r="B24" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="40"/>
-      <c r="D24" s="41">
+      <c r="C24" s="24"/>
+      <c r="D24" s="62">
         <f>SUM(D21:E23)</f>
-        <v>92</v>
-      </c>
-      <c r="E24" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="E24" s="31"/>
       <c r="F24" s="74">
         <v>1</v>
       </c>
-      <c r="G24" s="16"/>
-      <c r="H24" s="14"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="3"/>
       <c r="I24" s="2"/>
-      <c r="J24" s="39" t="s">
+      <c r="J24" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="K24" s="40"/>
-      <c r="L24" s="71">
+      <c r="K24" s="24"/>
+      <c r="L24" s="25">
         <f>SUM(L21:M23)</f>
         <v>0</v>
       </c>
-      <c r="M24" s="72"/>
-      <c r="N24" s="72"/>
-      <c r="O24" s="73"/>
+      <c r="M24" s="26"/>
+      <c r="N24" s="26"/>
+      <c r="O24" s="27"/>
     </row>
     <row r="25" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -3158,149 +3152,190 @@
       <c r="O25" s="2"/>
     </row>
     <row r="26" spans="2:15" ht="27.75" customHeight="1">
-      <c r="B26" s="61" t="s">
+      <c r="B26" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="C26" s="62"/>
-      <c r="D26" s="62"/>
-      <c r="E26" s="62"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="62"/>
-      <c r="H26" s="62"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="62"/>
-      <c r="K26" s="62"/>
-      <c r="L26" s="62"/>
-      <c r="M26" s="62"/>
-      <c r="N26" s="62"/>
-      <c r="O26" s="62"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="47"/>
+      <c r="J26" s="47"/>
+      <c r="K26" s="47"/>
+      <c r="L26" s="47"/>
+      <c r="M26" s="47"/>
+      <c r="N26" s="47"/>
+      <c r="O26" s="47"/>
     </row>
     <row r="27" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B27" s="42" t="s">
+      <c r="B27" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="C27" s="43"/>
-      <c r="D27" s="44" t="s">
+      <c r="C27" s="42"/>
+      <c r="D27" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="E27" s="44" t="s">
+      <c r="E27" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="44" t="s">
+      <c r="F27" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="G27" s="44" t="s">
+      <c r="G27" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="H27" s="44" t="s">
+      <c r="H27" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="I27" s="44" t="s">
+      <c r="I27" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="J27" s="44" t="s">
+      <c r="J27" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="K27" s="44" t="s">
+      <c r="K27" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="L27" s="44" t="s">
+      <c r="L27" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="M27" s="44" t="s">
+      <c r="M27" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="N27" s="44" t="s">
+      <c r="N27" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="O27" s="44" t="s">
+      <c r="O27" s="15" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="28" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B28" s="56" t="s">
+      <c r="B28" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="C28" s="57"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="45"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="45"/>
-      <c r="J28" s="45"/>
-      <c r="K28" s="45"/>
-      <c r="L28" s="45"/>
-      <c r="M28" s="45"/>
-      <c r="N28" s="45"/>
-      <c r="O28" s="46"/>
+      <c r="C28" s="54"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
+      <c r="N28" s="16"/>
+      <c r="O28" s="17"/>
     </row>
     <row r="29" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B29" s="58" t="s">
+      <c r="B29" s="63" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="59"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="47"/>
-      <c r="H29" s="47"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="47"/>
-      <c r="K29" s="47"/>
-      <c r="L29" s="47"/>
-      <c r="M29" s="47"/>
-      <c r="N29" s="47"/>
-      <c r="O29" s="48"/>
+      <c r="C29" s="64"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="18"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="18"/>
+      <c r="M29" s="18"/>
+      <c r="N29" s="18"/>
+      <c r="O29" s="19"/>
     </row>
     <row r="30" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B30" s="52" t="s">
+      <c r="B30" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="C30" s="53"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="45"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="45"/>
-      <c r="K30" s="45"/>
-      <c r="L30" s="45"/>
-      <c r="M30" s="45"/>
-      <c r="N30" s="45"/>
-      <c r="O30" s="46"/>
+      <c r="C30" s="66"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="16"/>
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
+      <c r="M30" s="16"/>
+      <c r="N30" s="16"/>
+      <c r="O30" s="17"/>
     </row>
     <row r="31" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B31" s="54" t="s">
+      <c r="B31" s="55" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="55"/>
-      <c r="D31" s="49" t="s">
+      <c r="C31" s="56"/>
+      <c r="D31" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="E31" s="50" t="str">
+      <c r="E31" s="21" t="str">
         <f>IF(D28=0,"-",E28/D28)</f>
         <v>-</v>
       </c>
-      <c r="F31" s="50"/>
-      <c r="G31" s="50"/>
-      <c r="H31" s="50"/>
-      <c r="I31" s="50"/>
-      <c r="J31" s="50"/>
-      <c r="K31" s="50"/>
-      <c r="L31" s="50"/>
-      <c r="M31" s="50"/>
-      <c r="N31" s="50"/>
-      <c r="O31" s="51"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="21"/>
+      <c r="K31" s="21"/>
+      <c r="L31" s="21"/>
+      <c r="M31" s="21"/>
+      <c r="N31" s="21"/>
+      <c r="O31" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:O24"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="J9:O9"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="J19:O19"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="B26:O26"/>
+    <mergeCell ref="J5:O5"/>
+    <mergeCell ref="B4:O4"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="D6:E6"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
@@ -3310,54 +3345,13 @@
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="B26:O26"/>
-    <mergeCell ref="J5:O5"/>
-    <mergeCell ref="B4:O4"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="J19:O19"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="J9:O9"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="L7:M7"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:O24"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
     <mergeCell ref="F24:G24"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="N21:O21"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/my_project/templates/template_B.xlsx
+++ b/my_project/templates/template_B.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\OneDrive\바탕 화면\my_project\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="37140" windowHeight="13905" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="37140" windowHeight="10845" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="요약보고서" sheetId="1" r:id="rId1"/>
@@ -19,17 +19,41 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="66">
-  <si>
-    <t>정상 운영</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="63">
+  <si>
+    <t>임관리비 / 재고 현황 요약 보고서</t>
+  </si>
+  <si>
+    <t>▎ 전체 현황 요약</t>
+  </si>
+  <si>
+    <t>전체</t>
   </si>
   <si>
     <t>폐업</t>
   </si>
   <si>
+    <t>출고중</t>
+  </si>
+  <si>
+    <t>보유중</t>
+  </si>
+  <si>
+    <t>▎ 지역별 가맹점 현황</t>
+  </si>
+  <si>
+    <t>▎ 임대자산 현황</t>
+  </si>
+  <si>
     <t>지역</t>
   </si>
   <si>
+    <t>정상운영</t>
+  </si>
+  <si>
+    <t>폐업률</t>
+  </si>
+  <si>
     <t>구분</t>
   </si>
   <si>
@@ -45,40 +69,79 @@
     <t>자산가치(원)</t>
   </si>
   <si>
+    <t>출고율</t>
+  </si>
+  <si>
+    <t>충청</t>
+  </si>
+  <si>
+    <t>무상임대(A-1)</t>
+  </si>
+  <si>
+    <t>경기</t>
+  </si>
+  <si>
+    <t>무상임대(A-2)</t>
+  </si>
+  <si>
+    <t>경상</t>
+  </si>
+  <si>
+    <t>유상임대(A-2)</t>
+  </si>
+  <si>
+    <t>강원</t>
+  </si>
+  <si>
+    <t>무상임대(A-3)</t>
+  </si>
+  <si>
+    <t>전라</t>
+  </si>
+  <si>
+    <t>유상임대(A-3)</t>
+  </si>
+  <si>
+    <t>합계</t>
+  </si>
+  <si>
+    <t>중고출고(A-3)</t>
+  </si>
+  <si>
+    <t>▎ 자산 보관 현황</t>
+  </si>
+  <si>
+    <t>▎ 자산별 현황</t>
+  </si>
+  <si>
+    <t>보관위치</t>
+  </si>
+  <si>
     <t>비율</t>
   </si>
   <si>
-    <t>무상임대(A-1)</t>
-  </si>
-  <si>
-    <t>경기</t>
-  </si>
-  <si>
-    <t>무상임대(A-2)</t>
-  </si>
-  <si>
-    <t>경상</t>
-  </si>
-  <si>
-    <t>유상임대(A-2)</t>
-  </si>
-  <si>
-    <t>강원</t>
-  </si>
-  <si>
-    <t>무상임대(A-3)</t>
-  </si>
-  <si>
-    <t>전라</t>
-  </si>
-  <si>
-    <t>유상임대(A-3)</t>
-  </si>
-  <si>
-    <t>합계</t>
-  </si>
-  <si>
-    <t>중고출고(A-3)</t>
+    <t>제품</t>
+  </si>
+  <si>
+    <t>출고 대수</t>
+  </si>
+  <si>
+    <t>보관 대수</t>
+  </si>
+  <si>
+    <t>A-1</t>
+  </si>
+  <si>
+    <t>본사보관</t>
+  </si>
+  <si>
+    <t>A-2</t>
+  </si>
+  <si>
+    <t>지사보관</t>
+  </si>
+  <si>
+    <t>A-3</t>
   </si>
   <si>
     <t>'25.01</t>
@@ -117,256 +180,40 @@
     <t>'25.12</t>
   </si>
   <si>
+    <t>임관리비 납부금액</t>
+  </si>
+  <si>
     <t>전월대비</t>
   </si>
   <si>
-    <t>보관위치</t>
-  </si>
-  <si>
-    <t>제품</t>
-  </si>
-  <si>
-    <t>A-1</t>
-  </si>
-  <si>
-    <t>A-2</t>
-  </si>
-  <si>
-    <t>A-3</t>
-  </si>
-  <si>
-    <t>가맹점</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>재고</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>전체</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>출고중</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>전체</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>보유중</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>임대자산 출고</t>
   </si>
   <si>
     <t>-</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>▎</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 지역별 가맹점 현황</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>▎</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 임대자산 현황</t>
-    </r>
-  </si>
-  <si>
-    <t>전월대비</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>임관리비 납부금액</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>임대자산 출고</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>충청</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>임관리비 / 재고 현황 요약 보고서</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Microsoft JhengHei Console"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>▎</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 전체 현황 요약</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>전체</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>정상운영</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>폐업</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>폐업률</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>출고율</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>출고 대수</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>보관 대수</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Microsoft JhengHei Console"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>▎</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 자산 보관 현황</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Microsoft JhengHei Console"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>▎</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 자산별 현황</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>지사보관</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>본사보관</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>출고</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Microsoft JhengHei Console"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>▎</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 월별 임관리비 납부 및 임대자산 출고 추이</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당연월</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>▎ 월별 임관리비 납부 및 임대자산 출고 추이</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 가맹점</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 재고</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -378,7 +225,7 @@
     <numFmt numFmtId="177" formatCode="\+0.0%;\-0.0%"/>
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-_);_(@_)"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -388,14 +235,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
@@ -420,21 +259,6 @@
       <name val="G마켓 산스 TTF Medium"/>
       <family val="3"/>
       <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Microsoft JhengHei Console"/>
-      <family val="3"/>
-      <charset val="136"/>
     </font>
     <font>
       <b/>
@@ -569,7 +393,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -658,17 +482,6 @@
       <bottom style="thin">
         <color rgb="FFB4C6E7"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB4C6E7"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFB4C6E7"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -775,15 +588,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB4C6E7"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color rgb="FFB4C6E7"/>
@@ -792,239 +596,236 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB4C6E7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB4C6E7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color theme="8"/>
+      </right>
+      <top style="thin">
+        <color theme="8"/>
+      </top>
+      <bottom style="hair">
+        <color theme="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color theme="8"/>
+      </right>
+      <top style="hair">
+        <color theme="8"/>
+      </top>
+      <bottom style="thin">
+        <color theme="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="13" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="13" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="13" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1136,11 +937,11 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" baseline="0">
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
-                    <a:lumMod val="50000"/>
-                    <a:lumOff val="50000"/>
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -1149,22 +950,22 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="ko-KR" altLang="en-US"/>
-              <a:t>월별 임관리비 납부 및 임대자산 출고 추이</a:t>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1800" b="1"/>
+              <a:t>▎ 월별 임관리비 납부 및 임대자산 출고 추이</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR"/>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1800" b="1"/>
               <a:t>(</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="ko-KR" altLang="en-US"/>
+              <a:rPr lang="ko-KR" altLang="en-US" sz="1800" b="1"/>
               <a:t>그래프</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR"/>
+              <a:rPr lang="en-US" altLang="ko-KR" sz="1800" b="1"/>
               <a:t>)</a:t>
             </a:r>
-            <a:endParaRPr lang="ko-KR"/>
+            <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1800" b="1"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -1182,11 +983,11 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" baseline="0">
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
-                  <a:lumMod val="50000"/>
-                  <a:lumOff val="50000"/>
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -1209,9 +1010,9 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>요약보고서!$B$28:$E$28</c:f>
+              <c:f>요약보고서!$B$28</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>임관리비 납부금액</c:v>
                 </c:pt>
@@ -1219,50 +1020,122 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="38100" cap="flat" cmpd="dbl" algn="ctr">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:miter lim="800000"/>
+              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>요약보고서!$F$27:$O$27</c:f>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>요약보고서!$C$27:$O$27</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>요약보고서!$D$27:$O$27</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
+                  <c:v>'25.01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>'25.02</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>'25.03</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>'25.04</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>'25.05</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>'25.06</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>'25.07</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>'25.08</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>'25.09</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>'25.10</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>'25.11</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>'25.12</c:v>
                 </c:pt>
               </c:strCache>
@@ -1270,28 +1143,52 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>요약보고서!$F$28:$O$28</c:f>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>요약보고서!$C$28:$O$28</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>요약보고서!$D$28:$O$28</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="12"/>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3121-47EF-9BD8-88AF9FBCC688}"/>
+              <c16:uniqueId val="{00000000-6DF1-484C-972A-AA538BF060E8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1310948831"/>
+        <c:axId val="1310958399"/>
+      </c:lineChart>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
+          <c:idx val="1"/>
+          <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>요약보고서!$B$30:$E$30</c:f>
+              <c:f>요약보고서!$B$30</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>임대자산 출고</c:v>
                 </c:pt>
@@ -1299,50 +1196,122 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="38100" cap="flat" cmpd="dbl" algn="ctr">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
-              <a:miter lim="800000"/>
+              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>요약보고서!$F$27:$O$27</c:f>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>요약보고서!$C$27:$O$27</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>요약보고서!$D$27:$O$27</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
+                  <c:v>'25.01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>'25.02</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>'25.03</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>'25.04</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>'25.05</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>'25.06</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>'25.07</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>'25.08</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>'25.09</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>'25.10</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>'25.11</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>'25.12</c:v>
                 </c:pt>
               </c:strCache>
@@ -1350,17 +1319,24 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>요약보고서!$F$30:$O$30</c:f>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>요약보고서!$C$30:$O$30</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>요약보고서!$D$30:$O$30</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="12"/>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-3121-47EF-9BD8-88AF9FBCC688}"/>
+              <c16:uniqueId val="{00000001-6DF1-484C-972A-AA538BF060E8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1372,275 +1348,25 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
+        <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="1310956319"/>
-        <c:axId val="1310958815"/>
-        <c:extLst>
-          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-            <c15:filteredLineSeries>
-              <c15:ser>
-                <c:idx val="1"/>
-                <c:order val="1"/>
-                <c:tx>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>요약보고서!$B$29:$E$29</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:strCache>
-                      <c:ptCount val="4"/>
-                      <c:pt idx="0">
-                        <c:v>전월대비</c:v>
-                      </c:pt>
-                    </c:strCache>
-                  </c:strRef>
-                </c:tx>
-                <c:spPr>
-                  <a:ln w="38100" cap="flat" cmpd="dbl" algn="ctr">
-                    <a:solidFill>
-                      <a:schemeClr val="accent2"/>
-                    </a:solidFill>
-                    <a:miter lim="800000"/>
-                  </a:ln>
-                  <a:effectLst/>
-                </c:spPr>
-                <c:marker>
-                  <c:symbol val="circle"/>
-                  <c:size val="6"/>
-                  <c:spPr>
-                    <a:solidFill>
-                      <a:schemeClr val="accent2"/>
-                    </a:solidFill>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="lt1"/>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c:marker>
-                <c:cat>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>요약보고서!$F$27:$O$27</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:strCache>
-                      <c:ptCount val="10"/>
-                      <c:pt idx="0">
-                        <c:v>'25.03</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>'25.04</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>'25.05</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>'25.06</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>'25.07</c:v>
-                      </c:pt>
-                      <c:pt idx="5">
-                        <c:v>'25.08</c:v>
-                      </c:pt>
-                      <c:pt idx="6">
-                        <c:v>'25.09</c:v>
-                      </c:pt>
-                      <c:pt idx="7">
-                        <c:v>'25.10</c:v>
-                      </c:pt>
-                      <c:pt idx="8">
-                        <c:v>'25.11</c:v>
-                      </c:pt>
-                      <c:pt idx="9">
-                        <c:v>'25.12</c:v>
-                      </c:pt>
-                    </c:strCache>
-                  </c:strRef>
-                </c:cat>
-                <c:val>
-                  <c:numRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>요약보고서!$F$29:$O$29</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>#,##0</c:formatCode>
-                      <c:ptCount val="10"/>
-                    </c:numCache>
-                  </c:numRef>
-                </c:val>
-                <c:smooth val="0"/>
-                <c:extLst>
-                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000001-3121-47EF-9BD8-88AF9FBCC688}"/>
-                  </c:ext>
-                </c:extLst>
-              </c15:ser>
-            </c15:filteredLineSeries>
-            <c15:filteredLineSeries>
-              <c15:ser>
-                <c:idx val="3"/>
-                <c:order val="3"/>
-                <c:tx>
-                  <c:strRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>요약보고서!$B$31:$E$31</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:strCache>
-                      <c:ptCount val="4"/>
-                      <c:pt idx="0">
-                        <c:v>전월대비</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>-</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>-</c:v>
-                      </c:pt>
-                    </c:strCache>
-                  </c:strRef>
-                </c:tx>
-                <c:spPr>
-                  <a:ln w="38100" cap="flat" cmpd="dbl" algn="ctr">
-                    <a:solidFill>
-                      <a:schemeClr val="accent4"/>
-                    </a:solidFill>
-                    <a:miter lim="800000"/>
-                  </a:ln>
-                  <a:effectLst/>
-                </c:spPr>
-                <c:marker>
-                  <c:symbol val="circle"/>
-                  <c:size val="6"/>
-                  <c:spPr>
-                    <a:solidFill>
-                      <a:schemeClr val="accent4"/>
-                    </a:solidFill>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="lt1"/>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c:marker>
-                <c:cat>
-                  <c:strRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>요약보고서!$F$27:$O$27</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:strCache>
-                      <c:ptCount val="10"/>
-                      <c:pt idx="0">
-                        <c:v>'25.03</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>'25.04</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>'25.05</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>'25.06</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>'25.07</c:v>
-                      </c:pt>
-                      <c:pt idx="5">
-                        <c:v>'25.08</c:v>
-                      </c:pt>
-                      <c:pt idx="6">
-                        <c:v>'25.09</c:v>
-                      </c:pt>
-                      <c:pt idx="7">
-                        <c:v>'25.10</c:v>
-                      </c:pt>
-                      <c:pt idx="8">
-                        <c:v>'25.11</c:v>
-                      </c:pt>
-                      <c:pt idx="9">
-                        <c:v>'25.12</c:v>
-                      </c:pt>
-                    </c:strCache>
-                  </c:strRef>
-                </c:cat>
-                <c:val>
-                  <c:numRef>
-                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>요약보고서!$F$31:$O$31</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>\+0.0%;\-0.0%</c:formatCode>
-                      <c:ptCount val="10"/>
-                    </c:numCache>
-                  </c:numRef>
-                </c:val>
-                <c:smooth val="0"/>
-                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000003-3121-47EF-9BD8-88AF9FBCC688}"/>
-                  </c:ext>
-                </c:extLst>
-              </c15:ser>
-            </c15:filteredLineSeries>
-          </c:ext>
-        </c:extLst>
+        <c:axId val="1311033279"/>
+        <c:axId val="1311023295"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1310956319"/>
+        <c:axId val="1310948831"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                  <a:alpha val="32000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -1648,7 +1374,6 @@
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
-            <a:tailEnd type="none" w="med" len="lg"/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -1657,7 +1382,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1672,7 +1397,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1310958815"/>
+        <c:crossAx val="1310958399"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1680,7 +1405,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1310958815"/>
+        <c:axId val="1310958399"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1693,7 +1418,6 @@
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
                   <a:lumOff val="85000"/>
-                  <a:alpha val="32000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -1701,21 +1425,14 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-            <a:tailEnd type="none" w="med" len="lg"/>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -1724,7 +1441,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1739,10 +1456,69 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1310956319"/>
+        <c:crossAx val="1310948831"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:valAx>
+        <c:axId val="1311023295"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1311033279"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="1311033279"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1311023295"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -1752,7 +1528,7 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="t"/>
+      <c:legendPos val="b"/>
       <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
@@ -1767,7 +1543,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -1861,7 +1637,7 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="237">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -1872,7 +1648,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200" cap="all"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -1885,7 +1661,7 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
@@ -1893,7 +1669,6 @@
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
-        <a:tailEnd type="none" w="med" len="lg"/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -1919,7 +1694,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -1963,7 +1738,7 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
@@ -1978,7 +1753,7 @@
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
@@ -1995,17 +1770,17 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="38100" cap="flat" cmpd="dbl" algn="ctr">
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:miter lim="800000"/>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointLine>
@@ -2013,7 +1788,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
@@ -2024,20 +1799,19 @@
       <a:solidFill>
         <a:schemeClr val="phClr"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="lt1"/>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -2062,13 +1836,15 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2078,13 +1854,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:ln w="9525">
@@ -2105,13 +1881,14 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -2123,13 +1900,14 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:errorBar>
@@ -2140,6 +1918,12 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
@@ -2154,7 +1938,6 @@
           <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
-            <a:alpha val="32000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2169,14 +1952,14 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="5000"/>
             <a:lumOff val="95000"/>
-            <a:alpha val="32000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
@@ -2188,10 +1971,14 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
@@ -2203,13 +1990,14 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -2246,20 +2034,11 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-        <a:tailEnd type="none" w="med" len="lg"/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -2270,13 +2049,14 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:seriesLine>
@@ -2286,11 +2066,11 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1">
-        <a:lumMod val="50000"/>
-        <a:lumOff val="50000"/>
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1800" b="1" kern="1200" cap="all" spc="150" baseline="0"/>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -2302,7 +2082,12 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="12700" cap="rnd"/>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
     </cs:spPr>
   </cs:trendline>
   <cs:trendlineLabel>
@@ -2322,7 +2107,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -2331,8 +2116,8 @@
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -2348,18 +2133,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-        <a:tailEnd type="none" w="med" len="lg"/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -2369,6 +2142,12 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -2378,19 +2157,19 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>142874</xdr:colOff>
+      <xdr:colOff>145676</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
+      <xdr:rowOff>45942</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:colOff>11206</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>212912</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="차트 1"/>
+        <xdr:cNvPr id="5" name="차트 4"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -2588,121 +2367,130 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O31"/>
-  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="17.25"/>
+  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="17.25" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="7" width="13" style="1" customWidth="1"/>
-    <col min="8" max="9" width="7.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.75" style="1" customWidth="1"/>
-    <col min="11" max="13" width="13" style="1" customWidth="1"/>
-    <col min="14" max="14" width="16.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.5" style="2"/>
+    <col min="2" max="3" width="13" style="1" customWidth="1"/>
+    <col min="4" max="15" width="13.125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="8.5" style="2" customWidth="1"/>
+    <col min="17" max="16384" width="8.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" ht="12.75" customHeight="1"/>
-    <row r="2" spans="2:15" ht="31.5" customHeight="1">
+    <row r="1" spans="2:15" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="45" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
+        <v>0</v>
+      </c>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="46"/>
     </row>
-    <row r="3" spans="2:15" ht="13.5" customHeight="1"/>
-    <row r="4" spans="2:15" ht="27.75" customHeight="1">
-      <c r="B4" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
-      <c r="M4" s="47"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
+    <row r="3" spans="2:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="21"/>
     </row>
-    <row r="5" spans="2:15" ht="27.75" customHeight="1">
-      <c r="B5" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
+    <row r="5" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="63" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="K5" s="49"/>
-      <c r="L5" s="49"/>
-      <c r="M5" s="49"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="49"/>
+      <c r="J5" s="64" t="s">
+        <v>62</v>
+      </c>
+      <c r="K5" s="62"/>
+      <c r="L5" s="62"/>
+      <c r="M5" s="62"/>
+      <c r="N5" s="62"/>
+      <c r="O5" s="62"/>
     </row>
-    <row r="6" spans="2:15" ht="41.25" customHeight="1">
-      <c r="B6" s="60" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="51"/>
-      <c r="D6" s="61" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="51"/>
-      <c r="F6" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" s="51"/>
+    <row r="6" spans="2:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="23"/>
+      <c r="D6" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="23"/>
+      <c r="F6" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="23"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
-      <c r="J6" s="60" t="s">
-        <v>42</v>
-      </c>
-      <c r="K6" s="51"/>
-      <c r="L6" s="61" t="s">
-        <v>41</v>
-      </c>
-      <c r="M6" s="51"/>
-      <c r="N6" s="50" t="s">
-        <v>43</v>
-      </c>
-      <c r="O6" s="51"/>
+      <c r="J6" s="43" t="s">
+        <v>2</v>
+      </c>
+      <c r="K6" s="23"/>
+      <c r="L6" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="M6" s="23"/>
+      <c r="N6" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="O6" s="23"/>
     </row>
-    <row r="7" spans="2:15" ht="30" customHeight="1">
-      <c r="B7" s="69"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="51"/>
+    <row r="7" spans="2:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="27">
+        <v>1962</v>
+      </c>
+      <c r="C7" s="23"/>
+      <c r="D7" s="26">
+        <v>1891</v>
+      </c>
+      <c r="E7" s="23"/>
+      <c r="F7" s="28">
+        <v>71</v>
+      </c>
+      <c r="G7" s="23"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
-      <c r="J7" s="69"/>
-      <c r="K7" s="51"/>
-      <c r="L7" s="68"/>
-      <c r="M7" s="51"/>
-      <c r="N7" s="52"/>
-      <c r="O7" s="51"/>
+      <c r="J7" s="27">
+        <v>1962</v>
+      </c>
+      <c r="K7" s="23"/>
+      <c r="L7" s="26">
+        <v>1865</v>
+      </c>
+      <c r="M7" s="23"/>
+      <c r="N7" s="28">
+        <v>71</v>
+      </c>
+      <c r="O7" s="23"/>
     </row>
-    <row r="8" spans="2:15" ht="21.75" customHeight="1">
+    <row r="8" spans="2:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
@@ -2718,230 +2506,230 @@
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
     </row>
-    <row r="9" spans="2:15" ht="27.75" customHeight="1">
-      <c r="B9" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" s="40"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="40"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="40"/>
+    <row r="9" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
       <c r="H9" s="2"/>
       <c r="I9" s="4"/>
-      <c r="J9" s="71" t="s">
-        <v>46</v>
-      </c>
-      <c r="K9" s="72"/>
-      <c r="L9" s="72"/>
-      <c r="M9" s="72"/>
-      <c r="N9" s="72"/>
-      <c r="O9" s="31"/>
+      <c r="J9" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="K9" s="39"/>
+      <c r="L9" s="39"/>
+      <c r="M9" s="39"/>
+      <c r="N9" s="39"/>
+      <c r="O9" s="23"/>
     </row>
-    <row r="10" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B10" s="41" t="s">
+    <row r="10" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="35"/>
+      <c r="D10" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>56</v>
+      <c r="E10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="4"/>
-      <c r="J10" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>57</v>
+      <c r="J10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="11" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B11" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="7" t="str">
+    <row r="11" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="23"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="15" t="str">
         <f t="shared" ref="G11:G16" si="0">IF(E11=0,"-",F11/D11)</f>
         <v>-</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="4"/>
-      <c r="J11" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="7" t="str">
-        <f>IF(K11=0,"-",L11/K11)</f>
+      <c r="J11" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="57"/>
+      <c r="O11" s="15" t="str">
+        <f t="shared" ref="O11:O17" si="1">IF(K11=0,"-",L11/K11)</f>
         <v>-</v>
       </c>
     </row>
-    <row r="12" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B12" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="34"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="10" t="str">
+    <row r="12" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="23"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="16" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="4"/>
-      <c r="J12" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="10" t="str">
-        <f t="shared" ref="O12:O17" si="1">IF(K12=0,"-",L12/K12)</f>
+      <c r="J12" s="56" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="58"/>
+      <c r="O12" s="16" t="str">
+        <f t="shared" si="1"/>
         <v>-</v>
       </c>
     </row>
-    <row r="13" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B13" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="7" t="str">
+    <row r="13" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="23"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="15" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="4"/>
-      <c r="J13" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="7" t="str">
+      <c r="J13" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="57"/>
+      <c r="O13" s="15" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
     </row>
-    <row r="14" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B14" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="34"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="10" t="str">
+    <row r="14" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="23"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="16" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="4"/>
-      <c r="J14" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="10" t="str">
+      <c r="J14" s="56" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="58"/>
+      <c r="O14" s="16" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
     </row>
-    <row r="15" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B15" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="7" t="str">
+    <row r="15" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="23"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="15" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="4"/>
-      <c r="J15" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="7" t="str">
+      <c r="J15" s="55" t="s">
+        <v>26</v>
+      </c>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="57"/>
+      <c r="O15" s="15" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
     </row>
-    <row r="16" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B16" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="36"/>
-      <c r="D16" s="13">
+    <row r="16" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="25"/>
+      <c r="D16" s="9">
         <f>SUM(D11:D15)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="9">
         <f>SUM(E11:E15)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="9">
         <f>SUM(F11:F15)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="14" t="str">
+      <c r="G16" s="17" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="4"/>
-      <c r="J16" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="10" t="str">
+      <c r="J16" s="56" t="s">
+        <v>28</v>
+      </c>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="58"/>
+      <c r="O16" s="16" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
     </row>
-    <row r="17" spans="2:15" ht="21.75" customHeight="1">
+    <row r="17" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -2950,31 +2738,31 @@
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="K17" s="13">
+      <c r="J17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K17" s="9">
         <f>SUM(K11:K16)</f>
         <v>0</v>
       </c>
-      <c r="L17" s="13">
+      <c r="L17" s="9">
         <f>SUM(L11:L16)</f>
         <v>0</v>
       </c>
-      <c r="M17" s="13">
+      <c r="M17" s="9">
         <f>SUM(M11:M16)</f>
         <v>0</v>
       </c>
-      <c r="N17" s="13">
+      <c r="N17" s="59">
         <f>SUM(N11:N16)</f>
         <v>0</v>
       </c>
-      <c r="O17" s="14" t="str">
+      <c r="O17" s="17" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
     </row>
-    <row r="18" spans="2:15" ht="21.75" customHeight="1">
+    <row r="18" spans="2:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -2990,152 +2778,152 @@
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
     </row>
-    <row r="19" spans="2:15" ht="27.75" customHeight="1">
-      <c r="B19" s="57" t="s">
-        <v>60</v>
-      </c>
-      <c r="C19" s="58"/>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
-      <c r="F19" s="58"/>
-      <c r="G19" s="59"/>
+    <row r="19" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="23"/>
       <c r="H19" s="3"/>
       <c r="I19" s="2"/>
-      <c r="J19" s="57" t="s">
-        <v>61</v>
-      </c>
-      <c r="K19" s="58"/>
-      <c r="L19" s="58"/>
-      <c r="M19" s="58"/>
-      <c r="N19" s="58"/>
-      <c r="O19" s="59"/>
+      <c r="J19" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="K19" s="39"/>
+      <c r="L19" s="39"/>
+      <c r="M19" s="39"/>
+      <c r="N19" s="39"/>
+      <c r="O19" s="23"/>
     </row>
-    <row r="20" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B20" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="44"/>
-      <c r="D20" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="31"/>
-      <c r="F20" s="67" t="s">
-        <v>8</v>
-      </c>
-      <c r="G20" s="31"/>
+    <row r="20" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="23"/>
+      <c r="D20" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="23"/>
+      <c r="F20" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" s="23"/>
       <c r="H20" s="3"/>
       <c r="I20" s="2"/>
-      <c r="J20" s="43" t="s">
+      <c r="J20" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="K20" s="23"/>
+      <c r="L20" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="K20" s="44"/>
-      <c r="L20" s="67" t="s">
-        <v>58</v>
-      </c>
-      <c r="M20" s="31"/>
-      <c r="N20" s="67" t="s">
-        <v>59</v>
-      </c>
-      <c r="O20" s="31"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="O20" s="23"/>
     </row>
-    <row r="21" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B21" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="29"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="32" t="str">
+    <row r="21" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="23"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="37" t="str">
         <f>IF(D24=0,"-",D21/D24)</f>
         <v>-</v>
       </c>
-      <c r="G21" s="31"/>
+      <c r="G21" s="23"/>
       <c r="H21" s="3"/>
       <c r="I21" s="2"/>
-      <c r="J21" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="K21" s="29"/>
-      <c r="L21" s="30"/>
-      <c r="M21" s="31"/>
-      <c r="N21" s="30"/>
-      <c r="O21" s="31"/>
+      <c r="J21" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="K21" s="23"/>
+      <c r="L21" s="36"/>
+      <c r="M21" s="23"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="23"/>
     </row>
-    <row r="22" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B22" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" s="34"/>
-      <c r="D22" s="70"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="73" t="str">
+    <row r="22" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="23"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="51" t="str">
         <f>IF(D24=0,"-",D22/D24)</f>
         <v>-</v>
       </c>
-      <c r="G22" s="31"/>
+      <c r="G22" s="23"/>
       <c r="H22" s="3"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="K22" s="34"/>
-      <c r="L22" s="70"/>
-      <c r="M22" s="31"/>
-      <c r="N22" s="70"/>
-      <c r="O22" s="31"/>
+      <c r="J22" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="K22" s="23"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="31"/>
+      <c r="O22" s="23"/>
     </row>
-    <row r="23" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B23" s="28" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" s="29"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="32" t="str">
+    <row r="23" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="23"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="37" t="str">
         <f>IF(D24=0,"-",D23/D24)</f>
         <v>-</v>
       </c>
-      <c r="G23" s="31"/>
+      <c r="G23" s="23"/>
       <c r="H23" s="3"/>
       <c r="I23" s="2"/>
-      <c r="J23" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="K23" s="29"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="31"/>
-      <c r="N23" s="30"/>
-      <c r="O23" s="31"/>
+      <c r="J23" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="K23" s="23"/>
+      <c r="L23" s="36"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="36"/>
+      <c r="O23" s="23"/>
     </row>
-    <row r="24" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B24" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" s="24"/>
-      <c r="D24" s="62">
+    <row r="24" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="23"/>
+      <c r="D24" s="52">
         <f>SUM(D21:E23)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="31"/>
-      <c r="F24" s="74">
+      <c r="E24" s="23"/>
+      <c r="F24" s="42">
         <v>1</v>
       </c>
-      <c r="G24" s="31"/>
+      <c r="G24" s="23"/>
       <c r="H24" s="3"/>
       <c r="I24" s="2"/>
-      <c r="J24" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="K24" s="24"/>
-      <c r="L24" s="25">
+      <c r="J24" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="K24" s="23"/>
+      <c r="L24" s="52">
         <f>SUM(L21:M23)</f>
         <v>0</v>
       </c>
-      <c r="M24" s="26"/>
-      <c r="N24" s="26"/>
-      <c r="O24" s="27"/>
+      <c r="M24" s="39"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="23"/>
     </row>
-    <row r="25" spans="2:15" ht="21.75" customHeight="1">
+    <row r="25" spans="2:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -3151,209 +2939,274 @@
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
     </row>
-    <row r="26" spans="2:15" ht="27.75" customHeight="1">
-      <c r="B26" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="47"/>
-      <c r="J26" s="47"/>
-      <c r="K26" s="47"/>
-      <c r="L26" s="47"/>
-      <c r="M26" s="47"/>
-      <c r="N26" s="47"/>
-      <c r="O26" s="47"/>
+    <row r="26" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="21"/>
+      <c r="M26" s="21"/>
+      <c r="N26" s="21"/>
+      <c r="O26" s="21"/>
     </row>
-    <row r="27" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B27" s="41" t="s">
-        <v>3</v>
-      </c>
-      <c r="C27" s="42"/>
-      <c r="D27" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="G27" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="H27" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="I27" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="J27" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="K27" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="L27" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="M27" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="N27" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="O27" s="15" t="s">
-        <v>31</v>
+    <row r="27" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="35"/>
+      <c r="D27" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="K27" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="L27" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="M27" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="N27" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="O27" s="10" t="s">
+        <v>52</v>
       </c>
     </row>
-    <row r="28" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B28" s="53" t="s">
-        <v>48</v>
-      </c>
-      <c r="C28" s="54"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="16"/>
-      <c r="O28" s="17"/>
+    <row r="28" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="50"/>
+      <c r="D28" s="60"/>
+      <c r="E28" s="60"/>
+      <c r="F28" s="60"/>
+      <c r="G28" s="60"/>
+      <c r="H28" s="60"/>
+      <c r="I28" s="60"/>
+      <c r="J28" s="60"/>
+      <c r="K28" s="60"/>
+      <c r="L28" s="60"/>
+      <c r="M28" s="60"/>
+      <c r="N28" s="60"/>
+      <c r="O28" s="61"/>
     </row>
-    <row r="29" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B29" s="63" t="s">
-        <v>47</v>
-      </c>
-      <c r="C29" s="64"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="18"/>
-      <c r="K29" s="18"/>
-      <c r="L29" s="18"/>
-      <c r="M29" s="18"/>
-      <c r="N29" s="18"/>
-      <c r="O29" s="19"/>
+    <row r="29" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="33"/>
+      <c r="D29" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E29" s="18" t="str">
+        <f>IF(E28=0,"-",E28/D28-1)</f>
+        <v>-</v>
+      </c>
+      <c r="F29" s="18" t="str">
+        <f t="shared" ref="F29" si="2">IF(F28=0,"-",F28/E28-1)</f>
+        <v>-</v>
+      </c>
+      <c r="G29" s="18" t="str">
+        <f t="shared" ref="G29" si="3">IF(G28=0,"-",G28/F28-1)</f>
+        <v>-</v>
+      </c>
+      <c r="H29" s="18" t="str">
+        <f t="shared" ref="H29" si="4">IF(H28=0,"-",H28/G28-1)</f>
+        <v>-</v>
+      </c>
+      <c r="I29" s="18" t="str">
+        <f t="shared" ref="I29" si="5">IF(I28=0,"-",I28/H28-1)</f>
+        <v>-</v>
+      </c>
+      <c r="J29" s="18" t="str">
+        <f t="shared" ref="J29" si="6">IF(J28=0,"-",J28/I28-1)</f>
+        <v>-</v>
+      </c>
+      <c r="K29" s="18" t="str">
+        <f t="shared" ref="K29" si="7">IF(K28=0,"-",K28/J28-1)</f>
+        <v>-</v>
+      </c>
+      <c r="L29" s="18" t="str">
+        <f t="shared" ref="L29" si="8">IF(L28=0,"-",L28/K28-1)</f>
+        <v>-</v>
+      </c>
+      <c r="M29" s="18" t="str">
+        <f t="shared" ref="M29" si="9">IF(M28=0,"-",M28/L28-1)</f>
+        <v>-</v>
+      </c>
+      <c r="N29" s="18" t="str">
+        <f t="shared" ref="N29" si="10">IF(N28=0,"-",N28/M28-1)</f>
+        <v>-</v>
+      </c>
+      <c r="O29" s="19" t="str">
+        <f t="shared" ref="O29" si="11">IF(O28=0,"-",O28/N28-1)</f>
+        <v>-</v>
+      </c>
     </row>
-    <row r="30" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B30" s="65" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" s="66"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="16"/>
-      <c r="O30" s="17"/>
+    <row r="30" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="50"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="12"/>
     </row>
-    <row r="31" spans="2:15" ht="21.75" customHeight="1">
-      <c r="B31" s="55" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" s="56"/>
-      <c r="D31" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="E31" s="21" t="str">
-        <f>IF(D28=0,"-",E28/D28)</f>
-        <v>-</v>
-      </c>
-      <c r="F31" s="21"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="21"/>
-      <c r="I31" s="21"/>
-      <c r="J31" s="21"/>
-      <c r="K31" s="21"/>
-      <c r="L31" s="21"/>
-      <c r="M31" s="21"/>
-      <c r="N31" s="21"/>
-      <c r="O31" s="22"/>
+    <row r="31" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="33"/>
+      <c r="D31" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E31" s="18" t="str">
+        <f>IF(E30=0,"-",E30/D30-1)</f>
+        <v>-</v>
+      </c>
+      <c r="F31" s="18" t="str">
+        <f t="shared" ref="F31:O31" si="12">IF(F30=0,"-",F30/E30-1)</f>
+        <v>-</v>
+      </c>
+      <c r="G31" s="18" t="str">
+        <f t="shared" si="12"/>
+        <v>-</v>
+      </c>
+      <c r="H31" s="18" t="str">
+        <f t="shared" si="12"/>
+        <v>-</v>
+      </c>
+      <c r="I31" s="18" t="str">
+        <f t="shared" si="12"/>
+        <v>-</v>
+      </c>
+      <c r="J31" s="18" t="str">
+        <f t="shared" si="12"/>
+        <v>-</v>
+      </c>
+      <c r="K31" s="18" t="str">
+        <f t="shared" si="12"/>
+        <v>-</v>
+      </c>
+      <c r="L31" s="18" t="str">
+        <f t="shared" si="12"/>
+        <v>-</v>
+      </c>
+      <c r="M31" s="18" t="str">
+        <f t="shared" si="12"/>
+        <v>-</v>
+      </c>
+      <c r="N31" s="18" t="str">
+        <f t="shared" si="12"/>
+        <v>-</v>
+      </c>
+      <c r="O31" s="19" t="str">
+        <f t="shared" si="12"/>
+        <v>-</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="62">
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J5:O5"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="J19:O19"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="J9:O9"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="B10:C10"/>
     <mergeCell ref="J7:K7"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="L24:O24"/>
+    <mergeCell ref="B26:O26"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B4:O4"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="F6:G6"/>
     <mergeCell ref="D22:E22"/>
-    <mergeCell ref="J9:O9"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J22:K22"/>
     <mergeCell ref="L22:M22"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="J19:O19"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="B26:O26"/>
-    <mergeCell ref="J5:O5"/>
-    <mergeCell ref="B4:O4"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="N7:O7"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:O24"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>

--- a/my_project/templates/template_B.xlsx
+++ b/my_project/templates/template_B.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\OneDrive\바탕 화면\my_project\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -708,68 +708,65 @@
     <xf numFmtId="177" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -778,54 +775,57 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="176" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -937,35 +937,41 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
                   </a:schemeClr>
                 </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="ko-KR" altLang="en-US" sz="1800" b="1"/>
+              <a:rPr lang="ko-KR"/>
               <a:t>▎ 월별 임관리비 납부 및 임대자산 출고 추이</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="1800" b="1"/>
+              <a:rPr lang="en-US"/>
               <a:t>(</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="ko-KR" altLang="en-US" sz="1800" b="1"/>
+              <a:rPr lang="ko-KR"/>
               <a:t>그래프</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" altLang="ko-KR" sz="1800" b="1"/>
+              <a:rPr lang="en-US"/>
               <a:t>)</a:t>
             </a:r>
-            <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1800" b="1"/>
+            <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -983,13 +989,19 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
                 </a:schemeClr>
               </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
@@ -1020,7 +1032,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="34925" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -1046,11 +1058,10 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
                       </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
@@ -1075,14 +1086,13 @@
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                    <a:ln w="9525">
                       <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="95000"/>
+                          <a:alpha val="54000"/>
                         </a:schemeClr>
                       </a:solidFill>
-                      <a:round/>
                     </a:ln>
                     <a:effectLst/>
                   </c:spPr>
@@ -1196,7 +1206,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln w="34925" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
@@ -1222,11 +1232,10 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
                       </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
@@ -1251,14 +1260,13 @@
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                    <a:ln w="9525">
                       <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="95000"/>
+                          <a:alpha val="54000"/>
                         </a:schemeClr>
                       </a:solidFill>
-                      <a:round/>
                     </a:ln>
                     <a:effectLst/>
                   </c:spPr>
@@ -1366,11 +1374,11 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+                <a:alpha val="54000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -1382,11 +1390,10 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -1415,9 +1422,9 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -1441,11 +1448,10 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -1468,7 +1474,7 @@
         <c:delete val="0"/>
         <c:axPos val="r"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
@@ -1483,11 +1489,10 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -1510,10 +1515,11 @@
         <c:delete val="1"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1311023295"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -1543,11 +1549,10 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -1564,17 +1569,28 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
     </a:ln>
     <a:effectLst/>
   </c:spPr>
@@ -1637,35 +1653,33 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="328">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -1673,26 +1687,34 @@
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+  <cs:chartArea>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
     </cs:spPr>
     <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
@@ -1701,9 +1723,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -1722,14 +1743,6 @@
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
@@ -1738,45 +1751,35 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="28575" cap="rnd">
+      <a:ln w="34925" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -1788,31 +1791,29 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
@@ -1830,21 +1831,18 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -1854,20 +1852,33 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="95000"/>
+              <a:lumOff val="5000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="75000"/>
+              <a:lumOff val="25000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+      </a:gradFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -1883,10 +1894,7 @@
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
+          <a:schemeClr val="lt1"/>
         </a:solidFill>
         <a:round/>
       </a:ln>
@@ -1902,9 +1910,8 @@
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -1918,12 +1925,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
@@ -1935,9 +1936,9 @@
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -1952,14 +1953,13 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln>
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
@@ -1973,10 +1973,7 @@
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
+          <a:schemeClr val="lt1"/>
         </a:solidFill>
         <a:round/>
       </a:ln>
@@ -1990,14 +1987,13 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -2006,14 +2002,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
@@ -2021,7 +2016,7 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea3D>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
@@ -2034,11 +2029,21 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -2046,14 +2051,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2065,12 +2070,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -2086,7 +2098,6 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -2095,9 +2106,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2107,19 +2117,29 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
+      <a:gradFill>
+        <a:gsLst>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="85000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
+          <a:schemeClr val="lt1"/>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -2128,9 +2148,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2142,12 +2161,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -2378,117 +2391,117 @@
   <sheetData>
     <row r="1" spans="2:15" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43"/>
     </row>
     <row r="3" spans="2:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
-      <c r="N4" s="21"/>
-      <c r="O4" s="21"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="61"/>
+      <c r="L4" s="61"/>
+      <c r="M4" s="61"/>
+      <c r="N4" s="61"/>
+      <c r="O4" s="61"/>
     </row>
     <row r="5" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="64" t="s">
+      <c r="J5" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="K5" s="62"/>
-      <c r="L5" s="62"/>
-      <c r="M5" s="62"/>
-      <c r="N5" s="62"/>
-      <c r="O5" s="62"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="33"/>
+      <c r="M5" s="33"/>
+      <c r="N5" s="33"/>
+      <c r="O5" s="33"/>
     </row>
     <row r="6" spans="2:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="41" t="s">
+      <c r="C6" s="28"/>
+      <c r="D6" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="E6" s="23"/>
-      <c r="F6" s="30" t="s">
+      <c r="E6" s="28"/>
+      <c r="F6" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="23"/>
+      <c r="G6" s="28"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
-      <c r="J6" s="43" t="s">
+      <c r="J6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="K6" s="23"/>
-      <c r="L6" s="41" t="s">
+      <c r="K6" s="28"/>
+      <c r="L6" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="M6" s="23"/>
-      <c r="N6" s="30" t="s">
+      <c r="M6" s="28"/>
+      <c r="N6" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="O6" s="23"/>
+      <c r="O6" s="28"/>
     </row>
     <row r="7" spans="2:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="27">
+      <c r="B7" s="51">
         <v>1962</v>
       </c>
-      <c r="C7" s="23"/>
-      <c r="D7" s="26">
+      <c r="C7" s="28"/>
+      <c r="D7" s="46">
         <v>1891</v>
       </c>
-      <c r="E7" s="23"/>
-      <c r="F7" s="28">
+      <c r="E7" s="28"/>
+      <c r="F7" s="56">
         <v>71</v>
       </c>
-      <c r="G7" s="23"/>
+      <c r="G7" s="28"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
-      <c r="J7" s="27">
+      <c r="J7" s="51">
         <v>1962</v>
       </c>
-      <c r="K7" s="23"/>
-      <c r="L7" s="26">
+      <c r="K7" s="28"/>
+      <c r="L7" s="46">
         <v>1865</v>
       </c>
-      <c r="M7" s="23"/>
-      <c r="N7" s="28">
+      <c r="M7" s="28"/>
+      <c r="N7" s="56">
         <v>71</v>
       </c>
-      <c r="O7" s="23"/>
+      <c r="O7" s="28"/>
     </row>
     <row r="8" spans="2:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="3"/>
@@ -2507,30 +2520,30 @@
       <c r="O8" s="3"/>
     </row>
     <row r="9" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
       <c r="H9" s="2"/>
       <c r="I9" s="4"/>
-      <c r="J9" s="54" t="s">
+      <c r="J9" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="K9" s="39"/>
-      <c r="L9" s="39"/>
-      <c r="M9" s="39"/>
-      <c r="N9" s="39"/>
-      <c r="O9" s="23"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="36"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="28"/>
     </row>
     <row r="10" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="35"/>
+      <c r="C10" s="50"/>
       <c r="D10" s="6" t="s">
         <v>2</v>
       </c>
@@ -2565,10 +2578,10 @@
       </c>
     </row>
     <row r="11" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="23"/>
+      <c r="C11" s="28"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
@@ -2578,23 +2591,23 @@
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="4"/>
-      <c r="J11" s="55" t="s">
+      <c r="J11" s="20" t="s">
         <v>18</v>
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
-      <c r="N11" s="57"/>
+      <c r="N11" s="22"/>
       <c r="O11" s="15" t="str">
         <f t="shared" ref="O11:O17" si="1">IF(K11=0,"-",L11/K11)</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="23"/>
+      <c r="C12" s="28"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
@@ -2604,23 +2617,23 @@
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="4"/>
-      <c r="J12" s="56" t="s">
+      <c r="J12" s="21" t="s">
         <v>20</v>
       </c>
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
-      <c r="N12" s="58"/>
+      <c r="N12" s="23"/>
       <c r="O12" s="16" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
     </row>
     <row r="13" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="23"/>
+      <c r="C13" s="28"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
@@ -2630,23 +2643,23 @@
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="4"/>
-      <c r="J13" s="55" t="s">
+      <c r="J13" s="20" t="s">
         <v>22</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
       <c r="M13" s="7"/>
-      <c r="N13" s="57"/>
+      <c r="N13" s="22"/>
       <c r="O13" s="15" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
     </row>
     <row r="14" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="23"/>
+      <c r="C14" s="28"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
@@ -2656,23 +2669,23 @@
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="4"/>
-      <c r="J14" s="56" t="s">
+      <c r="J14" s="21" t="s">
         <v>24</v>
       </c>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
-      <c r="N14" s="58"/>
+      <c r="N14" s="23"/>
       <c r="O14" s="16" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
     </row>
     <row r="15" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="23"/>
+      <c r="C15" s="28"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -2682,23 +2695,23 @@
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="4"/>
-      <c r="J15" s="55" t="s">
+      <c r="J15" s="20" t="s">
         <v>26</v>
       </c>
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
-      <c r="N15" s="57"/>
+      <c r="N15" s="22"/>
       <c r="O15" s="15" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
     </row>
     <row r="16" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="25"/>
+      <c r="C16" s="63"/>
       <c r="D16" s="9">
         <f>SUM(D11:D15)</f>
         <v>0</v>
@@ -2717,13 +2730,13 @@
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="4"/>
-      <c r="J16" s="56" t="s">
+      <c r="J16" s="21" t="s">
         <v>28</v>
       </c>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
       <c r="M16" s="8"/>
-      <c r="N16" s="58"/>
+      <c r="N16" s="23"/>
       <c r="O16" s="16" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
@@ -2753,7 +2766,7 @@
         <f>SUM(M11:M16)</f>
         <v>0</v>
       </c>
-      <c r="N17" s="59">
+      <c r="N17" s="24">
         <f>SUM(N11:N16)</f>
         <v>0</v>
       </c>
@@ -2779,149 +2792,149 @@
       <c r="O18" s="3"/>
     </row>
     <row r="19" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="38" t="s">
+      <c r="B19" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="23"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="28"/>
       <c r="H19" s="3"/>
       <c r="I19" s="2"/>
-      <c r="J19" s="38" t="s">
+      <c r="J19" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="K19" s="39"/>
-      <c r="L19" s="39"/>
-      <c r="M19" s="39"/>
-      <c r="N19" s="39"/>
-      <c r="O19" s="23"/>
+      <c r="K19" s="36"/>
+      <c r="L19" s="36"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="28"/>
     </row>
     <row r="20" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="23"/>
-      <c r="D20" s="22" t="s">
+      <c r="C20" s="28"/>
+      <c r="D20" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="23"/>
-      <c r="F20" s="22" t="s">
+      <c r="E20" s="28"/>
+      <c r="F20" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="23"/>
+      <c r="G20" s="28"/>
       <c r="H20" s="3"/>
       <c r="I20" s="2"/>
-      <c r="J20" s="22" t="s">
+      <c r="J20" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="K20" s="23"/>
-      <c r="L20" s="22" t="s">
+      <c r="K20" s="28"/>
+      <c r="L20" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="M20" s="23"/>
-      <c r="N20" s="22" t="s">
+      <c r="M20" s="28"/>
+      <c r="N20" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="O20" s="23"/>
+      <c r="O20" s="28"/>
     </row>
     <row r="21" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="40" t="s">
+      <c r="B21" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="23"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="37" t="str">
+      <c r="C21" s="28"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="48" t="str">
         <f>IF(D24=0,"-",D21/D24)</f>
         <v>-</v>
       </c>
-      <c r="G21" s="23"/>
+      <c r="G21" s="28"/>
       <c r="H21" s="3"/>
       <c r="I21" s="2"/>
-      <c r="J21" s="40" t="s">
+      <c r="J21" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="K21" s="23"/>
-      <c r="L21" s="36"/>
-      <c r="M21" s="23"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="23"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="38"/>
+      <c r="M21" s="28"/>
+      <c r="N21" s="38"/>
+      <c r="O21" s="28"/>
     </row>
     <row r="22" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="29" t="s">
+      <c r="B22" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="23"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="51" t="str">
+      <c r="C22" s="28"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="52" t="str">
         <f>IF(D24=0,"-",D22/D24)</f>
         <v>-</v>
       </c>
-      <c r="G22" s="23"/>
+      <c r="G22" s="28"/>
       <c r="H22" s="3"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="29" t="s">
+      <c r="J22" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="K22" s="23"/>
-      <c r="L22" s="31"/>
-      <c r="M22" s="23"/>
-      <c r="N22" s="31"/>
-      <c r="O22" s="23"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="28"/>
+      <c r="N22" s="55"/>
+      <c r="O22" s="28"/>
     </row>
     <row r="23" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="40" t="s">
+      <c r="B23" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="23"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="37" t="str">
+      <c r="C23" s="28"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="48" t="str">
         <f>IF(D24=0,"-",D23/D24)</f>
         <v>-</v>
       </c>
-      <c r="G23" s="23"/>
+      <c r="G23" s="28"/>
       <c r="H23" s="3"/>
       <c r="I23" s="2"/>
-      <c r="J23" s="40" t="s">
+      <c r="J23" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="K23" s="23"/>
-      <c r="L23" s="36"/>
-      <c r="M23" s="23"/>
-      <c r="N23" s="36"/>
-      <c r="O23" s="23"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="38"/>
+      <c r="M23" s="28"/>
+      <c r="N23" s="38"/>
+      <c r="O23" s="28"/>
     </row>
     <row r="24" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="44" t="s">
+      <c r="B24" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="23"/>
-      <c r="D24" s="52">
+      <c r="C24" s="28"/>
+      <c r="D24" s="34">
         <f>SUM(D21:E23)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="23"/>
-      <c r="F24" s="42">
+      <c r="E24" s="28"/>
+      <c r="F24" s="57">
         <v>1</v>
       </c>
-      <c r="G24" s="23"/>
+      <c r="G24" s="28"/>
       <c r="H24" s="3"/>
       <c r="I24" s="2"/>
-      <c r="J24" s="44" t="s">
+      <c r="J24" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="K24" s="23"/>
-      <c r="L24" s="52">
+      <c r="K24" s="28"/>
+      <c r="L24" s="34">
         <f>SUM(L21:M23)</f>
         <v>0</v>
       </c>
-      <c r="M24" s="39"/>
-      <c r="N24" s="39"/>
-      <c r="O24" s="23"/>
+      <c r="M24" s="36"/>
+      <c r="N24" s="36"/>
+      <c r="O24" s="28"/>
     </row>
     <row r="25" spans="2:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="3"/>
@@ -2940,28 +2953,28 @@
       <c r="O25" s="2"/>
     </row>
     <row r="26" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="20" t="s">
+      <c r="B26" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="21"/>
-      <c r="K26" s="21"/>
-      <c r="L26" s="21"/>
-      <c r="M26" s="21"/>
-      <c r="N26" s="21"/>
-      <c r="O26" s="21"/>
+      <c r="C26" s="61"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="61"/>
+      <c r="F26" s="61"/>
+      <c r="G26" s="61"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="61"/>
+      <c r="K26" s="61"/>
+      <c r="L26" s="61"/>
+      <c r="M26" s="61"/>
+      <c r="N26" s="61"/>
+      <c r="O26" s="61"/>
     </row>
     <row r="27" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="34" t="s">
+      <c r="B27" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="C27" s="35"/>
+      <c r="C27" s="50"/>
       <c r="D27" s="10" t="s">
         <v>41</v>
       </c>
@@ -3000,28 +3013,28 @@
       </c>
     </row>
     <row r="28" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="49" t="s">
+      <c r="B28" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="C28" s="50"/>
-      <c r="D28" s="60"/>
-      <c r="E28" s="60"/>
-      <c r="F28" s="60"/>
-      <c r="G28" s="60"/>
-      <c r="H28" s="60"/>
-      <c r="I28" s="60"/>
-      <c r="J28" s="60"/>
-      <c r="K28" s="60"/>
-      <c r="L28" s="60"/>
-      <c r="M28" s="60"/>
-      <c r="N28" s="60"/>
-      <c r="O28" s="61"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="25"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="25"/>
+      <c r="M28" s="25"/>
+      <c r="N28" s="25"/>
+      <c r="O28" s="26"/>
     </row>
     <row r="29" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="48" t="s">
+      <c r="B29" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="C29" s="33"/>
+      <c r="C29" s="54"/>
       <c r="D29" s="13" t="s">
         <v>58</v>
       </c>
@@ -3071,10 +3084,10 @@
       </c>
     </row>
     <row r="30" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="53" t="s">
+      <c r="B30" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="C30" s="50"/>
+      <c r="C30" s="30"/>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
@@ -3089,10 +3102,10 @@
       <c r="O30" s="12"/>
     </row>
     <row r="31" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="32" t="s">
+      <c r="B31" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="C31" s="33"/>
+      <c r="C31" s="54"/>
       <c r="D31" s="14" t="s">
         <v>56</v>
       </c>
@@ -3143,20 +3156,36 @@
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J5:O5"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="J19:O19"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="J9:O9"/>
-    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B4:O4"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="L24:O24"/>
     <mergeCell ref="B2:O2"/>
     <mergeCell ref="B9:G9"/>
     <mergeCell ref="F20:G20"/>
@@ -3173,38 +3202,22 @@
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="J7:K7"/>
     <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="L24:O24"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J5:O5"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="J19:O19"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="J9:O9"/>
+    <mergeCell ref="J23:K23"/>
     <mergeCell ref="B26:O26"/>
     <mergeCell ref="D20:E20"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B4:O4"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="B6:C6"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/my_project/templates/template_B.xlsx
+++ b/my_project/templates/template_B.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="62">
   <si>
     <t>임관리비 / 재고 현황 요약 보고서</t>
   </si>
@@ -180,13 +180,7 @@
     <t>'25.12</t>
   </si>
   <si>
-    <t>임관리비 납부금액</t>
-  </si>
-  <si>
     <t>전월대비</t>
-  </si>
-  <si>
-    <t>임대자산 출고</t>
   </si>
   <si>
     <t>-</t>
@@ -196,23 +190,27 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>-</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>해당연월</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>▎ 월별 임관리비 납부 및 임대자산 출고 추이</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> 가맹점</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve"> 재고</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>▎ 월별 임관리비 납부 및 임대자산 출고 추이</t>
+  </si>
+  <si>
+    <t>해당연월</t>
+  </si>
+  <si>
+    <t>임관리비
+납부금액</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>임대자산
+출고수량</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -393,7 +391,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -607,32 +605,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="hair">
-        <color theme="8"/>
-      </right>
-      <top style="thin">
-        <color theme="8"/>
-      </top>
-      <bottom style="hair">
-        <color theme="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="hair">
-        <color theme="8"/>
-      </right>
-      <top style="hair">
-        <color theme="8"/>
-      </top>
-      <bottom style="thin">
-        <color theme="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -651,7 +623,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -660,9 +632,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -676,9 +645,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -729,44 +695,71 @@
     <xf numFmtId="3" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -775,57 +768,41 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1026,7 +1003,8 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>임관리비 납부금액</c:v>
+                  <c:v>임관리비
+납부금액</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1111,41 +1089,38 @@
               </c:extLst>
               <c:f>요약보고서!$D$27:$O$27</c:f>
               <c:strCache>
-                <c:ptCount val="12"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>'25.01</c:v>
+                  <c:v>'25.02</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>'25.02</c:v>
+                  <c:v>'25.03</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>'25.03</c:v>
+                  <c:v>'25.04</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>'25.04</c:v>
+                  <c:v>'25.05</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>'25.05</c:v>
+                  <c:v>'25.06</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>'25.06</c:v>
+                  <c:v>'25.07</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>'25.07</c:v>
+                  <c:v>'25.08</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>'25.08</c:v>
+                  <c:v>'25.09</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>'25.09</c:v>
+                  <c:v>'25.10</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>'25.10</c:v>
+                  <c:v>'25.11</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>'25.11</c:v>
-                </c:pt>
-                <c:pt idx="11">
                   <c:v>'25.12</c:v>
                 </c:pt>
               </c:strCache>
@@ -1200,7 +1175,8 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>임대자산 출고</c:v>
+                  <c:v>임대자산
+출고수량</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1285,41 +1261,38 @@
               </c:extLst>
               <c:f>요약보고서!$D$27:$O$27</c:f>
               <c:strCache>
-                <c:ptCount val="12"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>'25.01</c:v>
+                  <c:v>'25.02</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>'25.02</c:v>
+                  <c:v>'25.03</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>'25.03</c:v>
+                  <c:v>'25.04</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>'25.04</c:v>
+                  <c:v>'25.05</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>'25.05</c:v>
+                  <c:v>'25.06</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>'25.06</c:v>
+                  <c:v>'25.07</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>'25.07</c:v>
+                  <c:v>'25.08</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>'25.08</c:v>
+                  <c:v>'25.09</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>'25.09</c:v>
+                  <c:v>'25.10</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>'25.10</c:v>
+                  <c:v>'25.11</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>'25.11</c:v>
-                </c:pt>
-                <c:pt idx="11">
                   <c:v>'25.12</c:v>
                 </c:pt>
               </c:strCache>
@@ -1432,7 +1405,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1473,7 +1446,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="r"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2175,8 +2148,8 @@
       <xdr:rowOff>45942</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>11206</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>49</xdr:row>
       <xdr:rowOff>212912</xdr:rowOff>
     </xdr:to>
@@ -2379,131 +2352,126 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="17.25" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
     <col min="2" max="3" width="13" style="1" customWidth="1"/>
-    <col min="4" max="15" width="13.125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="8.5" style="2" customWidth="1"/>
-    <col min="17" max="16384" width="8.5" style="2"/>
+    <col min="4" max="14" width="13.125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="8.5" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="8.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="42" t="s">
+    <row r="1" spans="2:14" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="43"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
     </row>
-    <row r="3" spans="2:15" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="60" t="s">
+    <row r="3" spans="2:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="61"/>
-      <c r="J4" s="61"/>
-      <c r="K4" s="61"/>
-      <c r="L4" s="61"/>
-      <c r="M4" s="61"/>
-      <c r="N4" s="61"/>
-      <c r="O4" s="61"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
     </row>
-    <row r="5" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="47" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
+    <row r="5" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="54" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="K5" s="33"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="33"/>
-      <c r="N5" s="33"/>
-      <c r="O5" s="33"/>
+      <c r="I5" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="J5" s="55"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="55"/>
+      <c r="M5" s="55"/>
+      <c r="N5" s="55"/>
     </row>
-    <row r="6" spans="2:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="64" t="s">
+    <row r="6" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="29" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="28"/>
-      <c r="D6" s="37" t="s">
-        <v>57</v>
+      <c r="D6" s="32" t="s">
+        <v>55</v>
       </c>
       <c r="E6" s="28"/>
-      <c r="F6" s="39" t="s">
+      <c r="F6" s="31" t="s">
         <v>3</v>
       </c>
       <c r="G6" s="28"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="64" t="s">
+      <c r="I6" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="K6" s="28"/>
-      <c r="L6" s="37" t="s">
+      <c r="J6" s="28"/>
+      <c r="K6" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="M6" s="28"/>
-      <c r="N6" s="39" t="s">
+      <c r="L6" s="28"/>
+      <c r="M6" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="O6" s="28"/>
+      <c r="N6" s="28"/>
     </row>
-    <row r="7" spans="2:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="51">
+    <row r="7" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="39">
         <v>1962</v>
       </c>
       <c r="C7" s="28"/>
-      <c r="D7" s="46">
+      <c r="D7" s="37">
         <v>1891</v>
       </c>
       <c r="E7" s="28"/>
-      <c r="F7" s="56">
+      <c r="F7" s="40">
         <v>71</v>
       </c>
       <c r="G7" s="28"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="51">
+      <c r="I7" s="39">
         <v>1962</v>
       </c>
-      <c r="K7" s="28"/>
-      <c r="L7" s="46">
+      <c r="J7" s="28"/>
+      <c r="K7" s="37">
         <v>1865</v>
       </c>
-      <c r="M7" s="28"/>
-      <c r="N7" s="56">
+      <c r="L7" s="28"/>
+      <c r="M7" s="40">
         <v>71</v>
       </c>
-      <c r="O7" s="28"/>
+      <c r="N7" s="28"/>
     </row>
-    <row r="8" spans="2:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
@@ -2511,238 +2479,229 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
+      <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
     </row>
-    <row r="9" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="44" t="s">
+    <row r="9" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="41" t="s">
+      <c r="I9" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="K9" s="36"/>
-      <c r="L9" s="36"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="28"/>
+      <c r="J9" s="46"/>
+      <c r="K9" s="46"/>
+      <c r="L9" s="46"/>
+      <c r="M9" s="46"/>
+      <c r="N9" s="28"/>
     </row>
-    <row r="10" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="49" t="s">
+    <row r="10" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="50"/>
-      <c r="D10" s="6" t="s">
+      <c r="C10" s="42"/>
+      <c r="D10" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="5" t="s">
         <v>10</v>
       </c>
       <c r="H10" s="2"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="6" t="s">
+      <c r="I10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="J10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="K10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="L10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="N10" s="6" t="s">
+      <c r="M10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="O10" s="6" t="s">
+      <c r="N10" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="31" t="s">
+    <row r="11" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="47" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="28"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="15" t="str">
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="13" t="str">
         <f t="shared" ref="G11:G16" si="0">IF(E11=0,"-",F11/D11)</f>
         <v>-</v>
       </c>
       <c r="H11" s="2"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="20" t="s">
+      <c r="I11" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="15" t="str">
-        <f t="shared" ref="O11:O17" si="1">IF(K11=0,"-",L11/K11)</f>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="13" t="str">
+        <f t="shared" ref="N11:N17" si="1">IF(J11=0,"-",K11/J11)</f>
         <v>-</v>
       </c>
     </row>
-    <row r="12" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="45" t="s">
+    <row r="12" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="30" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="28"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="16" t="str">
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="14" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H12" s="2"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="21" t="s">
+      <c r="I12" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="23"/>
-      <c r="O12" s="16" t="str">
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="14" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
     </row>
-    <row r="13" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="31" t="s">
+    <row r="13" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="47" t="s">
         <v>21</v>
       </c>
       <c r="C13" s="28"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="15" t="str">
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="13" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H13" s="2"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="20" t="s">
+      <c r="I13" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="22"/>
-      <c r="O13" s="15" t="str">
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="13" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
     </row>
-    <row r="14" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="45" t="s">
+    <row r="14" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="30" t="s">
         <v>23</v>
       </c>
       <c r="C14" s="28"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="16" t="str">
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="14" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H14" s="2"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="21" t="s">
+      <c r="I14" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="16" t="str">
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="14" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
     </row>
-    <row r="15" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="31" t="s">
+    <row r="15" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="47" t="s">
         <v>25</v>
       </c>
       <c r="C15" s="28"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="15" t="str">
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="13" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H15" s="2"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="20" t="s">
+      <c r="I15" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="22"/>
-      <c r="O15" s="15" t="str">
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="13" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
     </row>
-    <row r="16" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="62" t="s">
+    <row r="16" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="63"/>
-      <c r="D16" s="9">
+      <c r="C16" s="34"/>
+      <c r="D16" s="8">
         <f>SUM(D11:D15)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="8">
         <f>SUM(E11:E15)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="8">
         <f>SUM(F11:F15)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="17" t="str">
+      <c r="G16" s="15" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
       <c r="H16" s="2"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="21" t="s">
+      <c r="I16" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="23"/>
-      <c r="O16" s="16" t="str">
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="21"/>
+      <c r="N16" s="14" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
     </row>
-    <row r="17" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -2750,32 +2709,31 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="5" t="s">
+      <c r="I17" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K17" s="9">
+      <c r="J17" s="8">
+        <f>SUM(J11:J16)</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="8">
         <f>SUM(K11:K16)</f>
         <v>0</v>
       </c>
-      <c r="L17" s="9">
+      <c r="L17" s="8">
         <f>SUM(L11:L16)</f>
         <v>0</v>
       </c>
-      <c r="M17" s="9">
+      <c r="M17" s="22">
         <f>SUM(M11:M16)</f>
         <v>0</v>
       </c>
-      <c r="N17" s="24">
-        <f>SUM(N11:N16)</f>
-        <v>0</v>
-      </c>
-      <c r="O17" s="17" t="str">
+      <c r="N17" s="15" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
     </row>
-    <row r="18" spans="2:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -2789,154 +2747,147 @@
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
     </row>
-    <row r="19" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
+    <row r="19" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
       <c r="G19" s="28"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="K19" s="36"/>
-      <c r="L19" s="36"/>
-      <c r="M19" s="36"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="28"/>
+      <c r="I19" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="J19" s="46"/>
+      <c r="K19" s="46"/>
+      <c r="L19" s="46"/>
+      <c r="M19" s="46"/>
+      <c r="N19" s="28"/>
     </row>
-    <row r="20" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="40" t="s">
-        <v>31</v>
+    <row r="20" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="38" t="s">
+        <v>33</v>
       </c>
       <c r="C20" s="28"/>
-      <c r="D20" s="40" t="s">
-        <v>12</v>
+      <c r="D20" s="38" t="s">
+        <v>34</v>
       </c>
       <c r="E20" s="28"/>
-      <c r="F20" s="40" t="s">
-        <v>32</v>
+      <c r="F20" s="38" t="s">
+        <v>35</v>
       </c>
       <c r="G20" s="28"/>
       <c r="H20" s="3"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="K20" s="28"/>
-      <c r="L20" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="M20" s="28"/>
-      <c r="N20" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="O20" s="28"/>
+      <c r="I20" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="J20" s="28"/>
+      <c r="K20" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="L20" s="28"/>
+      <c r="M20" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="N20" s="28"/>
     </row>
-    <row r="21" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="31" t="s">
-        <v>13</v>
+    <row r="21" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="47" t="s">
+        <v>36</v>
       </c>
       <c r="C21" s="28"/>
-      <c r="D21" s="38"/>
+      <c r="D21" s="43"/>
       <c r="E21" s="28"/>
-      <c r="F21" s="48" t="str">
-        <f>IF(D24=0,"-",D21/D24)</f>
-        <v>-</v>
-      </c>
+      <c r="F21" s="43"/>
       <c r="G21" s="28"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="K21" s="28"/>
-      <c r="L21" s="38"/>
-      <c r="M21" s="28"/>
-      <c r="N21" s="38"/>
-      <c r="O21" s="28"/>
+      <c r="I21" s="47" t="s">
+        <v>13</v>
+      </c>
+      <c r="J21" s="28"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="44" t="str">
+        <f>IF(K24=0,"-",K21/K24)</f>
+        <v>-</v>
+      </c>
+      <c r="N21" s="28"/>
     </row>
-    <row r="22" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="45" t="s">
-        <v>37</v>
+    <row r="22" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="30" t="s">
+        <v>38</v>
       </c>
       <c r="C22" s="28"/>
-      <c r="D22" s="55"/>
+      <c r="D22" s="27"/>
       <c r="E22" s="28"/>
-      <c r="F22" s="52" t="str">
-        <f>IF(D24=0,"-",D22/D24)</f>
-        <v>-</v>
-      </c>
+      <c r="F22" s="27"/>
       <c r="G22" s="28"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="45" t="s">
-        <v>38</v>
-      </c>
-      <c r="K22" s="28"/>
-      <c r="L22" s="55"/>
-      <c r="M22" s="28"/>
-      <c r="N22" s="55"/>
-      <c r="O22" s="28"/>
+      <c r="I22" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="J22" s="28"/>
+      <c r="K22" s="27"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="56" t="str">
+        <f>IF(K24=0,"-",K22/K24)</f>
+        <v>-</v>
+      </c>
+      <c r="N22" s="28"/>
     </row>
-    <row r="23" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="31" t="s">
-        <v>39</v>
+    <row r="23" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="47" t="s">
+        <v>40</v>
       </c>
       <c r="C23" s="28"/>
-      <c r="D23" s="38"/>
+      <c r="D23" s="43"/>
       <c r="E23" s="28"/>
-      <c r="F23" s="48" t="str">
-        <f>IF(D24=0,"-",D23/D24)</f>
-        <v>-</v>
-      </c>
+      <c r="F23" s="43"/>
       <c r="G23" s="28"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="K23" s="28"/>
-      <c r="L23" s="38"/>
-      <c r="M23" s="28"/>
-      <c r="N23" s="38"/>
-      <c r="O23" s="28"/>
+      <c r="I23" s="47" t="s">
+        <v>39</v>
+      </c>
+      <c r="J23" s="28"/>
+      <c r="K23" s="43"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="44" t="str">
+        <f>IF(K24=0,"-",K23/K24)</f>
+        <v>-</v>
+      </c>
+      <c r="N23" s="28"/>
     </row>
-    <row r="24" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="27" t="s">
+    <row r="24" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="49" t="s">
         <v>27</v>
       </c>
       <c r="C24" s="28"/>
-      <c r="D24" s="34">
+      <c r="D24" s="50">
         <f>SUM(D21:E23)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="28"/>
-      <c r="F24" s="57">
-        <v>1</v>
-      </c>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
       <c r="G24" s="28"/>
       <c r="H24" s="3"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="27" t="s">
+      <c r="I24" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="K24" s="28"/>
-      <c r="L24" s="34">
-        <f>SUM(L21:M23)</f>
+      <c r="J24" s="28"/>
+      <c r="K24" s="50">
+        <f>SUM(K21:L23)</f>
         <v>0</v>
       </c>
-      <c r="M24" s="36"/>
-      <c r="N24" s="36"/>
-      <c r="O24" s="28"/>
+      <c r="L24" s="28"/>
+      <c r="M24" s="48">
+        <v>1</v>
+      </c>
+      <c r="N24" s="28"/>
     </row>
-    <row r="25" spans="2:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -2950,274 +2901,268 @@
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
     </row>
-    <row r="26" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="60" t="s">
+    <row r="26" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="25"/>
+      <c r="B26" s="64" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="65"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="65"/>
+      <c r="F26" s="65"/>
+      <c r="G26" s="65"/>
+      <c r="H26" s="65"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="65"/>
+      <c r="K26" s="65"/>
+      <c r="L26" s="65"/>
+      <c r="M26" s="65"/>
+      <c r="N26" s="65"/>
+    </row>
+    <row r="27" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="25"/>
+      <c r="B27" s="59" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="G27" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="H27" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="I27" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="J27" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="K27" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="26" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="25"/>
+      <c r="B28" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="C26" s="61"/>
-      <c r="D26" s="61"/>
-      <c r="E26" s="61"/>
-      <c r="F26" s="61"/>
-      <c r="G26" s="61"/>
-      <c r="H26" s="61"/>
-      <c r="I26" s="61"/>
-      <c r="J26" s="61"/>
-      <c r="K26" s="61"/>
-      <c r="L26" s="61"/>
-      <c r="M26" s="61"/>
-      <c r="N26" s="61"/>
-      <c r="O26" s="61"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="24"/>
     </row>
-    <row r="27" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="49" t="s">
-        <v>59</v>
-      </c>
-      <c r="C27" s="50"/>
-      <c r="D27" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="I27" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="J27" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="K27" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="L27" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="M27" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="N27" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="O27" s="10" t="s">
-        <v>52</v>
+    <row r="29" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="25"/>
+      <c r="B29" s="61" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="16" t="str">
+        <f>IF(D28=0,"-",D28/C28-1)</f>
+        <v>-</v>
+      </c>
+      <c r="E29" s="16" t="str">
+        <f>IF(E28=0,"-",E28/D28-1)</f>
+        <v>-</v>
+      </c>
+      <c r="F29" s="16" t="str">
+        <f>IF(F28=0,"-",F28/E28-1)</f>
+        <v>-</v>
+      </c>
+      <c r="G29" s="16" t="str">
+        <f>IF(G28=0,"-",G28/F28-1)</f>
+        <v>-</v>
+      </c>
+      <c r="H29" s="16" t="str">
+        <f>IF(H28=0,"-",H28/G28-1)</f>
+        <v>-</v>
+      </c>
+      <c r="I29" s="16" t="str">
+        <f>IF(I28=0,"-",I28/H28-1)</f>
+        <v>-</v>
+      </c>
+      <c r="J29" s="16" t="str">
+        <f t="shared" ref="J29:N29" si="2">IF(J28=0,"-",J28/I28-1)</f>
+        <v>-</v>
+      </c>
+      <c r="K29" s="16" t="str">
+        <f t="shared" si="2"/>
+        <v>-</v>
+      </c>
+      <c r="L29" s="16" t="str">
+        <f t="shared" si="2"/>
+        <v>-</v>
+      </c>
+      <c r="M29" s="16" t="str">
+        <f t="shared" si="2"/>
+        <v>-</v>
+      </c>
+      <c r="N29" s="17" t="str">
+        <f t="shared" si="2"/>
+        <v>-</v>
       </c>
     </row>
-    <row r="28" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="59" t="s">
+    <row r="30" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="25"/>
+      <c r="B30" s="62" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="10"/>
+    </row>
+    <row r="31" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="25"/>
+      <c r="B31" s="63" t="s">
         <v>53</v>
       </c>
-      <c r="C28" s="30"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="25"/>
-      <c r="I28" s="25"/>
-      <c r="J28" s="25"/>
-      <c r="K28" s="25"/>
-      <c r="L28" s="25"/>
-      <c r="M28" s="25"/>
-      <c r="N28" s="25"/>
-      <c r="O28" s="26"/>
-    </row>
-    <row r="29" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="58" t="s">
+      <c r="C31" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C29" s="54"/>
-      <c r="D29" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E29" s="18" t="str">
-        <f>IF(E28=0,"-",E28/D28-1)</f>
-        <v>-</v>
-      </c>
-      <c r="F29" s="18" t="str">
-        <f t="shared" ref="F29" si="2">IF(F28=0,"-",F28/E28-1)</f>
-        <v>-</v>
-      </c>
-      <c r="G29" s="18" t="str">
-        <f t="shared" ref="G29" si="3">IF(G28=0,"-",G28/F28-1)</f>
-        <v>-</v>
-      </c>
-      <c r="H29" s="18" t="str">
-        <f t="shared" ref="H29" si="4">IF(H28=0,"-",H28/G28-1)</f>
-        <v>-</v>
-      </c>
-      <c r="I29" s="18" t="str">
-        <f t="shared" ref="I29" si="5">IF(I28=0,"-",I28/H28-1)</f>
-        <v>-</v>
-      </c>
-      <c r="J29" s="18" t="str">
-        <f t="shared" ref="J29" si="6">IF(J28=0,"-",J28/I28-1)</f>
-        <v>-</v>
-      </c>
-      <c r="K29" s="18" t="str">
-        <f t="shared" ref="K29" si="7">IF(K28=0,"-",K28/J28-1)</f>
-        <v>-</v>
-      </c>
-      <c r="L29" s="18" t="str">
-        <f t="shared" ref="L29" si="8">IF(L28=0,"-",L28/K28-1)</f>
-        <v>-</v>
-      </c>
-      <c r="M29" s="18" t="str">
-        <f t="shared" ref="M29" si="9">IF(M28=0,"-",M28/L28-1)</f>
-        <v>-</v>
-      </c>
-      <c r="N29" s="18" t="str">
-        <f t="shared" ref="N29" si="10">IF(N28=0,"-",N28/M28-1)</f>
-        <v>-</v>
-      </c>
-      <c r="O29" s="19" t="str">
-        <f t="shared" ref="O29" si="11">IF(O28=0,"-",O28/N28-1)</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="30" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="C30" s="30"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="11"/>
-      <c r="O30" s="12"/>
-    </row>
-    <row r="31" spans="2:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="53" t="s">
-        <v>54</v>
-      </c>
-      <c r="C31" s="54"/>
-      <c r="D31" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="E31" s="18" t="str">
+      <c r="D31" s="16" t="str">
+        <f>IF(D30=0,"-",D30/C30-1)</f>
+        <v>-</v>
+      </c>
+      <c r="E31" s="16" t="str">
         <f>IF(E30=0,"-",E30/D30-1)</f>
         <v>-</v>
       </c>
-      <c r="F31" s="18" t="str">
-        <f t="shared" ref="F31:O31" si="12">IF(F30=0,"-",F30/E30-1)</f>
-        <v>-</v>
-      </c>
-      <c r="G31" s="18" t="str">
-        <f t="shared" si="12"/>
-        <v>-</v>
-      </c>
-      <c r="H31" s="18" t="str">
-        <f t="shared" si="12"/>
-        <v>-</v>
-      </c>
-      <c r="I31" s="18" t="str">
-        <f t="shared" si="12"/>
-        <v>-</v>
-      </c>
-      <c r="J31" s="18" t="str">
-        <f t="shared" si="12"/>
-        <v>-</v>
-      </c>
-      <c r="K31" s="18" t="str">
-        <f t="shared" si="12"/>
-        <v>-</v>
-      </c>
-      <c r="L31" s="18" t="str">
-        <f t="shared" si="12"/>
-        <v>-</v>
-      </c>
-      <c r="M31" s="18" t="str">
-        <f t="shared" si="12"/>
-        <v>-</v>
-      </c>
-      <c r="N31" s="18" t="str">
-        <f t="shared" si="12"/>
-        <v>-</v>
-      </c>
-      <c r="O31" s="19" t="str">
-        <f t="shared" si="12"/>
+      <c r="F31" s="16" t="str">
+        <f>IF(F30=0,"-",F30/E30-1)</f>
+        <v>-</v>
+      </c>
+      <c r="G31" s="16" t="str">
+        <f>IF(G30=0,"-",G30/F30-1)</f>
+        <v>-</v>
+      </c>
+      <c r="H31" s="16" t="str">
+        <f>IF(H30=0,"-",H30/G30-1)</f>
+        <v>-</v>
+      </c>
+      <c r="I31" s="16" t="str">
+        <f>IF(I30=0,"-",I30/H30-1)</f>
+        <v>-</v>
+      </c>
+      <c r="J31" s="16" t="str">
+        <f t="shared" ref="J31:N31" si="3">IF(J30=0,"-",J30/I30-1)</f>
+        <v>-</v>
+      </c>
+      <c r="K31" s="16" t="str">
+        <f t="shared" si="3"/>
+        <v>-</v>
+      </c>
+      <c r="L31" s="16" t="str">
+        <f t="shared" si="3"/>
+        <v>-</v>
+      </c>
+      <c r="M31" s="16" t="str">
+        <f t="shared" si="3"/>
+        <v>-</v>
+      </c>
+      <c r="N31" s="17" t="str">
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="62">
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B4:O4"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="N22:O22"/>
-    <mergeCell ref="F7:G7"/>
+  <mergeCells count="57">
+    <mergeCell ref="B26:N26"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="I5:N5"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="K6:L6"/>
     <mergeCell ref="D21:E21"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="L24:O24"/>
-    <mergeCell ref="B2:O2"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="I9:N9"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="B2:N2"/>
     <mergeCell ref="B9:G9"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="I23:J23"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
     <mergeCell ref="B13:C13"/>
-    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="B5:G5"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="M23:N23"/>
     <mergeCell ref="B10:C10"/>
-    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="M22:N22"/>
     <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="I19:N19"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J5:O5"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="J19:O19"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="J9:O9"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="B26:O26"/>
-    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D24:G24"/>
+    <mergeCell ref="B4:N4"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B16:C16"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/my_project/templates/template_B.xlsx
+++ b/my_project/templates/template_B.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="62">
   <si>
     <t>임관리비 / 재고 현황 요약 보고서</t>
   </si>
@@ -623,7 +623,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -699,67 +699,61 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -768,41 +762,53 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="176" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2364,112 +2370,112 @@
   <sheetData>
     <row r="1" spans="2:14" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52"/>
-      <c r="N2" s="52"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
     </row>
     <row r="3" spans="2:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="36"/>
-      <c r="M4" s="36"/>
-      <c r="N4" s="36"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="62"/>
+      <c r="L4" s="62"/>
+      <c r="M4" s="62"/>
+      <c r="N4" s="62"/>
     </row>
     <row r="5" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="52" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="57" t="s">
+      <c r="I5" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="55"/>
-      <c r="N5" s="55"/>
+      <c r="J5" s="38"/>
+      <c r="K5" s="38"/>
+      <c r="L5" s="38"/>
+      <c r="M5" s="38"/>
+      <c r="N5" s="38"/>
     </row>
     <row r="6" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="28"/>
-      <c r="D6" s="32" t="s">
+      <c r="C6" s="35"/>
+      <c r="D6" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="E6" s="28"/>
-      <c r="F6" s="31" t="s">
+      <c r="E6" s="35"/>
+      <c r="F6" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="28"/>
+      <c r="G6" s="35"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="29" t="s">
+      <c r="I6" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="J6" s="28"/>
-      <c r="K6" s="32" t="s">
+      <c r="J6" s="35"/>
+      <c r="K6" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="L6" s="28"/>
-      <c r="M6" s="31" t="s">
+      <c r="L6" s="35"/>
+      <c r="M6" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="N6" s="28"/>
+      <c r="N6" s="35"/>
     </row>
     <row r="7" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="39">
+      <c r="B7" s="56">
         <v>1962</v>
       </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="37">
+      <c r="C7" s="35"/>
+      <c r="D7" s="51">
         <v>1891</v>
       </c>
-      <c r="E7" s="28"/>
-      <c r="F7" s="40">
+      <c r="E7" s="35"/>
+      <c r="F7" s="59">
         <v>71</v>
       </c>
-      <c r="G7" s="28"/>
+      <c r="G7" s="35"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="39">
+      <c r="I7" s="56">
         <v>1962</v>
       </c>
-      <c r="J7" s="28"/>
-      <c r="K7" s="37">
+      <c r="J7" s="35"/>
+      <c r="K7" s="51">
         <v>1865</v>
       </c>
-      <c r="L7" s="28"/>
-      <c r="M7" s="40">
+      <c r="L7" s="35"/>
+      <c r="M7" s="59">
         <v>71</v>
       </c>
-      <c r="N7" s="28"/>
+      <c r="N7" s="35"/>
     </row>
     <row r="8" spans="2:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="3"/>
@@ -2487,29 +2493,29 @@
       <c r="N8" s="3"/>
     </row>
     <row r="9" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="53" t="s">
+      <c r="B9" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46"/>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="58" t="s">
+      <c r="I9" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
-      <c r="L9" s="46"/>
-      <c r="M9" s="46"/>
-      <c r="N9" s="28"/>
+      <c r="J9" s="41"/>
+      <c r="K9" s="41"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="41"/>
+      <c r="N9" s="35"/>
     </row>
     <row r="10" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="42"/>
+      <c r="C10" s="55"/>
       <c r="D10" s="5" t="s">
         <v>2</v>
       </c>
@@ -2543,10 +2549,10 @@
       </c>
     </row>
     <row r="11" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="28"/>
+      <c r="C11" s="35"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
@@ -2568,10 +2574,10 @@
       </c>
     </row>
     <row r="12" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="28"/>
+      <c r="C12" s="35"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -2593,10 +2599,10 @@
       </c>
     </row>
     <row r="13" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="47" t="s">
+      <c r="B13" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="28"/>
+      <c r="C13" s="35"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
@@ -2618,10 +2624,10 @@
       </c>
     </row>
     <row r="14" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="28"/>
+      <c r="C14" s="35"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -2643,10 +2649,10 @@
       </c>
     </row>
     <row r="15" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="47" t="s">
+      <c r="B15" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="28"/>
+      <c r="C15" s="35"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
@@ -2668,10 +2674,10 @@
       </c>
     </row>
     <row r="16" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="34"/>
+      <c r="C16" s="65"/>
       <c r="D16" s="8">
         <f>SUM(D11:D15)</f>
         <v>0</v>
@@ -2749,143 +2755,136 @@
       <c r="N18" s="3"/>
     </row>
     <row r="19" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="45" t="s">
+      <c r="B19" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="28"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="35"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="45" t="s">
+      <c r="I19" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
-      <c r="L19" s="46"/>
-      <c r="M19" s="46"/>
-      <c r="N19" s="28"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="41"/>
+      <c r="L19" s="41"/>
+      <c r="M19" s="41"/>
+      <c r="N19" s="35"/>
     </row>
     <row r="20" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="38" t="s">
+      <c r="B20" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="28"/>
-      <c r="D20" s="38" t="s">
+      <c r="C20" s="35"/>
+      <c r="D20" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="28"/>
-      <c r="F20" s="38" t="s">
+      <c r="E20" s="35"/>
+      <c r="F20" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="G20" s="28"/>
+      <c r="G20" s="35"/>
       <c r="H20" s="3"/>
-      <c r="I20" s="38" t="s">
+      <c r="I20" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="J20" s="28"/>
-      <c r="K20" s="38" t="s">
+      <c r="J20" s="35"/>
+      <c r="K20" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="L20" s="28"/>
-      <c r="M20" s="38" t="s">
+      <c r="L20" s="35"/>
+      <c r="M20" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="N20" s="28"/>
+      <c r="N20" s="35"/>
     </row>
     <row r="21" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="47" t="s">
+      <c r="B21" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="28"/>
+      <c r="C21" s="35"/>
       <c r="D21" s="43"/>
-      <c r="E21" s="28"/>
+      <c r="E21" s="35"/>
       <c r="F21" s="43"/>
-      <c r="G21" s="28"/>
+      <c r="G21" s="35"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="47" t="s">
-        <v>13</v>
-      </c>
-      <c r="J21" s="28"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="28"/>
-      <c r="M21" s="44" t="str">
-        <f>IF(K24=0,"-",K21/K24)</f>
-        <v>-</v>
-      </c>
-      <c r="N21" s="28"/>
+      <c r="I21" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="J21" s="35"/>
+      <c r="K21" s="58"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="57" t="str">
+        <f>IF(K23=0,"-",K21/K23)</f>
+        <v>-</v>
+      </c>
+      <c r="N21" s="35"/>
     </row>
     <row r="22" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="30" t="s">
+      <c r="B22" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="28"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="58"/>
+      <c r="G22" s="35"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="J22" s="28"/>
-      <c r="K22" s="27"/>
-      <c r="L22" s="28"/>
-      <c r="M22" s="56" t="str">
-        <f>IF(K24=0,"-",K22/K24)</f>
-        <v>-</v>
-      </c>
-      <c r="N22" s="28"/>
+      <c r="I22" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="J22" s="35"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="53" t="str">
+        <f>IF(K23=0,"-",K22/K23)</f>
+        <v>-</v>
+      </c>
+      <c r="N22" s="35"/>
     </row>
     <row r="23" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="47" t="s">
+      <c r="B23" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="28"/>
+      <c r="C23" s="35"/>
       <c r="D23" s="43"/>
-      <c r="E23" s="28"/>
+      <c r="E23" s="35"/>
       <c r="F23" s="43"/>
-      <c r="G23" s="28"/>
+      <c r="G23" s="35"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="47" t="s">
-        <v>39</v>
-      </c>
-      <c r="J23" s="28"/>
-      <c r="K23" s="43"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="44" t="str">
-        <f>IF(K24=0,"-",K23/K24)</f>
-        <v>-</v>
-      </c>
-      <c r="N23" s="28"/>
+      <c r="I23" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="J23" s="35"/>
+      <c r="K23" s="39">
+        <f>SUM(K21:L22)</f>
+        <v>0</v>
+      </c>
+      <c r="L23" s="35"/>
+      <c r="M23" s="60" t="str">
+        <f>IF(K23=0,"-",(K21+K22)/K23)</f>
+        <v>-</v>
+      </c>
+      <c r="N23" s="35"/>
     </row>
     <row r="24" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="49" t="s">
+      <c r="B24" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="28"/>
-      <c r="D24" s="50">
+      <c r="C24" s="35"/>
+      <c r="D24" s="66">
         <f>SUM(D21:E23)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="28"/>
+      <c r="E24" s="67"/>
+      <c r="F24" s="66">
+        <f>SUM(F21:G23)</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="67"/>
       <c r="H24" s="3"/>
-      <c r="I24" s="49" t="s">
-        <v>27</v>
-      </c>
-      <c r="J24" s="28"/>
-      <c r="K24" s="50">
-        <f>SUM(K21:L23)</f>
-        <v>0</v>
-      </c>
-      <c r="L24" s="28"/>
-      <c r="M24" s="48">
-        <v>1</v>
-      </c>
-      <c r="N24" s="28"/>
     </row>
     <row r="25" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="3"/>
@@ -2904,25 +2903,25 @@
     </row>
     <row r="26" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="25"/>
-      <c r="B26" s="64" t="s">
+      <c r="B26" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="65"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="65"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="65"/>
-      <c r="H26" s="65"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="65"/>
-      <c r="K26" s="65"/>
-      <c r="L26" s="65"/>
-      <c r="M26" s="65"/>
-      <c r="N26" s="65"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
+      <c r="N26" s="33"/>
     </row>
     <row r="27" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="25"/>
-      <c r="B27" s="59" t="s">
+      <c r="B27" s="27" t="s">
         <v>59</v>
       </c>
       <c r="C27" s="26" t="s">
@@ -2964,7 +2963,7 @@
     </row>
     <row r="28" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="25"/>
-      <c r="B28" s="60" t="s">
+      <c r="B28" s="28" t="s">
         <v>60</v>
       </c>
       <c r="C28" s="23"/>
@@ -2982,60 +2981,60 @@
     </row>
     <row r="29" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="25"/>
-      <c r="B29" s="61" t="s">
+      <c r="B29" s="29" t="s">
         <v>53</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>54</v>
       </c>
       <c r="D29" s="16" t="str">
-        <f>IF(D28=0,"-",D28/C28-1)</f>
+        <f t="shared" ref="D29:I29" si="2">IF(D28=0,"-",D28/C28-1)</f>
         <v>-</v>
       </c>
       <c r="E29" s="16" t="str">
-        <f>IF(E28=0,"-",E28/D28-1)</f>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="F29" s="16" t="str">
-        <f>IF(F28=0,"-",F28/E28-1)</f>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="G29" s="16" t="str">
-        <f>IF(G28=0,"-",G28/F28-1)</f>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="H29" s="16" t="str">
-        <f>IF(H28=0,"-",H28/G28-1)</f>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="I29" s="16" t="str">
-        <f>IF(I28=0,"-",I28/H28-1)</f>
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
       <c r="J29" s="16" t="str">
-        <f t="shared" ref="J29:N29" si="2">IF(J28=0,"-",J28/I28-1)</f>
+        <f t="shared" ref="J29:N29" si="3">IF(J28=0,"-",J28/I28-1)</f>
         <v>-</v>
       </c>
       <c r="K29" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="L29" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="M29" s="16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
       <c r="N29" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="25"/>
-      <c r="B30" s="62" t="s">
+      <c r="B30" s="30" t="s">
         <v>61</v>
       </c>
       <c r="C30" s="9"/>
@@ -3053,78 +3052,86 @@
     </row>
     <row r="31" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="25"/>
-      <c r="B31" s="63" t="s">
+      <c r="B31" s="31" t="s">
         <v>53</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>54</v>
       </c>
       <c r="D31" s="16" t="str">
-        <f>IF(D30=0,"-",D30/C30-1)</f>
+        <f t="shared" ref="D31:I31" si="4">IF(D30=0,"-",D30/C30-1)</f>
         <v>-</v>
       </c>
       <c r="E31" s="16" t="str">
-        <f>IF(E30=0,"-",E30/D30-1)</f>
+        <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="F31" s="16" t="str">
-        <f>IF(F30=0,"-",F30/E30-1)</f>
+        <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="G31" s="16" t="str">
-        <f>IF(G30=0,"-",G30/F30-1)</f>
+        <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="H31" s="16" t="str">
-        <f>IF(H30=0,"-",H30/G30-1)</f>
+        <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="I31" s="16" t="str">
-        <f>IF(I30=0,"-",I30/H30-1)</f>
+        <f t="shared" si="4"/>
         <v>-</v>
       </c>
       <c r="J31" s="16" t="str">
-        <f t="shared" ref="J31:N31" si="3">IF(J30=0,"-",J30/I30-1)</f>
+        <f t="shared" ref="J31:N31" si="5">IF(J30=0,"-",J30/I30-1)</f>
         <v>-</v>
       </c>
       <c r="K31" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="L31" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="M31" s="16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
       <c r="N31" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>-</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="57">
-    <mergeCell ref="B26:N26"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="I5:N5"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="I9:N9"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="K20:L20"/>
+  <mergeCells count="55">
+    <mergeCell ref="B4:N4"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="I19:N19"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B9:G9"/>
     <mergeCell ref="M20:N20"/>
-    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I22:J22"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="F23:G23"/>
@@ -3133,36 +3140,26 @@
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="B5:G5"/>
     <mergeCell ref="D20:E20"/>
-    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="M22:N22"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="I7:J7"/>
-    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="B26:N26"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="I5:N5"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="I9:N9"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="K20:L20"/>
     <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="I19:N19"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:G24"/>
-    <mergeCell ref="B4:N4"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B16:C16"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/my_project/templates/template_B.xlsx
+++ b/my_project/templates/template_B.xlsx
@@ -42,9 +42,6 @@
     <t>▎ 지역별 가맹점 현황</t>
   </si>
   <si>
-    <t>▎ 임대자산 현황</t>
-  </si>
-  <si>
     <t>지역</t>
   </si>
   <si>
@@ -106,12 +103,6 @@
   </si>
   <si>
     <t>중고출고(A-3)</t>
-  </si>
-  <si>
-    <t>▎ 자산 보관 현황</t>
-  </si>
-  <si>
-    <t>▎ 자산별 현황</t>
   </si>
   <si>
     <t>보관위치</t>
@@ -211,6 +202,18 @@
   <si>
     <t>임대자산
 출고수량</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>▎ 자산 보관 위치 현황</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>▎ 임대자산별 현황</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>▎ 임대형태 및 임대자산별 현황</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -699,9 +702,6 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
@@ -714,47 +714,67 @@
     <xf numFmtId="0" fontId="9" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -762,15 +782,12 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="176" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -778,37 +795,23 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1089,45 +1092,45 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>요약보고서!$C$27:$O$27</c15:sqref>
+                    <c15:sqref>요약보고서!$C$27:$N$27</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>요약보고서!$D$27:$O$27</c:f>
+              <c:f>요약보고서!$D$27:$N$27</c:f>
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>'25.02</c:v>
+                  <c:v>'25.04</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>'25.03</c:v>
+                  <c:v>'25.05</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>'25.04</c:v>
+                  <c:v>'25.06</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>'25.05</c:v>
+                  <c:v>'25.07</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>'25.06</c:v>
+                  <c:v>'25.08</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>'25.07</c:v>
+                  <c:v>'25.09</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>'25.08</c:v>
+                  <c:v>'25.10</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>'25.09</c:v>
+                  <c:v>'25.11</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>'25.10</c:v>
+                  <c:v>'25.12</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>'25.11</c:v>
+                  <c:v>'25.01</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>'25.12</c:v>
+                  <c:v>'25.02</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1261,45 +1264,45 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>요약보고서!$C$27:$O$27</c15:sqref>
+                    <c15:sqref>요약보고서!$C$27:$N$27</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>요약보고서!$D$27:$O$27</c:f>
+              <c:f>요약보고서!$D$27:$N$27</c:f>
               <c:strCache>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>'25.02</c:v>
+                  <c:v>'25.04</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>'25.03</c:v>
+                  <c:v>'25.05</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>'25.04</c:v>
+                  <c:v>'25.06</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>'25.05</c:v>
+                  <c:v>'25.07</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>'25.06</c:v>
+                  <c:v>'25.08</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>'25.07</c:v>
+                  <c:v>'25.09</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>'25.08</c:v>
+                  <c:v>'25.10</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>'25.09</c:v>
+                  <c:v>'25.11</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>'25.10</c:v>
+                  <c:v>'25.12</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>'25.11</c:v>
+                  <c:v>'25.01</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>'25.12</c:v>
+                  <c:v>'25.02</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2370,109 +2373,109 @@
   <sheetData>
     <row r="1" spans="2:14" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="48"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
     </row>
     <row r="3" spans="2:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
-      <c r="L4" s="62"/>
-      <c r="M4" s="62"/>
-      <c r="N4" s="62"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="33"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="33"/>
     </row>
     <row r="5" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="52" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
+      <c r="B5" s="57" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="J5" s="38"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="38"/>
+      <c r="I5" s="65" t="s">
+        <v>54</v>
+      </c>
+      <c r="J5" s="58"/>
+      <c r="K5" s="58"/>
+      <c r="L5" s="58"/>
+      <c r="M5" s="58"/>
+      <c r="N5" s="58"/>
     </row>
     <row r="6" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="63" t="s">
+      <c r="B6" s="39" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="35"/>
-      <c r="D6" s="42" t="s">
-        <v>55</v>
+      <c r="D6" s="41" t="s">
+        <v>52</v>
       </c>
       <c r="E6" s="35"/>
-      <c r="F6" s="44" t="s">
+      <c r="F6" s="40" t="s">
         <v>3</v>
       </c>
       <c r="G6" s="35"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="63" t="s">
+      <c r="I6" s="39" t="s">
         <v>2</v>
       </c>
       <c r="J6" s="35"/>
-      <c r="K6" s="42" t="s">
+      <c r="K6" s="41" t="s">
         <v>4</v>
       </c>
       <c r="L6" s="35"/>
-      <c r="M6" s="44" t="s">
+      <c r="M6" s="40" t="s">
         <v>5</v>
       </c>
       <c r="N6" s="35"/>
     </row>
     <row r="7" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="56">
+      <c r="B7" s="37">
         <v>1962</v>
       </c>
       <c r="C7" s="35"/>
-      <c r="D7" s="51">
+      <c r="D7" s="34">
         <v>1891</v>
       </c>
       <c r="E7" s="35"/>
-      <c r="F7" s="59">
+      <c r="F7" s="38">
         <v>71</v>
       </c>
       <c r="G7" s="35"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="56">
+      <c r="I7" s="37">
         <v>1962</v>
       </c>
       <c r="J7" s="35"/>
-      <c r="K7" s="51">
+      <c r="K7" s="34">
         <v>1865</v>
       </c>
       <c r="L7" s="35"/>
-      <c r="M7" s="59">
+      <c r="M7" s="38">
         <v>71</v>
       </c>
       <c r="N7" s="35"/>
@@ -2493,64 +2496,64 @@
       <c r="N8" s="3"/>
     </row>
     <row r="9" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="49" t="s">
+      <c r="B9" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="J9" s="41"/>
-      <c r="K9" s="41"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="41"/>
+      <c r="I9" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9" s="53"/>
+      <c r="K9" s="53"/>
+      <c r="L9" s="53"/>
+      <c r="M9" s="53"/>
       <c r="N9" s="35"/>
     </row>
     <row r="10" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="55"/>
+      <c r="B10" s="60" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="61"/>
       <c r="D10" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>3</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="K10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="L10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="L10" s="5" t="s">
+      <c r="M10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="M10" s="5" t="s">
+      <c r="N10" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="11" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="36" t="s">
-        <v>17</v>
+      <c r="B11" s="46" t="s">
+        <v>16</v>
       </c>
       <c r="C11" s="35"/>
       <c r="D11" s="6"/>
@@ -2562,7 +2565,7 @@
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
@@ -2574,8 +2577,8 @@
       </c>
     </row>
     <row r="12" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="50" t="s">
-        <v>19</v>
+      <c r="B12" s="49" t="s">
+        <v>18</v>
       </c>
       <c r="C12" s="35"/>
       <c r="D12" s="7"/>
@@ -2587,7 +2590,7 @@
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
@@ -2599,8 +2602,8 @@
       </c>
     </row>
     <row r="13" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="36" t="s">
-        <v>21</v>
+      <c r="B13" s="46" t="s">
+        <v>20</v>
       </c>
       <c r="C13" s="35"/>
       <c r="D13" s="6"/>
@@ -2612,7 +2615,7 @@
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
@@ -2624,8 +2627,8 @@
       </c>
     </row>
     <row r="14" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="50" t="s">
-        <v>23</v>
+      <c r="B14" s="49" t="s">
+        <v>22</v>
       </c>
       <c r="C14" s="35"/>
       <c r="D14" s="7"/>
@@ -2637,7 +2640,7 @@
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -2649,8 +2652,8 @@
       </c>
     </row>
     <row r="15" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="36" t="s">
-        <v>25</v>
+      <c r="B15" s="46" t="s">
+        <v>24</v>
       </c>
       <c r="C15" s="35"/>
       <c r="D15" s="6"/>
@@ -2662,7 +2665,7 @@
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
@@ -2674,10 +2677,10 @@
       </c>
     </row>
     <row r="16" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="64" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="65"/>
+      <c r="B16" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="43"/>
       <c r="D16" s="8">
         <f>SUM(D11:D15)</f>
         <v>0</v>
@@ -2696,7 +2699,7 @@
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
@@ -2716,7 +2719,7 @@
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J17" s="8">
         <f>SUM(J11:J16)</f>
@@ -2755,135 +2758,135 @@
       <c r="N18" s="3"/>
     </row>
     <row r="19" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
+      <c r="B19" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
       <c r="G19" s="35"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="40" t="s">
-        <v>29</v>
-      </c>
-      <c r="J19" s="41"/>
-      <c r="K19" s="41"/>
-      <c r="L19" s="41"/>
-      <c r="M19" s="41"/>
+      <c r="I19" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J19" s="53"/>
+      <c r="K19" s="53"/>
+      <c r="L19" s="53"/>
+      <c r="M19" s="53"/>
       <c r="N19" s="35"/>
     </row>
     <row r="20" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="45" t="s">
-        <v>33</v>
+      <c r="B20" s="36" t="s">
+        <v>30</v>
       </c>
       <c r="C20" s="35"/>
-      <c r="D20" s="45" t="s">
-        <v>34</v>
+      <c r="D20" s="36" t="s">
+        <v>31</v>
       </c>
       <c r="E20" s="35"/>
-      <c r="F20" s="45" t="s">
-        <v>35</v>
+      <c r="F20" s="36" t="s">
+        <v>32</v>
       </c>
       <c r="G20" s="35"/>
       <c r="H20" s="3"/>
-      <c r="I20" s="45" t="s">
-        <v>31</v>
+      <c r="I20" s="36" t="s">
+        <v>28</v>
       </c>
       <c r="J20" s="35"/>
-      <c r="K20" s="45" t="s">
-        <v>12</v>
+      <c r="K20" s="36" t="s">
+        <v>11</v>
       </c>
       <c r="L20" s="35"/>
-      <c r="M20" s="45" t="s">
-        <v>32</v>
+      <c r="M20" s="36" t="s">
+        <v>29</v>
       </c>
       <c r="N20" s="35"/>
     </row>
     <row r="21" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="36" t="s">
-        <v>36</v>
+      <c r="B21" s="46" t="s">
+        <v>33</v>
       </c>
       <c r="C21" s="35"/>
-      <c r="D21" s="43"/>
+      <c r="D21" s="45"/>
       <c r="E21" s="35"/>
-      <c r="F21" s="43"/>
+      <c r="F21" s="45"/>
       <c r="G21" s="35"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="50" t="s">
-        <v>37</v>
+      <c r="I21" s="49" t="s">
+        <v>34</v>
       </c>
       <c r="J21" s="35"/>
-      <c r="K21" s="58"/>
+      <c r="K21" s="48"/>
       <c r="L21" s="35"/>
-      <c r="M21" s="57" t="str">
+      <c r="M21" s="62" t="str">
         <f>IF(K23=0,"-",K21/K23)</f>
         <v>-</v>
       </c>
       <c r="N21" s="35"/>
     </row>
     <row r="22" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="50" t="s">
-        <v>38</v>
+      <c r="B22" s="49" t="s">
+        <v>35</v>
       </c>
       <c r="C22" s="35"/>
-      <c r="D22" s="58"/>
+      <c r="D22" s="48"/>
       <c r="E22" s="35"/>
-      <c r="F22" s="58"/>
+      <c r="F22" s="48"/>
       <c r="G22" s="35"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="36" t="s">
-        <v>39</v>
+      <c r="I22" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="J22" s="35"/>
-      <c r="K22" s="43"/>
+      <c r="K22" s="45"/>
       <c r="L22" s="35"/>
-      <c r="M22" s="53" t="str">
+      <c r="M22" s="59" t="str">
         <f>IF(K23=0,"-",K22/K23)</f>
         <v>-</v>
       </c>
       <c r="N22" s="35"/>
     </row>
     <row r="23" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="36" t="s">
-        <v>40</v>
+      <c r="B23" s="46" t="s">
+        <v>37</v>
       </c>
       <c r="C23" s="35"/>
-      <c r="D23" s="43"/>
+      <c r="D23" s="45"/>
       <c r="E23" s="35"/>
-      <c r="F23" s="43"/>
+      <c r="F23" s="45"/>
       <c r="G23" s="35"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="34" t="s">
-        <v>27</v>
+      <c r="I23" s="47" t="s">
+        <v>26</v>
       </c>
       <c r="J23" s="35"/>
-      <c r="K23" s="39">
+      <c r="K23" s="66">
         <f>SUM(K21:L22)</f>
         <v>0</v>
       </c>
       <c r="L23" s="35"/>
-      <c r="M23" s="60" t="str">
+      <c r="M23" s="44" t="str">
         <f>IF(K23=0,"-",(K21+K22)/K23)</f>
         <v>-</v>
       </c>
       <c r="N23" s="35"/>
     </row>
     <row r="24" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="34" t="s">
-        <v>27</v>
+      <c r="B24" s="47" t="s">
+        <v>26</v>
       </c>
       <c r="C24" s="35"/>
-      <c r="D24" s="66">
+      <c r="D24" s="50">
         <f>SUM(D21:E23)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="67"/>
-      <c r="F24" s="66">
+      <c r="E24" s="51"/>
+      <c r="F24" s="50">
         <f>SUM(F21:G23)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="67"/>
+      <c r="G24" s="51"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2903,68 +2906,68 @@
     </row>
     <row r="26" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="25"/>
-      <c r="B26" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="33"/>
-      <c r="M26" s="33"/>
-      <c r="N26" s="33"/>
+      <c r="B26" s="63" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="64"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="64"/>
+      <c r="F26" s="64"/>
+      <c r="G26" s="64"/>
+      <c r="H26" s="64"/>
+      <c r="I26" s="64"/>
+      <c r="J26" s="64"/>
+      <c r="K26" s="64"/>
+      <c r="L26" s="64"/>
+      <c r="M26" s="64"/>
+      <c r="N26" s="64"/>
     </row>
     <row r="27" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="25"/>
-      <c r="B27" s="27" t="s">
-        <v>59</v>
+      <c r="B27" s="31" t="s">
+        <v>56</v>
       </c>
       <c r="C27" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="26" t="s">
+      <c r="E27" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="E27" s="26" t="s">
+      <c r="F27" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="F27" s="26" t="s">
+      <c r="G27" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="G27" s="26" t="s">
+      <c r="H27" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="H27" s="26" t="s">
+      <c r="I27" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="I27" s="26" t="s">
+      <c r="J27" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="J27" s="26" t="s">
+      <c r="K27" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="K27" s="26" t="s">
+      <c r="L27" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="L27" s="26" t="s">
-        <v>50</v>
-      </c>
       <c r="M27" s="26" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="N27" s="26" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="25"/>
-      <c r="B28" s="28" t="s">
-        <v>60</v>
+      <c r="B28" s="27" t="s">
+        <v>57</v>
       </c>
       <c r="C28" s="23"/>
       <c r="D28" s="23"/>
@@ -2981,11 +2984,11 @@
     </row>
     <row r="29" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="25"/>
-      <c r="B29" s="29" t="s">
-        <v>53</v>
+      <c r="B29" s="28" t="s">
+        <v>50</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D29" s="16" t="str">
         <f t="shared" ref="D29:I29" si="2">IF(D28=0,"-",D28/C28-1)</f>
@@ -3034,8 +3037,8 @@
     </row>
     <row r="30" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="25"/>
-      <c r="B30" s="30" t="s">
-        <v>61</v>
+      <c r="B30" s="29" t="s">
+        <v>58</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
@@ -3052,11 +3055,11 @@
     </row>
     <row r="31" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="25"/>
-      <c r="B31" s="31" t="s">
-        <v>53</v>
+      <c r="B31" s="30" t="s">
+        <v>50</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D31" s="16" t="str">
         <f t="shared" ref="D31:I31" si="4">IF(D30=0,"-",D30/C30-1)</f>
@@ -3105,45 +3108,6 @@
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="B4:N4"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="I19:N19"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="M21:N21"/>
     <mergeCell ref="B26:N26"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="B21:C21"/>
@@ -3160,6 +3124,45 @@
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="K20:L20"/>
     <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="I19:N19"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="B4:N4"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="F7:G7"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/my_project/templates/template_B.xlsx
+++ b/my_project/templates/template_B.xlsx
@@ -135,12 +135,6 @@
     <t>A-3</t>
   </si>
   <si>
-    <t>'25.01</t>
-  </si>
-  <si>
-    <t>'25.02</t>
-  </si>
-  <si>
     <t>'25.03</t>
   </si>
   <si>
@@ -214,6 +208,14 @@
   </si>
   <si>
     <t>▎ 임대형태 및 임대자산별 현황</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.02</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -626,7 +628,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -718,63 +720,49 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -782,12 +770,15 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="176" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -795,23 +786,37 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="176" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1127,10 +1132,10 @@
                   <c:v>'25.12</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>'25.01</c:v>
+                  <c:v>26.01</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>'25.02</c:v>
+                  <c:v>26.02</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1299,10 +1304,10 @@
                   <c:v>'25.12</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>'25.01</c:v>
+                  <c:v>26.01</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>'25.02</c:v>
+                  <c:v>26.02</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2373,109 +2378,109 @@
   <sheetData>
     <row r="1" spans="2:14" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="49"/>
     </row>
     <row r="3" spans="2:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="63"/>
+      <c r="K4" s="63"/>
+      <c r="L4" s="63"/>
+      <c r="M4" s="63"/>
+      <c r="N4" s="63"/>
     </row>
     <row r="5" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="57" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
+      <c r="B5" s="53" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="65" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" s="58"/>
-      <c r="K5" s="58"/>
-      <c r="L5" s="58"/>
-      <c r="M5" s="58"/>
-      <c r="N5" s="58"/>
+      <c r="I5" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" s="38"/>
+      <c r="K5" s="38"/>
+      <c r="L5" s="38"/>
+      <c r="M5" s="38"/>
+      <c r="N5" s="38"/>
     </row>
     <row r="6" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="65" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="35"/>
-      <c r="D6" s="41" t="s">
-        <v>52</v>
+      <c r="D6" s="42" t="s">
+        <v>50</v>
       </c>
       <c r="E6" s="35"/>
-      <c r="F6" s="40" t="s">
+      <c r="F6" s="44" t="s">
         <v>3</v>
       </c>
       <c r="G6" s="35"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="39" t="s">
+      <c r="I6" s="65" t="s">
         <v>2</v>
       </c>
       <c r="J6" s="35"/>
-      <c r="K6" s="41" t="s">
+      <c r="K6" s="42" t="s">
         <v>4</v>
       </c>
       <c r="L6" s="35"/>
-      <c r="M6" s="40" t="s">
+      <c r="M6" s="44" t="s">
         <v>5</v>
       </c>
       <c r="N6" s="35"/>
     </row>
     <row r="7" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="37">
+      <c r="B7" s="57">
         <v>1962</v>
       </c>
       <c r="C7" s="35"/>
-      <c r="D7" s="34">
+      <c r="D7" s="52">
         <v>1891</v>
       </c>
       <c r="E7" s="35"/>
-      <c r="F7" s="38">
+      <c r="F7" s="64">
         <v>71</v>
       </c>
       <c r="G7" s="35"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="37">
+      <c r="I7" s="57">
         <v>1962</v>
       </c>
       <c r="J7" s="35"/>
-      <c r="K7" s="34">
+      <c r="K7" s="52">
         <v>1865</v>
       </c>
       <c r="L7" s="35"/>
-      <c r="M7" s="38">
+      <c r="M7" s="64">
         <v>71</v>
       </c>
       <c r="N7" s="35"/>
@@ -2496,29 +2501,29 @@
       <c r="N8" s="3"/>
     </row>
     <row r="9" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="56" t="s">
+      <c r="B9" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="53"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="67" t="s">
-        <v>61</v>
-      </c>
-      <c r="J9" s="53"/>
-      <c r="K9" s="53"/>
-      <c r="L9" s="53"/>
-      <c r="M9" s="53"/>
+      <c r="I9" s="46" t="s">
+        <v>59</v>
+      </c>
+      <c r="J9" s="41"/>
+      <c r="K9" s="41"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="41"/>
       <c r="N9" s="35"/>
     </row>
     <row r="10" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="60" t="s">
+      <c r="B10" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="61"/>
+      <c r="C10" s="56"/>
       <c r="D10" s="5" t="s">
         <v>2</v>
       </c>
@@ -2552,7 +2557,7 @@
       </c>
     </row>
     <row r="11" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="46" t="s">
+      <c r="B11" s="36" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="35"/>
@@ -2577,7 +2582,7 @@
       </c>
     </row>
     <row r="12" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="49" t="s">
+      <c r="B12" s="51" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="35"/>
@@ -2602,7 +2607,7 @@
       </c>
     </row>
     <row r="13" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="46" t="s">
+      <c r="B13" s="36" t="s">
         <v>20</v>
       </c>
       <c r="C13" s="35"/>
@@ -2627,7 +2632,7 @@
       </c>
     </row>
     <row r="14" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="49" t="s">
+      <c r="B14" s="51" t="s">
         <v>22</v>
       </c>
       <c r="C14" s="35"/>
@@ -2652,7 +2657,7 @@
       </c>
     </row>
     <row r="15" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="46" t="s">
+      <c r="B15" s="36" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="35"/>
@@ -2677,10 +2682,10 @@
       </c>
     </row>
     <row r="16" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="42" t="s">
+      <c r="B16" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="43"/>
+      <c r="C16" s="67"/>
       <c r="D16" s="8">
         <f>SUM(D11:D15)</f>
         <v>0</v>
@@ -2758,135 +2763,135 @@
       <c r="N18" s="3"/>
     </row>
     <row r="19" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="52" t="s">
-        <v>60</v>
-      </c>
-      <c r="C19" s="53"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="53"/>
-      <c r="F19" s="53"/>
+      <c r="B19" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
       <c r="G19" s="35"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="52" t="s">
-        <v>59</v>
-      </c>
-      <c r="J19" s="53"/>
-      <c r="K19" s="53"/>
-      <c r="L19" s="53"/>
-      <c r="M19" s="53"/>
+      <c r="I19" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="J19" s="41"/>
+      <c r="K19" s="41"/>
+      <c r="L19" s="41"/>
+      <c r="M19" s="41"/>
       <c r="N19" s="35"/>
     </row>
     <row r="20" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="36" t="s">
+      <c r="B20" s="45" t="s">
         <v>30</v>
       </c>
       <c r="C20" s="35"/>
-      <c r="D20" s="36" t="s">
+      <c r="D20" s="45" t="s">
         <v>31</v>
       </c>
       <c r="E20" s="35"/>
-      <c r="F20" s="36" t="s">
+      <c r="F20" s="45" t="s">
         <v>32</v>
       </c>
       <c r="G20" s="35"/>
       <c r="H20" s="3"/>
-      <c r="I20" s="36" t="s">
+      <c r="I20" s="45" t="s">
         <v>28</v>
       </c>
       <c r="J20" s="35"/>
-      <c r="K20" s="36" t="s">
+      <c r="K20" s="45" t="s">
         <v>11</v>
       </c>
       <c r="L20" s="35"/>
-      <c r="M20" s="36" t="s">
+      <c r="M20" s="45" t="s">
         <v>29</v>
       </c>
       <c r="N20" s="35"/>
     </row>
     <row r="21" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="46" t="s">
+      <c r="B21" s="36" t="s">
         <v>33</v>
       </c>
       <c r="C21" s="35"/>
-      <c r="D21" s="45"/>
+      <c r="D21" s="43"/>
       <c r="E21" s="35"/>
-      <c r="F21" s="45"/>
+      <c r="F21" s="43"/>
       <c r="G21" s="35"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="49" t="s">
+      <c r="I21" s="51" t="s">
         <v>34</v>
       </c>
       <c r="J21" s="35"/>
-      <c r="K21" s="48"/>
+      <c r="K21" s="47"/>
       <c r="L21" s="35"/>
-      <c r="M21" s="62" t="str">
+      <c r="M21" s="58" t="str">
         <f>IF(K23=0,"-",K21/K23)</f>
         <v>-</v>
       </c>
       <c r="N21" s="35"/>
     </row>
     <row r="22" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="49" t="s">
+      <c r="B22" s="51" t="s">
         <v>35</v>
       </c>
       <c r="C22" s="35"/>
-      <c r="D22" s="48"/>
+      <c r="D22" s="47"/>
       <c r="E22" s="35"/>
-      <c r="F22" s="48"/>
+      <c r="F22" s="47"/>
       <c r="G22" s="35"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="46" t="s">
+      <c r="I22" s="36" t="s">
         <v>36</v>
       </c>
       <c r="J22" s="35"/>
-      <c r="K22" s="45"/>
+      <c r="K22" s="43"/>
       <c r="L22" s="35"/>
-      <c r="M22" s="59" t="str">
+      <c r="M22" s="54" t="str">
         <f>IF(K23=0,"-",K22/K23)</f>
         <v>-</v>
       </c>
       <c r="N22" s="35"/>
     </row>
     <row r="23" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="46" t="s">
+      <c r="B23" s="36" t="s">
         <v>37</v>
       </c>
       <c r="C23" s="35"/>
-      <c r="D23" s="45"/>
+      <c r="D23" s="43"/>
       <c r="E23" s="35"/>
-      <c r="F23" s="45"/>
+      <c r="F23" s="43"/>
       <c r="G23" s="35"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="47" t="s">
+      <c r="I23" s="34" t="s">
         <v>26</v>
       </c>
       <c r="J23" s="35"/>
-      <c r="K23" s="66">
+      <c r="K23" s="39">
         <f>SUM(K21:L22)</f>
         <v>0</v>
       </c>
       <c r="L23" s="35"/>
-      <c r="M23" s="44" t="str">
+      <c r="M23" s="59" t="str">
         <f>IF(K23=0,"-",(K21+K22)/K23)</f>
         <v>-</v>
       </c>
       <c r="N23" s="35"/>
     </row>
     <row r="24" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="47" t="s">
+      <c r="B24" s="34" t="s">
         <v>26</v>
       </c>
       <c r="C24" s="35"/>
-      <c r="D24" s="50">
+      <c r="D24" s="60">
         <f>SUM(D21:E23)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="51"/>
-      <c r="F24" s="50">
+      <c r="E24" s="61"/>
+      <c r="F24" s="60">
         <f>SUM(F21:G23)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="51"/>
+      <c r="G24" s="61"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2906,68 +2911,68 @@
     </row>
     <row r="26" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="25"/>
-      <c r="B26" s="63" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" s="64"/>
-      <c r="D26" s="64"/>
-      <c r="E26" s="64"/>
-      <c r="F26" s="64"/>
-      <c r="G26" s="64"/>
-      <c r="H26" s="64"/>
-      <c r="I26" s="64"/>
-      <c r="J26" s="64"/>
-      <c r="K26" s="64"/>
-      <c r="L26" s="64"/>
-      <c r="M26" s="64"/>
-      <c r="N26" s="64"/>
+      <c r="B26" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="33"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
+      <c r="N26" s="33"/>
     </row>
     <row r="27" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="25"/>
       <c r="B27" s="31" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C27" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="26" t="s">
+      <c r="F27" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="E27" s="26" t="s">
+      <c r="G27" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="F27" s="26" t="s">
+      <c r="H27" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="G27" s="26" t="s">
+      <c r="I27" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="H27" s="26" t="s">
+      <c r="J27" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="I27" s="26" t="s">
+      <c r="K27" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="J27" s="26" t="s">
+      <c r="L27" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="K27" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="L27" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="M27" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="N27" s="26" t="s">
-        <v>39</v>
+      <c r="M27" s="68" t="s">
+        <v>60</v>
+      </c>
+      <c r="N27" s="68" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="25"/>
       <c r="B28" s="27" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C28" s="23"/>
       <c r="D28" s="23"/>
@@ -2985,10 +2990,10 @@
     <row r="29" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="25"/>
       <c r="B29" s="28" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D29" s="16" t="str">
         <f t="shared" ref="D29:I29" si="2">IF(D28=0,"-",D28/C28-1)</f>
@@ -3038,7 +3043,7 @@
     <row r="30" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="25"/>
       <c r="B30" s="29" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
@@ -3056,10 +3061,10 @@
     <row r="31" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="25"/>
       <c r="B31" s="30" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D31" s="16" t="str">
         <f t="shared" ref="D31:I31" si="4">IF(D30=0,"-",D30/C30-1)</f>
@@ -3108,6 +3113,45 @@
     </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="I19:N19"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="B4:N4"/>
+    <mergeCell ref="K7:L7"/>
     <mergeCell ref="B26:N26"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="B21:C21"/>
@@ -3124,45 +3168,6 @@
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="K20:L20"/>
     <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="I19:N19"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="B4:N4"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="F7:G7"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/my_project/templates/template_B.xlsx
+++ b/my_project/templates/template_B.xlsx
@@ -719,50 +719,60 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -770,15 +780,15 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="176" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -786,37 +796,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1101,40 +1101,43 @@
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>요약보고서!$D$27:$N$27</c:f>
+              <c:f>요약보고서!$C$27:$N$27</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
+                  <c:v>'25.03</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>'25.04</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>'25.05</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>'25.06</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>'25.07</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>'25.08</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>'25.09</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>'25.10</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>'25.11</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>'25.12</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>26.01</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>26.02</c:v>
                 </c:pt>
               </c:strCache>
@@ -1149,7 +1152,7 @@
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>요약보고서!$D$28:$O$28</c:f>
+              <c:f>요약보고서!$C$28:$N$28</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="12"/>
@@ -1273,40 +1276,43 @@
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>요약보고서!$D$27:$N$27</c:f>
+              <c:f>요약보고서!$C$27:$N$27</c:f>
               <c:strCache>
-                <c:ptCount val="11"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
+                  <c:v>'25.03</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>'25.04</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>'25.05</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>'25.06</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>'25.07</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>'25.08</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>'25.09</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>'25.10</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>'25.11</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>'25.12</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>26.01</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>26.02</c:v>
                 </c:pt>
               </c:strCache>
@@ -1321,7 +1327,7 @@
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>요약보고서!$D$30:$O$30</c:f>
+              <c:f>요약보고서!$C$30:$N$30</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="12"/>
@@ -2378,21 +2384,21 @@
   <sheetData>
     <row r="1" spans="2:14" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="49"/>
-      <c r="N2" s="49"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
     </row>
     <row r="3" spans="2:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -2413,77 +2419,77 @@
       <c r="N4" s="63"/>
     </row>
     <row r="5" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="37" t="s">
+      <c r="I5" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="J5" s="38"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="38"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+      <c r="M5" s="57"/>
+      <c r="N5" s="57"/>
     </row>
     <row r="6" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="65" t="s">
+      <c r="B6" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="42" t="s">
+      <c r="C6" s="34"/>
+      <c r="D6" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="35"/>
-      <c r="F6" s="44" t="s">
+      <c r="E6" s="34"/>
+      <c r="F6" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="35"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="65" t="s">
+      <c r="I6" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="J6" s="35"/>
-      <c r="K6" s="42" t="s">
+      <c r="J6" s="34"/>
+      <c r="K6" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="L6" s="35"/>
-      <c r="M6" s="44" t="s">
+      <c r="L6" s="34"/>
+      <c r="M6" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="N6" s="35"/>
+      <c r="N6" s="34"/>
     </row>
     <row r="7" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="57">
+      <c r="B7" s="33">
         <v>1962</v>
       </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="52">
+      <c r="C7" s="34"/>
+      <c r="D7" s="55">
         <v>1891</v>
       </c>
-      <c r="E7" s="35"/>
-      <c r="F7" s="64">
+      <c r="E7" s="34"/>
+      <c r="F7" s="35">
         <v>71</v>
       </c>
-      <c r="G7" s="35"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="57">
+      <c r="I7" s="33">
         <v>1962</v>
       </c>
-      <c r="J7" s="35"/>
-      <c r="K7" s="52">
+      <c r="J7" s="34"/>
+      <c r="K7" s="55">
         <v>1865</v>
       </c>
-      <c r="L7" s="35"/>
-      <c r="M7" s="64">
+      <c r="L7" s="34"/>
+      <c r="M7" s="35">
         <v>71</v>
       </c>
-      <c r="N7" s="35"/>
+      <c r="N7" s="34"/>
     </row>
     <row r="8" spans="2:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="3"/>
@@ -2501,29 +2507,29 @@
       <c r="N8" s="3"/>
     </row>
     <row r="9" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="50" t="s">
+      <c r="B9" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="46" t="s">
+      <c r="I9" s="68" t="s">
         <v>59</v>
       </c>
-      <c r="J9" s="41"/>
-      <c r="K9" s="41"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="41"/>
-      <c r="N9" s="35"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="48"/>
+      <c r="M9" s="48"/>
+      <c r="N9" s="34"/>
     </row>
     <row r="10" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="55" t="s">
+      <c r="B10" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="56"/>
+      <c r="C10" s="60"/>
       <c r="D10" s="5" t="s">
         <v>2</v>
       </c>
@@ -2557,10 +2563,10 @@
       </c>
     </row>
     <row r="11" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="36" t="s">
+      <c r="B11" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="35"/>
+      <c r="C11" s="34"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
@@ -2582,10 +2588,10 @@
       </c>
     </row>
     <row r="12" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="35"/>
+      <c r="C12" s="34"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -2607,10 +2613,10 @@
       </c>
     </row>
     <row r="13" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="36" t="s">
+      <c r="B13" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="35"/>
+      <c r="C13" s="34"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
@@ -2632,10 +2638,10 @@
       </c>
     </row>
     <row r="14" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="51" t="s">
+      <c r="B14" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="35"/>
+      <c r="C14" s="34"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -2657,10 +2663,10 @@
       </c>
     </row>
     <row r="15" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="36" t="s">
+      <c r="B15" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="35"/>
+      <c r="C15" s="34"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
@@ -2682,10 +2688,10 @@
       </c>
     </row>
     <row r="16" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="66" t="s">
+      <c r="B16" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="67"/>
+      <c r="C16" s="51"/>
       <c r="D16" s="8">
         <f>SUM(D11:D15)</f>
         <v>0</v>
@@ -2763,135 +2769,135 @@
       <c r="N18" s="3"/>
     </row>
     <row r="19" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="40" t="s">
+      <c r="B19" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="35"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="34"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="40" t="s">
+      <c r="I19" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="J19" s="41"/>
-      <c r="K19" s="41"/>
-      <c r="L19" s="41"/>
-      <c r="M19" s="41"/>
-      <c r="N19" s="35"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="34"/>
     </row>
     <row r="20" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="45" t="s">
+      <c r="B20" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="35"/>
-      <c r="D20" s="45" t="s">
+      <c r="C20" s="34"/>
+      <c r="D20" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="35"/>
-      <c r="F20" s="45" t="s">
+      <c r="E20" s="34"/>
+      <c r="F20" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="35"/>
+      <c r="G20" s="34"/>
       <c r="H20" s="3"/>
-      <c r="I20" s="45" t="s">
+      <c r="I20" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="J20" s="35"/>
-      <c r="K20" s="45" t="s">
+      <c r="J20" s="34"/>
+      <c r="K20" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="L20" s="35"/>
-      <c r="M20" s="45" t="s">
+      <c r="L20" s="34"/>
+      <c r="M20" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="N20" s="35"/>
+      <c r="N20" s="34"/>
     </row>
     <row r="21" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="36" t="s">
+      <c r="B21" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="35"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="35"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="34"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="51" t="s">
+      <c r="I21" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="J21" s="35"/>
-      <c r="K21" s="47"/>
-      <c r="L21" s="35"/>
-      <c r="M21" s="58" t="str">
+      <c r="J21" s="34"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="34"/>
+      <c r="M21" s="61" t="str">
         <f>IF(K23=0,"-",K21/K23)</f>
         <v>-</v>
       </c>
-      <c r="N21" s="35"/>
+      <c r="N21" s="34"/>
     </row>
     <row r="22" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="51" t="s">
+      <c r="B22" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="35"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="35"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="34"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="36" t="s">
+      <c r="I22" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="J22" s="35"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="35"/>
-      <c r="M22" s="54" t="str">
+      <c r="J22" s="34"/>
+      <c r="K22" s="40"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="58" t="str">
         <f>IF(K23=0,"-",K22/K23)</f>
         <v>-</v>
       </c>
-      <c r="N22" s="35"/>
+      <c r="N22" s="34"/>
     </row>
     <row r="23" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="36" t="s">
+      <c r="B23" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="35"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="35"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="34"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="34" t="s">
+      <c r="I23" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="J23" s="35"/>
-      <c r="K23" s="39">
+      <c r="J23" s="34"/>
+      <c r="K23" s="67">
         <f>SUM(K21:L22)</f>
         <v>0</v>
       </c>
-      <c r="L23" s="35"/>
-      <c r="M23" s="59" t="str">
+      <c r="L23" s="34"/>
+      <c r="M23" s="39" t="str">
         <f>IF(K23=0,"-",(K21+K22)/K23)</f>
         <v>-</v>
       </c>
-      <c r="N23" s="35"/>
+      <c r="N23" s="34"/>
     </row>
     <row r="24" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="34" t="s">
+      <c r="B24" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="35"/>
-      <c r="D24" s="60">
+      <c r="C24" s="34"/>
+      <c r="D24" s="45">
         <f>SUM(D21:E23)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="61"/>
-      <c r="F24" s="60">
+      <c r="E24" s="46"/>
+      <c r="F24" s="45">
         <f>SUM(F21:G23)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="61"/>
+      <c r="G24" s="46"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2911,21 +2917,21 @@
     </row>
     <row r="26" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="25"/>
-      <c r="B26" s="32" t="s">
+      <c r="B26" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="33"/>
-      <c r="M26" s="33"/>
-      <c r="N26" s="33"/>
+      <c r="C26" s="65"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="65"/>
+      <c r="F26" s="65"/>
+      <c r="G26" s="65"/>
+      <c r="H26" s="65"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="65"/>
+      <c r="K26" s="65"/>
+      <c r="L26" s="65"/>
+      <c r="M26" s="65"/>
+      <c r="N26" s="65"/>
     </row>
     <row r="27" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="25"/>
@@ -2962,10 +2968,10 @@
       <c r="L27" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="M27" s="68" t="s">
+      <c r="M27" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="N27" s="68" t="s">
+      <c r="N27" s="32" t="s">
         <v>61</v>
       </c>
     </row>
@@ -3113,13 +3119,38 @@
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B26:N26"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="I5:N5"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="I9:N9"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="B4:N4"/>
+    <mergeCell ref="K7:L7"/>
     <mergeCell ref="M23:N23"/>
     <mergeCell ref="F21:G21"/>
     <mergeCell ref="B11:C11"/>
@@ -3136,38 +3167,13 @@
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="B4:N4"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="B26:N26"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="I5:N5"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="I9:N9"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="F7:G7"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/my_project/templates/template_B.xlsx
+++ b/my_project/templates/template_B.xlsx
@@ -722,57 +722,50 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -780,15 +773,15 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="176" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -796,6 +789,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="176" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -803,20 +799,24 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1050,7 +1050,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="lt1">
                         <a:lumMod val="85000"/>
@@ -1225,7 +1225,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="lt1">
                         <a:lumMod val="85000"/>
@@ -1383,7 +1383,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="lt1">
                     <a:lumMod val="85000"/>
@@ -1441,7 +1441,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1300" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="lt1">
                     <a:lumMod val="85000"/>
@@ -1482,7 +1482,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1300" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="lt1">
                     <a:lumMod val="85000"/>
@@ -1542,7 +1542,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="lt1">
                   <a:lumMod val="85000"/>
@@ -2384,112 +2384,112 @@
   <sheetData>
     <row r="1" spans="2:14" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="50"/>
     </row>
     <row r="3" spans="2:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="62" t="s">
+      <c r="B4" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="63"/>
-      <c r="L4" s="63"/>
-      <c r="M4" s="63"/>
-      <c r="N4" s="63"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="61"/>
+      <c r="L4" s="61"/>
+      <c r="M4" s="61"/>
+      <c r="N4" s="61"/>
     </row>
     <row r="5" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="56" t="s">
+      <c r="B5" s="54" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="66" t="s">
+      <c r="I5" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="J5" s="57"/>
-      <c r="K5" s="57"/>
-      <c r="L5" s="57"/>
-      <c r="M5" s="57"/>
-      <c r="N5" s="57"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="39"/>
+      <c r="L5" s="39"/>
+      <c r="M5" s="39"/>
+      <c r="N5" s="39"/>
     </row>
     <row r="6" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="38" t="s">
+      <c r="C6" s="36"/>
+      <c r="D6" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="34"/>
-      <c r="F6" s="37" t="s">
+      <c r="E6" s="36"/>
+      <c r="F6" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="34"/>
+      <c r="G6" s="36"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="36" t="s">
+      <c r="I6" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="J6" s="34"/>
-      <c r="K6" s="38" t="s">
+      <c r="J6" s="36"/>
+      <c r="K6" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="L6" s="34"/>
-      <c r="M6" s="37" t="s">
+      <c r="L6" s="36"/>
+      <c r="M6" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="N6" s="34"/>
+      <c r="N6" s="36"/>
     </row>
     <row r="7" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="33">
+      <c r="B7" s="58">
         <v>1962</v>
       </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="55">
+      <c r="C7" s="36"/>
+      <c r="D7" s="53">
         <v>1891</v>
       </c>
-      <c r="E7" s="34"/>
-      <c r="F7" s="35">
+      <c r="E7" s="36"/>
+      <c r="F7" s="67">
         <v>71</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="36"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="33">
+      <c r="I7" s="58">
         <v>1962</v>
       </c>
-      <c r="J7" s="34"/>
-      <c r="K7" s="55">
+      <c r="J7" s="36"/>
+      <c r="K7" s="53">
         <v>1865</v>
       </c>
-      <c r="L7" s="34"/>
-      <c r="M7" s="35">
+      <c r="L7" s="36"/>
+      <c r="M7" s="67">
         <v>71</v>
       </c>
-      <c r="N7" s="34"/>
+      <c r="N7" s="36"/>
     </row>
     <row r="8" spans="2:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="3"/>
@@ -2507,29 +2507,29 @@
       <c r="N8" s="3"/>
     </row>
     <row r="9" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="68" t="s">
+      <c r="I9" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="J9" s="48"/>
-      <c r="K9" s="48"/>
-      <c r="L9" s="48"/>
-      <c r="M9" s="48"/>
-      <c r="N9" s="34"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="42"/>
+      <c r="L9" s="42"/>
+      <c r="M9" s="42"/>
+      <c r="N9" s="36"/>
     </row>
     <row r="10" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="59" t="s">
+      <c r="B10" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="60"/>
+      <c r="C10" s="57"/>
       <c r="D10" s="5" t="s">
         <v>2</v>
       </c>
@@ -2563,10 +2563,10 @@
       </c>
     </row>
     <row r="11" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="34"/>
+      <c r="C11" s="36"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
@@ -2588,10 +2588,10 @@
       </c>
     </row>
     <row r="12" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="44" t="s">
+      <c r="B12" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="34"/>
+      <c r="C12" s="36"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -2613,10 +2613,10 @@
       </c>
     </row>
     <row r="13" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="34"/>
+      <c r="C13" s="36"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
@@ -2638,10 +2638,10 @@
       </c>
     </row>
     <row r="14" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="44" t="s">
+      <c r="B14" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="34"/>
+      <c r="C14" s="36"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -2663,10 +2663,10 @@
       </c>
     </row>
     <row r="15" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="41" t="s">
+      <c r="B15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="34"/>
+      <c r="C15" s="36"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
@@ -2688,10 +2688,10 @@
       </c>
     </row>
     <row r="16" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="50" t="s">
+      <c r="B16" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="51"/>
+      <c r="C16" s="66"/>
       <c r="D16" s="8">
         <f>SUM(D11:D15)</f>
         <v>0</v>
@@ -2769,135 +2769,135 @@
       <c r="N18" s="3"/>
     </row>
     <row r="19" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="47" t="s">
+      <c r="B19" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="34"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="36"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="47" t="s">
+      <c r="I19" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="34"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="42"/>
+      <c r="M19" s="42"/>
+      <c r="N19" s="36"/>
     </row>
     <row r="20" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="49" t="s">
+      <c r="B20" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="34"/>
-      <c r="D20" s="49" t="s">
+      <c r="C20" s="36"/>
+      <c r="D20" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="34"/>
-      <c r="F20" s="49" t="s">
+      <c r="E20" s="36"/>
+      <c r="F20" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="34"/>
+      <c r="G20" s="36"/>
       <c r="H20" s="3"/>
-      <c r="I20" s="49" t="s">
+      <c r="I20" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="J20" s="34"/>
-      <c r="K20" s="49" t="s">
+      <c r="J20" s="36"/>
+      <c r="K20" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="L20" s="34"/>
-      <c r="M20" s="49" t="s">
+      <c r="L20" s="36"/>
+      <c r="M20" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="N20" s="34"/>
+      <c r="N20" s="36"/>
     </row>
     <row r="21" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="41" t="s">
+      <c r="B21" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="34"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="34"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="36"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="44" t="s">
+      <c r="I21" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="J21" s="34"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="34"/>
-      <c r="M21" s="61" t="str">
+      <c r="J21" s="36"/>
+      <c r="K21" s="48"/>
+      <c r="L21" s="36"/>
+      <c r="M21" s="59" t="str">
         <f>IF(K23=0,"-",K21/K23)</f>
         <v>-</v>
       </c>
-      <c r="N21" s="34"/>
+      <c r="N21" s="36"/>
     </row>
     <row r="22" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="44" t="s">
+      <c r="B22" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="34"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="34"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="36"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="41" t="s">
+      <c r="I22" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="J22" s="34"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="34"/>
-      <c r="M22" s="58" t="str">
+      <c r="J22" s="36"/>
+      <c r="K22" s="44"/>
+      <c r="L22" s="36"/>
+      <c r="M22" s="55" t="str">
         <f>IF(K23=0,"-",K22/K23)</f>
         <v>-</v>
       </c>
-      <c r="N22" s="34"/>
+      <c r="N22" s="36"/>
     </row>
     <row r="23" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="41" t="s">
+      <c r="B23" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="34"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="34"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="36"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="42" t="s">
+      <c r="I23" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="J23" s="34"/>
-      <c r="K23" s="67">
+      <c r="J23" s="36"/>
+      <c r="K23" s="40">
         <f>SUM(K21:L22)</f>
         <v>0</v>
       </c>
-      <c r="L23" s="34"/>
-      <c r="M23" s="39" t="str">
+      <c r="L23" s="36"/>
+      <c r="M23" s="62" t="str">
         <f>IF(K23=0,"-",(K21+K22)/K23)</f>
         <v>-</v>
       </c>
-      <c r="N23" s="34"/>
+      <c r="N23" s="36"/>
     </row>
     <row r="24" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="34"/>
-      <c r="D24" s="45">
+      <c r="C24" s="36"/>
+      <c r="D24" s="63">
         <f>SUM(D21:E23)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="46"/>
-      <c r="F24" s="45">
+      <c r="E24" s="64"/>
+      <c r="F24" s="63">
         <f>SUM(F21:G23)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="46"/>
+      <c r="G24" s="64"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2917,21 +2917,21 @@
     </row>
     <row r="26" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="25"/>
-      <c r="B26" s="64" t="s">
+      <c r="B26" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="65"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="65"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="65"/>
-      <c r="H26" s="65"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="65"/>
-      <c r="K26" s="65"/>
-      <c r="L26" s="65"/>
-      <c r="M26" s="65"/>
-      <c r="N26" s="65"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="34"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="34"/>
+      <c r="K26" s="34"/>
+      <c r="L26" s="34"/>
+      <c r="M26" s="34"/>
+      <c r="N26" s="34"/>
     </row>
     <row r="27" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="25"/>
@@ -3119,6 +3119,45 @@
     </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="I19:N19"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="B4:N4"/>
+    <mergeCell ref="K7:L7"/>
     <mergeCell ref="B26:N26"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="B21:C21"/>
@@ -3135,45 +3174,6 @@
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="K20:L20"/>
     <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="B4:N4"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="I19:N19"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="F7:G7"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/my_project/templates/template_B.xlsx
+++ b/my_project/templates/template_B.xlsx
@@ -722,50 +722,57 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -773,15 +780,15 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="176" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -789,9 +796,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -799,24 +803,20 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1050,10 +1050,11 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="lt1">
-                        <a:lumMod val="85000"/>
+                      <a:schemeClr val="accent5">
+                        <a:lumMod val="40000"/>
+                        <a:lumOff val="60000"/>
                       </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
@@ -1225,10 +1226,11 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="lt1">
-                        <a:lumMod val="85000"/>
+                      <a:schemeClr val="accent2">
+                        <a:lumMod val="40000"/>
+                        <a:lumOff val="60000"/>
                       </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
@@ -2384,112 +2386,112 @@
   <sheetData>
     <row r="1" spans="2:14" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
     </row>
     <row r="3" spans="2:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="60" t="s">
+      <c r="B4" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="61"/>
-      <c r="J4" s="61"/>
-      <c r="K4" s="61"/>
-      <c r="L4" s="61"/>
-      <c r="M4" s="61"/>
-      <c r="N4" s="61"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="63"/>
+      <c r="K4" s="63"/>
+      <c r="L4" s="63"/>
+      <c r="M4" s="63"/>
+      <c r="N4" s="63"/>
     </row>
     <row r="5" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="38" t="s">
+      <c r="I5" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="J5" s="39"/>
-      <c r="K5" s="39"/>
-      <c r="L5" s="39"/>
-      <c r="M5" s="39"/>
-      <c r="N5" s="39"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+      <c r="M5" s="57"/>
+      <c r="N5" s="57"/>
     </row>
     <row r="6" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="68" t="s">
+      <c r="B6" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="43" t="s">
+      <c r="C6" s="34"/>
+      <c r="D6" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="36"/>
-      <c r="F6" s="45" t="s">
+      <c r="E6" s="34"/>
+      <c r="F6" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="36"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="68" t="s">
+      <c r="I6" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="J6" s="36"/>
-      <c r="K6" s="43" t="s">
+      <c r="J6" s="34"/>
+      <c r="K6" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="L6" s="36"/>
-      <c r="M6" s="45" t="s">
+      <c r="L6" s="34"/>
+      <c r="M6" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="N6" s="36"/>
+      <c r="N6" s="34"/>
     </row>
     <row r="7" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="58">
+      <c r="B7" s="33">
         <v>1962</v>
       </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="53">
+      <c r="C7" s="34"/>
+      <c r="D7" s="55">
         <v>1891</v>
       </c>
-      <c r="E7" s="36"/>
-      <c r="F7" s="67">
+      <c r="E7" s="34"/>
+      <c r="F7" s="35">
         <v>71</v>
       </c>
-      <c r="G7" s="36"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="58">
+      <c r="I7" s="33">
         <v>1962</v>
       </c>
-      <c r="J7" s="36"/>
-      <c r="K7" s="53">
+      <c r="J7" s="34"/>
+      <c r="K7" s="55">
         <v>1865</v>
       </c>
-      <c r="L7" s="36"/>
-      <c r="M7" s="67">
+      <c r="L7" s="34"/>
+      <c r="M7" s="35">
         <v>71</v>
       </c>
-      <c r="N7" s="36"/>
+      <c r="N7" s="34"/>
     </row>
     <row r="8" spans="2:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="3"/>
@@ -2507,29 +2509,29 @@
       <c r="N8" s="3"/>
     </row>
     <row r="9" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="47" t="s">
+      <c r="I9" s="68" t="s">
         <v>59</v>
       </c>
-      <c r="J9" s="42"/>
-      <c r="K9" s="42"/>
-      <c r="L9" s="42"/>
-      <c r="M9" s="42"/>
-      <c r="N9" s="36"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="48"/>
+      <c r="M9" s="48"/>
+      <c r="N9" s="34"/>
     </row>
     <row r="10" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="56" t="s">
+      <c r="B10" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="57"/>
+      <c r="C10" s="60"/>
       <c r="D10" s="5" t="s">
         <v>2</v>
       </c>
@@ -2563,10 +2565,10 @@
       </c>
     </row>
     <row r="11" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="37" t="s">
+      <c r="B11" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="36"/>
+      <c r="C11" s="34"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
@@ -2588,10 +2590,10 @@
       </c>
     </row>
     <row r="12" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="52" t="s">
+      <c r="B12" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="36"/>
+      <c r="C12" s="34"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -2613,10 +2615,10 @@
       </c>
     </row>
     <row r="13" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="37" t="s">
+      <c r="B13" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="36"/>
+      <c r="C13" s="34"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
@@ -2638,10 +2640,10 @@
       </c>
     </row>
     <row r="14" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="52" t="s">
+      <c r="B14" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="36"/>
+      <c r="C14" s="34"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -2663,10 +2665,10 @@
       </c>
     </row>
     <row r="15" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="37" t="s">
+      <c r="B15" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="36"/>
+      <c r="C15" s="34"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
@@ -2688,10 +2690,10 @@
       </c>
     </row>
     <row r="16" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="65" t="s">
+      <c r="B16" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="66"/>
+      <c r="C16" s="51"/>
       <c r="D16" s="8">
         <f>SUM(D11:D15)</f>
         <v>0</v>
@@ -2769,135 +2771,135 @@
       <c r="N18" s="3"/>
     </row>
     <row r="19" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="41" t="s">
+      <c r="B19" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="36"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="34"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="41" t="s">
+      <c r="I19" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="J19" s="42"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="42"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="36"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="34"/>
     </row>
     <row r="20" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="46" t="s">
+      <c r="B20" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="46" t="s">
+      <c r="C20" s="34"/>
+      <c r="D20" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="36"/>
-      <c r="F20" s="46" t="s">
+      <c r="E20" s="34"/>
+      <c r="F20" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="36"/>
+      <c r="G20" s="34"/>
       <c r="H20" s="3"/>
-      <c r="I20" s="46" t="s">
+      <c r="I20" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="J20" s="36"/>
-      <c r="K20" s="46" t="s">
+      <c r="J20" s="34"/>
+      <c r="K20" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="L20" s="36"/>
-      <c r="M20" s="46" t="s">
+      <c r="L20" s="34"/>
+      <c r="M20" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="N20" s="36"/>
+      <c r="N20" s="34"/>
     </row>
     <row r="21" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="37" t="s">
+      <c r="B21" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="36"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="36"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="34"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="52" t="s">
+      <c r="I21" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="J21" s="36"/>
-      <c r="K21" s="48"/>
-      <c r="L21" s="36"/>
-      <c r="M21" s="59" t="str">
+      <c r="J21" s="34"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="34"/>
+      <c r="M21" s="61" t="str">
         <f>IF(K23=0,"-",K21/K23)</f>
         <v>-</v>
       </c>
-      <c r="N21" s="36"/>
+      <c r="N21" s="34"/>
     </row>
     <row r="22" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="52" t="s">
+      <c r="B22" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="36"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="34"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="37" t="s">
+      <c r="I22" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="J22" s="36"/>
-      <c r="K22" s="44"/>
-      <c r="L22" s="36"/>
-      <c r="M22" s="55" t="str">
+      <c r="J22" s="34"/>
+      <c r="K22" s="40"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="58" t="str">
         <f>IF(K23=0,"-",K22/K23)</f>
         <v>-</v>
       </c>
-      <c r="N22" s="36"/>
+      <c r="N22" s="34"/>
     </row>
     <row r="23" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="37" t="s">
+      <c r="B23" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="36"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="36"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="34"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="35" t="s">
+      <c r="I23" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="J23" s="36"/>
-      <c r="K23" s="40">
+      <c r="J23" s="34"/>
+      <c r="K23" s="67">
         <f>SUM(K21:L22)</f>
         <v>0</v>
       </c>
-      <c r="L23" s="36"/>
-      <c r="M23" s="62" t="str">
+      <c r="L23" s="34"/>
+      <c r="M23" s="39" t="str">
         <f>IF(K23=0,"-",(K21+K22)/K23)</f>
         <v>-</v>
       </c>
-      <c r="N23" s="36"/>
+      <c r="N23" s="34"/>
     </row>
     <row r="24" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="35" t="s">
+      <c r="B24" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="36"/>
-      <c r="D24" s="63">
+      <c r="C24" s="34"/>
+      <c r="D24" s="45">
         <f>SUM(D21:E23)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="64"/>
-      <c r="F24" s="63">
+      <c r="E24" s="46"/>
+      <c r="F24" s="45">
         <f>SUM(F21:G23)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="64"/>
+      <c r="G24" s="46"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2917,21 +2919,21 @@
     </row>
     <row r="26" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="25"/>
-      <c r="B26" s="33" t="s">
+      <c r="B26" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="34"/>
-      <c r="I26" s="34"/>
-      <c r="J26" s="34"/>
-      <c r="K26" s="34"/>
-      <c r="L26" s="34"/>
-      <c r="M26" s="34"/>
-      <c r="N26" s="34"/>
+      <c r="C26" s="65"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="65"/>
+      <c r="F26" s="65"/>
+      <c r="G26" s="65"/>
+      <c r="H26" s="65"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="65"/>
+      <c r="K26" s="65"/>
+      <c r="L26" s="65"/>
+      <c r="M26" s="65"/>
+      <c r="N26" s="65"/>
     </row>
     <row r="27" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="25"/>
@@ -3119,13 +3121,38 @@
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B26:N26"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="I5:N5"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="I9:N9"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="B4:N4"/>
+    <mergeCell ref="K7:L7"/>
     <mergeCell ref="M23:N23"/>
     <mergeCell ref="F21:G21"/>
     <mergeCell ref="B11:C11"/>
@@ -3142,38 +3169,13 @@
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="B4:N4"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="B26:N26"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="I5:N5"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="I9:N9"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="F7:G7"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/my_project/templates/template_B.xlsx
+++ b/my_project/templates/template_B.xlsx
@@ -722,57 +722,50 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -780,15 +773,15 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="176" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -796,6 +789,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="176" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -803,20 +799,24 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1564,26 +1564,9 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:gradFill flip="none" rotWithShape="1">
-      <a:gsLst>
-        <a:gs pos="0">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:gs>
-        <a:gs pos="100000">
-          <a:schemeClr val="dk1">
-            <a:lumMod val="85000"/>
-            <a:lumOff val="15000"/>
-          </a:schemeClr>
-        </a:gs>
-      </a:gsLst>
-      <a:path path="circle">
-        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-      </a:path>
-      <a:tileRect/>
-    </a:gradFill>
+    <a:solidFill>
+      <a:srgbClr val="002060"/>
+    </a:solidFill>
     <a:ln>
       <a:noFill/>
     </a:ln>
@@ -2386,112 +2369,112 @@
   <sheetData>
     <row r="1" spans="2:14" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="50"/>
     </row>
     <row r="3" spans="2:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="62" t="s">
+      <c r="B4" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="63"/>
-      <c r="L4" s="63"/>
-      <c r="M4" s="63"/>
-      <c r="N4" s="63"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="61"/>
+      <c r="L4" s="61"/>
+      <c r="M4" s="61"/>
+      <c r="N4" s="61"/>
     </row>
     <row r="5" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="56" t="s">
+      <c r="B5" s="54" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="66" t="s">
+      <c r="I5" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="J5" s="57"/>
-      <c r="K5" s="57"/>
-      <c r="L5" s="57"/>
-      <c r="M5" s="57"/>
-      <c r="N5" s="57"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="39"/>
+      <c r="L5" s="39"/>
+      <c r="M5" s="39"/>
+      <c r="N5" s="39"/>
     </row>
     <row r="6" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="38" t="s">
+      <c r="C6" s="36"/>
+      <c r="D6" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="34"/>
-      <c r="F6" s="37" t="s">
+      <c r="E6" s="36"/>
+      <c r="F6" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="34"/>
+      <c r="G6" s="36"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="36" t="s">
+      <c r="I6" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="J6" s="34"/>
-      <c r="K6" s="38" t="s">
+      <c r="J6" s="36"/>
+      <c r="K6" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="L6" s="34"/>
-      <c r="M6" s="37" t="s">
+      <c r="L6" s="36"/>
+      <c r="M6" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="N6" s="34"/>
+      <c r="N6" s="36"/>
     </row>
     <row r="7" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="33">
+      <c r="B7" s="58">
         <v>1962</v>
       </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="55">
+      <c r="C7" s="36"/>
+      <c r="D7" s="53">
         <v>1891</v>
       </c>
-      <c r="E7" s="34"/>
-      <c r="F7" s="35">
+      <c r="E7" s="36"/>
+      <c r="F7" s="67">
         <v>71</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="36"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="33">
+      <c r="I7" s="58">
         <v>1962</v>
       </c>
-      <c r="J7" s="34"/>
-      <c r="K7" s="55">
+      <c r="J7" s="36"/>
+      <c r="K7" s="53">
         <v>1865</v>
       </c>
-      <c r="L7" s="34"/>
-      <c r="M7" s="35">
+      <c r="L7" s="36"/>
+      <c r="M7" s="67">
         <v>71</v>
       </c>
-      <c r="N7" s="34"/>
+      <c r="N7" s="36"/>
     </row>
     <row r="8" spans="2:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="3"/>
@@ -2509,29 +2492,29 @@
       <c r="N8" s="3"/>
     </row>
     <row r="9" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="68" t="s">
+      <c r="I9" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="J9" s="48"/>
-      <c r="K9" s="48"/>
-      <c r="L9" s="48"/>
-      <c r="M9" s="48"/>
-      <c r="N9" s="34"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="42"/>
+      <c r="L9" s="42"/>
+      <c r="M9" s="42"/>
+      <c r="N9" s="36"/>
     </row>
     <row r="10" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="59" t="s">
+      <c r="B10" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="60"/>
+      <c r="C10" s="57"/>
       <c r="D10" s="5" t="s">
         <v>2</v>
       </c>
@@ -2565,10 +2548,10 @@
       </c>
     </row>
     <row r="11" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="34"/>
+      <c r="C11" s="36"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
@@ -2590,10 +2573,10 @@
       </c>
     </row>
     <row r="12" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="44" t="s">
+      <c r="B12" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="34"/>
+      <c r="C12" s="36"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -2615,10 +2598,10 @@
       </c>
     </row>
     <row r="13" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="34"/>
+      <c r="C13" s="36"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
@@ -2640,10 +2623,10 @@
       </c>
     </row>
     <row r="14" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="44" t="s">
+      <c r="B14" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="34"/>
+      <c r="C14" s="36"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -2665,10 +2648,10 @@
       </c>
     </row>
     <row r="15" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="41" t="s">
+      <c r="B15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="34"/>
+      <c r="C15" s="36"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
@@ -2690,10 +2673,10 @@
       </c>
     </row>
     <row r="16" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="50" t="s">
+      <c r="B16" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="51"/>
+      <c r="C16" s="66"/>
       <c r="D16" s="8">
         <f>SUM(D11:D15)</f>
         <v>0</v>
@@ -2771,135 +2754,135 @@
       <c r="N18" s="3"/>
     </row>
     <row r="19" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="47" t="s">
+      <c r="B19" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="34"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="36"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="47" t="s">
+      <c r="I19" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="34"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="42"/>
+      <c r="M19" s="42"/>
+      <c r="N19" s="36"/>
     </row>
     <row r="20" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="49" t="s">
+      <c r="B20" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="34"/>
-      <c r="D20" s="49" t="s">
+      <c r="C20" s="36"/>
+      <c r="D20" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="34"/>
-      <c r="F20" s="49" t="s">
+      <c r="E20" s="36"/>
+      <c r="F20" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="34"/>
+      <c r="G20" s="36"/>
       <c r="H20" s="3"/>
-      <c r="I20" s="49" t="s">
+      <c r="I20" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="J20" s="34"/>
-      <c r="K20" s="49" t="s">
+      <c r="J20" s="36"/>
+      <c r="K20" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="L20" s="34"/>
-      <c r="M20" s="49" t="s">
+      <c r="L20" s="36"/>
+      <c r="M20" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="N20" s="34"/>
+      <c r="N20" s="36"/>
     </row>
     <row r="21" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="41" t="s">
+      <c r="B21" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="34"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="34"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="36"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="44" t="s">
+      <c r="I21" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="J21" s="34"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="34"/>
-      <c r="M21" s="61" t="str">
+      <c r="J21" s="36"/>
+      <c r="K21" s="48"/>
+      <c r="L21" s="36"/>
+      <c r="M21" s="59" t="str">
         <f>IF(K23=0,"-",K21/K23)</f>
         <v>-</v>
       </c>
-      <c r="N21" s="34"/>
+      <c r="N21" s="36"/>
     </row>
     <row r="22" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="44" t="s">
+      <c r="B22" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="34"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="34"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="36"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="41" t="s">
+      <c r="I22" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="J22" s="34"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="34"/>
-      <c r="M22" s="58" t="str">
+      <c r="J22" s="36"/>
+      <c r="K22" s="44"/>
+      <c r="L22" s="36"/>
+      <c r="M22" s="55" t="str">
         <f>IF(K23=0,"-",K22/K23)</f>
         <v>-</v>
       </c>
-      <c r="N22" s="34"/>
+      <c r="N22" s="36"/>
     </row>
     <row r="23" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="41" t="s">
+      <c r="B23" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="34"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="34"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="36"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="42" t="s">
+      <c r="I23" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="J23" s="34"/>
-      <c r="K23" s="67">
+      <c r="J23" s="36"/>
+      <c r="K23" s="40">
         <f>SUM(K21:L22)</f>
         <v>0</v>
       </c>
-      <c r="L23" s="34"/>
-      <c r="M23" s="39" t="str">
+      <c r="L23" s="36"/>
+      <c r="M23" s="62" t="str">
         <f>IF(K23=0,"-",(K21+K22)/K23)</f>
         <v>-</v>
       </c>
-      <c r="N23" s="34"/>
+      <c r="N23" s="36"/>
     </row>
     <row r="24" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="34"/>
-      <c r="D24" s="45">
+      <c r="C24" s="36"/>
+      <c r="D24" s="63">
         <f>SUM(D21:E23)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="46"/>
-      <c r="F24" s="45">
+      <c r="E24" s="64"/>
+      <c r="F24" s="63">
         <f>SUM(F21:G23)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="46"/>
+      <c r="G24" s="64"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2919,21 +2902,21 @@
     </row>
     <row r="26" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="25"/>
-      <c r="B26" s="64" t="s">
+      <c r="B26" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="65"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="65"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="65"/>
-      <c r="H26" s="65"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="65"/>
-      <c r="K26" s="65"/>
-      <c r="L26" s="65"/>
-      <c r="M26" s="65"/>
-      <c r="N26" s="65"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="34"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="34"/>
+      <c r="K26" s="34"/>
+      <c r="L26" s="34"/>
+      <c r="M26" s="34"/>
+      <c r="N26" s="34"/>
     </row>
     <row r="27" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="25"/>
@@ -3121,6 +3104,45 @@
     </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="I19:N19"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="B4:N4"/>
+    <mergeCell ref="K7:L7"/>
     <mergeCell ref="B26:N26"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="B21:C21"/>
@@ -3137,45 +3159,6 @@
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="K20:L20"/>
     <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="B4:N4"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="I19:N19"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="F7:G7"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/my_project/templates/template_B.xlsx
+++ b/my_project/templates/template_B.xlsx
@@ -722,50 +722,57 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -773,15 +780,15 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="176" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -789,9 +796,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -799,24 +803,20 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -928,22 +928,16 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="95000"/>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:effectLst>
-                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-                    <a:prstClr val="black">
-                      <a:alpha val="40000"/>
-                    </a:prstClr>
-                  </a:outerShdw>
-                </a:effectLst>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:latin typeface="+mj-lt"/>
+                <a:ea typeface="+mj-ea"/>
+                <a:cs typeface="+mj-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -980,22 +974,16 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:effectLst>
-                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="40000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
+              <a:latin typeface="+mj-lt"/>
+              <a:ea typeface="+mj-ea"/>
+              <a:cs typeface="+mj-cs"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="ko-KR"/>
@@ -1024,7 +1012,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="34925" cap="rnd">
+            <a:ln w="22225" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -1050,11 +1038,11 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="accent5">
-                        <a:lumMod val="40000"/>
-                        <a:lumOff val="60000"/>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
                       </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
@@ -1079,13 +1067,14 @@
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
-                    <a:ln w="9525">
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
                       <a:solidFill>
-                        <a:schemeClr val="lt1">
-                          <a:lumMod val="95000"/>
-                          <a:alpha val="54000"/>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
                         </a:schemeClr>
                       </a:solidFill>
+                      <a:round/>
                     </a:ln>
                     <a:effectLst/>
                   </c:spPr>
@@ -1200,7 +1189,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="34925" cap="rnd">
+            <a:ln w="22225" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
@@ -1226,11 +1215,11 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="accent2">
-                        <a:lumMod val="40000"/>
-                        <a:lumOff val="60000"/>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
                       </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
@@ -1255,13 +1244,14 @@
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
-                    <a:ln w="9525">
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
                       <a:solidFill>
-                        <a:schemeClr val="lt1">
-                          <a:lumMod val="95000"/>
-                          <a:alpha val="54000"/>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
                         </a:schemeClr>
                       </a:solidFill>
+                      <a:round/>
                     </a:ln>
                     <a:effectLst/>
                   </c:spPr>
@@ -1363,17 +1353,31 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:lumMod val="95000"/>
-                <a:alpha val="54000"/>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -1385,10 +1389,11 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -1417,9 +1422,9 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="95000"/>
-                  <a:alpha val="10000"/>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -1443,10 +1448,11 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1300" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -1484,10 +1490,11 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1300" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="lt1">
-                    <a:lumMod val="85000"/>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -1510,7 +1517,7 @@
         <c:delete val="1"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1311023295"/>
@@ -1521,7 +1528,17 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:spPr>
-        <a:noFill/>
+        <a:pattFill prst="ltDnDiag">
+          <a:fgClr>
+            <a:schemeClr val="dk1">
+              <a:lumMod val="15000"/>
+              <a:lumOff val="85000"/>
+            </a:schemeClr>
+          </a:fgClr>
+          <a:bgClr>
+            <a:schemeClr val="lt1"/>
+          </a:bgClr>
+        </a:pattFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -1544,10 +1561,11 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:lumMod val="85000"/>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -1565,10 +1583,16 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="002060"/>
+      <a:schemeClr val="lt1"/>
     </a:solidFill>
-    <a:ln>
-      <a:noFill/>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
     </a:ln>
     <a:effectLst/>
   </c:spPr>
@@ -1631,39 +1655,41 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="328">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="221">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
   </cs:categoryAxis>
   <cs:chartArea>
     <cs:lnRef idx="0"/>
@@ -1673,36 +1699,29 @@
       <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:gradFill flip="none" rotWithShape="1">
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="65000"/>
-              <a:lumOff val="35000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="85000"/>
-              <a:lumOff val="15000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:path path="circle">
-          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-        </a:path>
-        <a:tileRect/>
-      </a:gradFill>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -1721,6 +1740,14 @@
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
@@ -1729,35 +1756,45 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="3"/>
+    <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="3"/>
+    <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="34925" cap="rnd">
+      <a:ln w="22225" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -1769,15 +1806,18 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="3">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="3"/>
+    <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="15875">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -1790,10 +1830,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -1809,56 +1849,46 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="800" kern="1200"/>
   </cs:dataTable>
   <cs:downBar>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:gradFill>
-        <a:gsLst>
-          <a:gs pos="100000">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="95000"/>
-              <a:lumOff val="5000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="0">
-            <a:schemeClr val="dk1">
-              <a:lumMod val="75000"/>
-              <a:lumOff val="25000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:path path="circle">
-          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-        </a:path>
-      </a:gradFill>
-      <a:ln w="9525">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -1867,12 +1897,15 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
@@ -1883,13 +1916,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -1901,22 +1935,35 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="10000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -1928,16 +1975,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="5000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
@@ -1946,12 +1994,15 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
@@ -1962,16 +2013,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -1980,8 +2032,9 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -1991,37 +2044,45 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
   </cs:plotArea>
   <cs:plotArea3D>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:plotArea3D>
   <cs:seriesAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -2029,14 +2090,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="54000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2047,20 +2108,13 @@
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="95000"/>
+    <cs:fontRef idx="major">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
-      <a:effectLst>
-        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-          <a:prstClr val="black">
-            <a:alpha val="40000"/>
-          </a:prstClr>
-        </a:outerShdw>
-      </a:effectLst>
-    </cs:defRPr>
+    <cs:defRPr sz="1600" b="1" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -2069,7 +2123,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
@@ -2084,8 +2138,9 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2095,27 +2150,18 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:gradFill>
-        <a:gsLst>
-          <a:gs pos="100000">
-            <a:schemeClr val="lt1">
-              <a:lumMod val="85000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="0">
-            <a:schemeClr val="lt1"/>
-          </a:gs>
-        </a:gsLst>
-        <a:path path="circle">
-          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-        </a:path>
-      </a:gradFill>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="lt1"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
@@ -2126,8 +2172,9 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1">
-        <a:lumMod val="85000"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2137,8 +2184,21 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -2369,112 +2429,112 @@
   <sheetData>
     <row r="1" spans="2:14" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
     </row>
     <row r="3" spans="2:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="60" t="s">
+      <c r="B4" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="61"/>
-      <c r="J4" s="61"/>
-      <c r="K4" s="61"/>
-      <c r="L4" s="61"/>
-      <c r="M4" s="61"/>
-      <c r="N4" s="61"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="63"/>
+      <c r="K4" s="63"/>
+      <c r="L4" s="63"/>
+      <c r="M4" s="63"/>
+      <c r="N4" s="63"/>
     </row>
     <row r="5" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="38" t="s">
+      <c r="I5" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="J5" s="39"/>
-      <c r="K5" s="39"/>
-      <c r="L5" s="39"/>
-      <c r="M5" s="39"/>
-      <c r="N5" s="39"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+      <c r="M5" s="57"/>
+      <c r="N5" s="57"/>
     </row>
     <row r="6" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="68" t="s">
+      <c r="B6" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="43" t="s">
+      <c r="C6" s="34"/>
+      <c r="D6" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="36"/>
-      <c r="F6" s="45" t="s">
+      <c r="E6" s="34"/>
+      <c r="F6" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="36"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="68" t="s">
+      <c r="I6" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="J6" s="36"/>
-      <c r="K6" s="43" t="s">
+      <c r="J6" s="34"/>
+      <c r="K6" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="L6" s="36"/>
-      <c r="M6" s="45" t="s">
+      <c r="L6" s="34"/>
+      <c r="M6" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="N6" s="36"/>
+      <c r="N6" s="34"/>
     </row>
     <row r="7" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="58">
+      <c r="B7" s="33">
         <v>1962</v>
       </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="53">
+      <c r="C7" s="34"/>
+      <c r="D7" s="55">
         <v>1891</v>
       </c>
-      <c r="E7" s="36"/>
-      <c r="F7" s="67">
+      <c r="E7" s="34"/>
+      <c r="F7" s="35">
         <v>71</v>
       </c>
-      <c r="G7" s="36"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="58">
+      <c r="I7" s="33">
         <v>1962</v>
       </c>
-      <c r="J7" s="36"/>
-      <c r="K7" s="53">
+      <c r="J7" s="34"/>
+      <c r="K7" s="55">
         <v>1865</v>
       </c>
-      <c r="L7" s="36"/>
-      <c r="M7" s="67">
+      <c r="L7" s="34"/>
+      <c r="M7" s="35">
         <v>71</v>
       </c>
-      <c r="N7" s="36"/>
+      <c r="N7" s="34"/>
     </row>
     <row r="8" spans="2:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="3"/>
@@ -2492,29 +2552,29 @@
       <c r="N8" s="3"/>
     </row>
     <row r="9" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="47" t="s">
+      <c r="I9" s="68" t="s">
         <v>59</v>
       </c>
-      <c r="J9" s="42"/>
-      <c r="K9" s="42"/>
-      <c r="L9" s="42"/>
-      <c r="M9" s="42"/>
-      <c r="N9" s="36"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="48"/>
+      <c r="M9" s="48"/>
+      <c r="N9" s="34"/>
     </row>
     <row r="10" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="56" t="s">
+      <c r="B10" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="57"/>
+      <c r="C10" s="60"/>
       <c r="D10" s="5" t="s">
         <v>2</v>
       </c>
@@ -2548,10 +2608,10 @@
       </c>
     </row>
     <row r="11" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="37" t="s">
+      <c r="B11" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="36"/>
+      <c r="C11" s="34"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
@@ -2573,10 +2633,10 @@
       </c>
     </row>
     <row r="12" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="52" t="s">
+      <c r="B12" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="36"/>
+      <c r="C12" s="34"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -2598,10 +2658,10 @@
       </c>
     </row>
     <row r="13" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="37" t="s">
+      <c r="B13" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="36"/>
+      <c r="C13" s="34"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
@@ -2623,10 +2683,10 @@
       </c>
     </row>
     <row r="14" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="52" t="s">
+      <c r="B14" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="36"/>
+      <c r="C14" s="34"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -2648,10 +2708,10 @@
       </c>
     </row>
     <row r="15" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="37" t="s">
+      <c r="B15" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="36"/>
+      <c r="C15" s="34"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
@@ -2673,10 +2733,10 @@
       </c>
     </row>
     <row r="16" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="65" t="s">
+      <c r="B16" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="66"/>
+      <c r="C16" s="51"/>
       <c r="D16" s="8">
         <f>SUM(D11:D15)</f>
         <v>0</v>
@@ -2754,135 +2814,135 @@
       <c r="N18" s="3"/>
     </row>
     <row r="19" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="41" t="s">
+      <c r="B19" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="36"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="34"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="41" t="s">
+      <c r="I19" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="J19" s="42"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="42"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="36"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="34"/>
     </row>
     <row r="20" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="46" t="s">
+      <c r="B20" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="46" t="s">
+      <c r="C20" s="34"/>
+      <c r="D20" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="36"/>
-      <c r="F20" s="46" t="s">
+      <c r="E20" s="34"/>
+      <c r="F20" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="36"/>
+      <c r="G20" s="34"/>
       <c r="H20" s="3"/>
-      <c r="I20" s="46" t="s">
+      <c r="I20" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="J20" s="36"/>
-      <c r="K20" s="46" t="s">
+      <c r="J20" s="34"/>
+      <c r="K20" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="L20" s="36"/>
-      <c r="M20" s="46" t="s">
+      <c r="L20" s="34"/>
+      <c r="M20" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="N20" s="36"/>
+      <c r="N20" s="34"/>
     </row>
     <row r="21" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="37" t="s">
+      <c r="B21" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="36"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="36"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="34"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="52" t="s">
+      <c r="I21" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="J21" s="36"/>
-      <c r="K21" s="48"/>
-      <c r="L21" s="36"/>
-      <c r="M21" s="59" t="str">
+      <c r="J21" s="34"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="34"/>
+      <c r="M21" s="61" t="str">
         <f>IF(K23=0,"-",K21/K23)</f>
         <v>-</v>
       </c>
-      <c r="N21" s="36"/>
+      <c r="N21" s="34"/>
     </row>
     <row r="22" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="52" t="s">
+      <c r="B22" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="36"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="34"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="37" t="s">
+      <c r="I22" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="J22" s="36"/>
-      <c r="K22" s="44"/>
-      <c r="L22" s="36"/>
-      <c r="M22" s="55" t="str">
+      <c r="J22" s="34"/>
+      <c r="K22" s="40"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="58" t="str">
         <f>IF(K23=0,"-",K22/K23)</f>
         <v>-</v>
       </c>
-      <c r="N22" s="36"/>
+      <c r="N22" s="34"/>
     </row>
     <row r="23" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="37" t="s">
+      <c r="B23" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="36"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="36"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="34"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="35" t="s">
+      <c r="I23" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="J23" s="36"/>
-      <c r="K23" s="40">
+      <c r="J23" s="34"/>
+      <c r="K23" s="67">
         <f>SUM(K21:L22)</f>
         <v>0</v>
       </c>
-      <c r="L23" s="36"/>
-      <c r="M23" s="62" t="str">
+      <c r="L23" s="34"/>
+      <c r="M23" s="39" t="str">
         <f>IF(K23=0,"-",(K21+K22)/K23)</f>
         <v>-</v>
       </c>
-      <c r="N23" s="36"/>
+      <c r="N23" s="34"/>
     </row>
     <row r="24" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="35" t="s">
+      <c r="B24" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="36"/>
-      <c r="D24" s="63">
+      <c r="C24" s="34"/>
+      <c r="D24" s="45">
         <f>SUM(D21:E23)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="64"/>
-      <c r="F24" s="63">
+      <c r="E24" s="46"/>
+      <c r="F24" s="45">
         <f>SUM(F21:G23)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="64"/>
+      <c r="G24" s="46"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2902,21 +2962,21 @@
     </row>
     <row r="26" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="25"/>
-      <c r="B26" s="33" t="s">
+      <c r="B26" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="34"/>
-      <c r="I26" s="34"/>
-      <c r="J26" s="34"/>
-      <c r="K26" s="34"/>
-      <c r="L26" s="34"/>
-      <c r="M26" s="34"/>
-      <c r="N26" s="34"/>
+      <c r="C26" s="65"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="65"/>
+      <c r="F26" s="65"/>
+      <c r="G26" s="65"/>
+      <c r="H26" s="65"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="65"/>
+      <c r="K26" s="65"/>
+      <c r="L26" s="65"/>
+      <c r="M26" s="65"/>
+      <c r="N26" s="65"/>
     </row>
     <row r="27" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="25"/>
@@ -3104,13 +3164,38 @@
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B26:N26"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="I5:N5"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="I9:N9"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="B4:N4"/>
+    <mergeCell ref="K7:L7"/>
     <mergeCell ref="M23:N23"/>
     <mergeCell ref="F21:G21"/>
     <mergeCell ref="B11:C11"/>
@@ -3127,38 +3212,13 @@
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="B4:N4"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="B26:N26"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="I5:N5"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="I9:N9"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="F7:G7"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/my_project/templates/template_B.xlsx
+++ b/my_project/templates/template_B.xlsx
@@ -722,57 +722,50 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -780,15 +773,15 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="176" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -796,6 +789,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="176" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -803,20 +799,24 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -928,35 +928,35 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="dk1">
+                  <a:schemeClr val="tx1">
                     <a:lumMod val="50000"/>
                     <a:lumOff val="50000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mj-lt"/>
-                <a:ea typeface="+mj-ea"/>
-                <a:cs typeface="+mj-cs"/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="ko-KR"/>
+              <a:rPr lang="ko-KR" b="1"/>
               <a:t>▎ 월별 임관리비 납부 및 임대자산 출고 추이</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-US" b="1"/>
               <a:t>(</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="ko-KR"/>
+              <a:rPr lang="ko-KR" b="1"/>
               <a:t>그래프</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-US" b="1"/>
               <a:t>)</a:t>
             </a:r>
-            <a:endParaRPr lang="ko-KR"/>
+            <a:endParaRPr lang="ko-KR" b="1"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -974,16 +974,16 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1">
+                <a:schemeClr val="tx1">
                   <a:lumMod val="50000"/>
                   <a:lumOff val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mj-lt"/>
-              <a:ea typeface="+mj-ea"/>
-              <a:cs typeface="+mj-cs"/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="ko-KR"/>
@@ -1012,7 +1012,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="22225" cap="rnd">
+            <a:ln w="38100" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -1038,12 +1038,9 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="dk1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
+                      <a:schemeClr val="accent5"/>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -1067,14 +1064,13 @@
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                    <a:ln w="9525">
                       <a:solidFill>
-                        <a:schemeClr val="dk1">
+                        <a:schemeClr val="tx1">
                           <a:lumMod val="35000"/>
                           <a:lumOff val="65000"/>
                         </a:schemeClr>
                       </a:solidFill>
-                      <a:round/>
                     </a:ln>
                     <a:effectLst/>
                   </c:spPr>
@@ -1189,7 +1185,7 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="22225" cap="rnd">
+            <a:ln w="38100" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
@@ -1215,12 +1211,9 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="dk1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
+                      <a:srgbClr val="FF0000"/>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -1244,14 +1237,13 @@
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                    <a:ln w="9525">
                       <a:solidFill>
-                        <a:schemeClr val="dk1">
+                        <a:schemeClr val="tx1">
                           <a:lumMod val="35000"/>
                           <a:lumOff val="65000"/>
                         </a:schemeClr>
                       </a:solidFill>
-                      <a:round/>
                     </a:ln>
                     <a:effectLst/>
                   </c:spPr>
@@ -1353,29 +1345,15 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="dk1">
+              <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
                 <a:lumOff val="85000"/>
               </a:schemeClr>
@@ -1389,11 +1367,11 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+              <a:defRPr sz="1300" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -1422,7 +1400,7 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="dk1">
+                <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
                   <a:lumOff val="85000"/>
                 </a:schemeClr>
@@ -1448,11 +1426,11 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1300" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -1490,11 +1468,11 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1300" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -1517,7 +1495,7 @@
         <c:delete val="1"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1311023295"/>
@@ -1528,17 +1506,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:spPr>
-        <a:pattFill prst="ltDnDiag">
-          <a:fgClr>
-            <a:schemeClr val="dk1">
-              <a:lumMod val="15000"/>
-              <a:lumOff val="85000"/>
-            </a:schemeClr>
-          </a:fgClr>
-          <a:bgClr>
-            <a:schemeClr val="lt1"/>
-          </a:bgClr>
-        </a:pattFill>
+        <a:noFill/>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -1561,11 +1529,11 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -1583,11 +1551,11 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="dk1">
+        <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
           <a:lumOff val="85000"/>
         </a:schemeClr>
@@ -1655,33 +1623,33 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="221">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="325">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="dk1">
+          <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -1689,9 +1657,9 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
-  <cs:chartArea>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
@@ -1700,11 +1668,11 @@
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="lt1"/>
+        <a:schemeClr val="bg1"/>
       </a:solidFill>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="dk1">
+          <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -1719,9 +1687,9 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -1755,46 +1723,62 @@
     </cs:bodyPr>
   </cs:dataLabelCallout>
   <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="1"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
     </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="1"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
     </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="22225" cap="rnd">
+      <a:ln w="15875" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -1806,31 +1790,30 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="2">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
+    <cs:effectRef idx="1"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="15875">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="2"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="dk1"/>
@@ -1849,23 +1832,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
+          <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="800" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:dataTable>
   <cs:downBar>
     <cs:lnRef idx="0"/>
@@ -1881,14 +1863,13 @@
           <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -1900,14 +1881,13 @@
       <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -1919,14 +1899,13 @@
       <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
+          <a:schemeClr val="tx1">
             <a:lumMod val="50000"/>
             <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:errorBar>
@@ -1937,19 +1916,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="dk1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:pattFill prst="ltDnDiag">
-        <a:fgClr>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:fgClr>
-        <a:bgClr>
-          <a:schemeClr val="lt1"/>
-        </a:bgClr>
-      </a:pattFill>
-    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
@@ -1961,7 +1927,7 @@
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="dk1">
+          <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -1978,14 +1944,13 @@
       <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln>
         <a:solidFill>
-          <a:schemeClr val="dk1">
+          <a:schemeClr val="tx1">
             <a:lumMod val="5000"/>
             <a:lumOff val="95000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
@@ -1997,14 +1962,13 @@
       <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
@@ -2016,14 +1980,13 @@
       <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
+          <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -2032,57 +1995,50 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="dk1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:pattFill prst="ltDnDiag">
-        <a:fgClr>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:fgClr>
-        <a:bgClr>
-          <a:schemeClr val="lt1"/>
-        </a:bgClr>
-      </a:pattFill>
-    </cs:spPr>
   </cs:plotArea>
-  <cs:plotArea3D>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="dk1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:plotArea3D>
   <cs:seriesAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -2093,14 +2049,14 @@
       <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
+          <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:seriesLine>
@@ -2108,25 +2064,25 @@
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="major">
-      <a:schemeClr val="dk1">
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
         <a:lumMod val="50000"/>
         <a:lumOff val="50000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
+    <cs:defRPr sz="1400" kern="1200" cap="none" spc="20" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="2"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="9525" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -2138,9 +2094,9 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2156,14 +2112,13 @@
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
+          <a:schemeClr val="tx1">
             <a:lumMod val="50000"/>
             <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -2172,9 +2127,9 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2186,19 +2141,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="dk1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:pattFill prst="ltDnDiag">
-        <a:fgClr>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:fgClr>
-        <a:bgClr>
-          <a:schemeClr val="lt1"/>
-        </a:bgClr>
-      </a:pattFill>
-    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -2429,112 +2371,112 @@
   <sheetData>
     <row r="1" spans="2:14" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="53"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="50"/>
     </row>
     <row r="3" spans="2:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="62" t="s">
+      <c r="B4" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="63"/>
-      <c r="L4" s="63"/>
-      <c r="M4" s="63"/>
-      <c r="N4" s="63"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="61"/>
+      <c r="L4" s="61"/>
+      <c r="M4" s="61"/>
+      <c r="N4" s="61"/>
     </row>
     <row r="5" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="56" t="s">
+      <c r="B5" s="54" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="66" t="s">
+      <c r="I5" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="J5" s="57"/>
-      <c r="K5" s="57"/>
-      <c r="L5" s="57"/>
-      <c r="M5" s="57"/>
-      <c r="N5" s="57"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="39"/>
+      <c r="L5" s="39"/>
+      <c r="M5" s="39"/>
+      <c r="N5" s="39"/>
     </row>
     <row r="6" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="38" t="s">
+      <c r="C6" s="36"/>
+      <c r="D6" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="34"/>
-      <c r="F6" s="37" t="s">
+      <c r="E6" s="36"/>
+      <c r="F6" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="34"/>
+      <c r="G6" s="36"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="36" t="s">
+      <c r="I6" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="J6" s="34"/>
-      <c r="K6" s="38" t="s">
+      <c r="J6" s="36"/>
+      <c r="K6" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="L6" s="34"/>
-      <c r="M6" s="37" t="s">
+      <c r="L6" s="36"/>
+      <c r="M6" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="N6" s="34"/>
+      <c r="N6" s="36"/>
     </row>
     <row r="7" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="33">
+      <c r="B7" s="58">
         <v>1962</v>
       </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="55">
+      <c r="C7" s="36"/>
+      <c r="D7" s="53">
         <v>1891</v>
       </c>
-      <c r="E7" s="34"/>
-      <c r="F7" s="35">
+      <c r="E7" s="36"/>
+      <c r="F7" s="67">
         <v>71</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="36"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="33">
+      <c r="I7" s="58">
         <v>1962</v>
       </c>
-      <c r="J7" s="34"/>
-      <c r="K7" s="55">
+      <c r="J7" s="36"/>
+      <c r="K7" s="53">
         <v>1865</v>
       </c>
-      <c r="L7" s="34"/>
-      <c r="M7" s="35">
+      <c r="L7" s="36"/>
+      <c r="M7" s="67">
         <v>71</v>
       </c>
-      <c r="N7" s="34"/>
+      <c r="N7" s="36"/>
     </row>
     <row r="8" spans="2:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="3"/>
@@ -2552,29 +2494,29 @@
       <c r="N8" s="3"/>
     </row>
     <row r="9" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="68" t="s">
+      <c r="I9" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="J9" s="48"/>
-      <c r="K9" s="48"/>
-      <c r="L9" s="48"/>
-      <c r="M9" s="48"/>
-      <c r="N9" s="34"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="42"/>
+      <c r="L9" s="42"/>
+      <c r="M9" s="42"/>
+      <c r="N9" s="36"/>
     </row>
     <row r="10" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="59" t="s">
+      <c r="B10" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="60"/>
+      <c r="C10" s="57"/>
       <c r="D10" s="5" t="s">
         <v>2</v>
       </c>
@@ -2608,10 +2550,10 @@
       </c>
     </row>
     <row r="11" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="34"/>
+      <c r="C11" s="36"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
@@ -2633,10 +2575,10 @@
       </c>
     </row>
     <row r="12" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="44" t="s">
+      <c r="B12" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="34"/>
+      <c r="C12" s="36"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -2658,10 +2600,10 @@
       </c>
     </row>
     <row r="13" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="34"/>
+      <c r="C13" s="36"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
@@ -2683,10 +2625,10 @@
       </c>
     </row>
     <row r="14" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="44" t="s">
+      <c r="B14" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="34"/>
+      <c r="C14" s="36"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -2708,10 +2650,10 @@
       </c>
     </row>
     <row r="15" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="41" t="s">
+      <c r="B15" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="34"/>
+      <c r="C15" s="36"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
@@ -2733,10 +2675,10 @@
       </c>
     </row>
     <row r="16" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="50" t="s">
+      <c r="B16" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="51"/>
+      <c r="C16" s="66"/>
       <c r="D16" s="8">
         <f>SUM(D11:D15)</f>
         <v>0</v>
@@ -2814,135 +2756,135 @@
       <c r="N18" s="3"/>
     </row>
     <row r="19" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="47" t="s">
+      <c r="B19" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="34"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="36"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="47" t="s">
+      <c r="I19" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="34"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="42"/>
+      <c r="M19" s="42"/>
+      <c r="N19" s="36"/>
     </row>
     <row r="20" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="49" t="s">
+      <c r="B20" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="34"/>
-      <c r="D20" s="49" t="s">
+      <c r="C20" s="36"/>
+      <c r="D20" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="34"/>
-      <c r="F20" s="49" t="s">
+      <c r="E20" s="36"/>
+      <c r="F20" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="34"/>
+      <c r="G20" s="36"/>
       <c r="H20" s="3"/>
-      <c r="I20" s="49" t="s">
+      <c r="I20" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="J20" s="34"/>
-      <c r="K20" s="49" t="s">
+      <c r="J20" s="36"/>
+      <c r="K20" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="L20" s="34"/>
-      <c r="M20" s="49" t="s">
+      <c r="L20" s="36"/>
+      <c r="M20" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="N20" s="34"/>
+      <c r="N20" s="36"/>
     </row>
     <row r="21" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="41" t="s">
+      <c r="B21" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="34"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="34"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="36"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="44" t="s">
+      <c r="I21" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="J21" s="34"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="34"/>
-      <c r="M21" s="61" t="str">
+      <c r="J21" s="36"/>
+      <c r="K21" s="48"/>
+      <c r="L21" s="36"/>
+      <c r="M21" s="59" t="str">
         <f>IF(K23=0,"-",K21/K23)</f>
         <v>-</v>
       </c>
-      <c r="N21" s="34"/>
+      <c r="N21" s="36"/>
     </row>
     <row r="22" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="44" t="s">
+      <c r="B22" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="34"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="34"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="36"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="41" t="s">
+      <c r="I22" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="J22" s="34"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="34"/>
-      <c r="M22" s="58" t="str">
+      <c r="J22" s="36"/>
+      <c r="K22" s="44"/>
+      <c r="L22" s="36"/>
+      <c r="M22" s="55" t="str">
         <f>IF(K23=0,"-",K22/K23)</f>
         <v>-</v>
       </c>
-      <c r="N22" s="34"/>
+      <c r="N22" s="36"/>
     </row>
     <row r="23" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="41" t="s">
+      <c r="B23" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="34"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="34"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="36"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="42" t="s">
+      <c r="I23" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="J23" s="34"/>
-      <c r="K23" s="67">
+      <c r="J23" s="36"/>
+      <c r="K23" s="40">
         <f>SUM(K21:L22)</f>
         <v>0</v>
       </c>
-      <c r="L23" s="34"/>
-      <c r="M23" s="39" t="str">
+      <c r="L23" s="36"/>
+      <c r="M23" s="62" t="str">
         <f>IF(K23=0,"-",(K21+K22)/K23)</f>
         <v>-</v>
       </c>
-      <c r="N23" s="34"/>
+      <c r="N23" s="36"/>
     </row>
     <row r="24" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="34"/>
-      <c r="D24" s="45">
+      <c r="C24" s="36"/>
+      <c r="D24" s="63">
         <f>SUM(D21:E23)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="46"/>
-      <c r="F24" s="45">
+      <c r="E24" s="64"/>
+      <c r="F24" s="63">
         <f>SUM(F21:G23)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="46"/>
+      <c r="G24" s="64"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2962,21 +2904,21 @@
     </row>
     <row r="26" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="25"/>
-      <c r="B26" s="64" t="s">
+      <c r="B26" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="65"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="65"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="65"/>
-      <c r="H26" s="65"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="65"/>
-      <c r="K26" s="65"/>
-      <c r="L26" s="65"/>
-      <c r="M26" s="65"/>
-      <c r="N26" s="65"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="34"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="34"/>
+      <c r="K26" s="34"/>
+      <c r="L26" s="34"/>
+      <c r="M26" s="34"/>
+      <c r="N26" s="34"/>
     </row>
     <row r="27" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="25"/>
@@ -3164,6 +3106,45 @@
     </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="I19:N19"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="B4:N4"/>
+    <mergeCell ref="K7:L7"/>
     <mergeCell ref="B26:N26"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="B21:C21"/>
@@ -3180,45 +3161,6 @@
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="K20:L20"/>
     <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="B4:N4"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="I19:N19"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="F7:G7"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/my_project/templates/template_B.xlsx
+++ b/my_project/templates/template_B.xlsx
@@ -14,6 +14,9 @@
   <sheets>
     <sheet name="요약보고서" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">요약보고서!$A$1:$AA$33</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
@@ -628,7 +631,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -722,101 +725,100 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -942,7 +944,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="ko-KR" b="1"/>
-              <a:t>▎ 월별 임관리비 납부 및 임대자산 출고 추이</a:t>
+              <a:t>▎ 월별 임관리비 납부 추이</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="en-US" b="1"/>
@@ -1169,6 +1171,686 @@
       <c:lineChart>
         <c:grouping val="stacked"/>
         <c:varyColors val="0"/>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1311033279"/>
+        <c:axId val="1311023295"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="1"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>요약보고서!$B$30</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>임대자산
+출고수량</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="38100" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:srgbClr val="FF0000"/>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="ko-KR"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="t"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:layout/>
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>요약보고서!$C$27:$N$27</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>요약보고서!$C$27:$N$27</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="12"/>
+                      <c:pt idx="0">
+                        <c:v>'25.03</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>'25.04</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>'25.05</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>'25.06</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>'25.07</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>'25.08</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>'25.09</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>'25.10</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>'25.11</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>'25.12</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>26.01</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>26.02</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>요약보고서!$C$30:$O$30</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>요약보고서!$C$30:$N$30</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>#,##0</c:formatCode>
+                      <c:ptCount val="12"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-6DF1-484C-972A-AA538BF060E8}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+          </c:ext>
+        </c:extLst>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1310948831"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1300" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1310958399"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1310958399"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1300" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1310948831"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1311023295"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1311033279"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="1311033279"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1311023295"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ko-KR" b="1"/>
+              <a:t>▎ 월별 임대자산 출고 추이</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" b="1"/>
+              <a:t>(</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ko-KR" b="1"/>
+              <a:t>그래프</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" b="1"/>
+              <a:t>)</a:t>
+            </a:r>
+            <a:endParaRPr lang="ko-KR" b="1"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:dLbls>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1310948831"/>
+        <c:axId val="1310958399"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="0"/>
+                <c:order val="0"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>요약보고서!$B$28</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>임관리비
+납부금액</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="38100" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="none"/>
+                </c:marker>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="accent5"/>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="ko-KR"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="t"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:layout/>
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>요약보고서!$C$27:$N$27</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>요약보고서!$C$27:$N$27</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="12"/>
+                      <c:pt idx="0">
+                        <c:v>'25.03</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>'25.04</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>'25.05</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>'25.06</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>'25.07</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>'25.08</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>'25.09</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>'25.10</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>'25.11</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>'25.12</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>26.01</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>26.02</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>요약보고서!$C$28:$O$28</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>요약보고서!$C$28:$N$28</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>#,##0</c:formatCode>
+                      <c:ptCount val="12"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-5191-4F33-BDAD-C1105F9E2598}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+          </c:ext>
+        </c:extLst>
+      </c:lineChart>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
@@ -1321,7 +2003,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-6DF1-484C-972A-AA538BF060E8}"/>
+              <c16:uniqueId val="{00000001-5191-4F33-BDAD-C1105F9E2598}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1450,39 +2132,12 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
+        <c:delete val="1"/>
         <c:axPos val="r"/>
         <c:numFmt formatCode="#,##0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1300" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="50000"/>
-                    <a:lumOff val="50000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ko-KR"/>
-          </a:p>
-        </c:txPr>
         <c:crossAx val="1311033279"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
@@ -1622,6 +2277,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="325">
   <cs:axisTitle>
@@ -2145,20 +2840,543 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="325">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="15875" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="1"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" kern="1200" cap="none" spc="20" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="2"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>145676</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>45942</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>291353</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>90765</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>212912</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>336177</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>22412</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2172,6 +3390,38 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>302559</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>22411</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>358588</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>156882</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="차트 2"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2359,126 +3609,144 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:AA31"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="17.25" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="3" width="13" style="1" customWidth="1"/>
-    <col min="4" max="14" width="13.125" style="1" customWidth="1"/>
+    <col min="2" max="12" width="11.5" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="11.5" style="1" customWidth="1"/>
     <col min="15" max="15" width="8.5" style="2" customWidth="1"/>
-    <col min="16" max="16384" width="8.5" style="2"/>
+    <col min="16" max="26" width="8.5" style="2"/>
+    <col min="27" max="27" width="5.125" style="2" customWidth="1"/>
+    <col min="28" max="28" width="8.5" style="2"/>
+    <col min="29" max="29" width="2.875" style="2" customWidth="1"/>
+    <col min="30" max="16384" width="8.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="49" t="s">
+    <row r="1" spans="2:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:27" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="52"/>
+      <c r="T2" s="52"/>
+      <c r="U2" s="52"/>
+      <c r="V2" s="52"/>
+      <c r="W2" s="52"/>
+      <c r="X2" s="52"/>
+      <c r="Y2" s="52"/>
+      <c r="Z2" s="52"/>
+      <c r="AA2" s="52"/>
     </row>
-    <row r="3" spans="2:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="60" t="s">
+    <row r="3" spans="2:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="2:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="61"/>
-      <c r="J4" s="61"/>
-      <c r="K4" s="61"/>
-      <c r="L4" s="61"/>
-      <c r="M4" s="61"/>
-      <c r="N4" s="61"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="62"/>
+      <c r="L4" s="62"/>
+      <c r="M4" s="62"/>
+      <c r="N4" s="62"/>
     </row>
-    <row r="5" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="54" t="s">
+    <row r="5" spans="2:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="38" t="s">
+      <c r="I5" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="J5" s="39"/>
-      <c r="K5" s="39"/>
-      <c r="L5" s="39"/>
-      <c r="M5" s="39"/>
-      <c r="N5" s="39"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="56"/>
+      <c r="L5" s="56"/>
+      <c r="M5" s="56"/>
+      <c r="N5" s="56"/>
     </row>
-    <row r="6" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="68" t="s">
+    <row r="6" spans="2:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="43" t="s">
+      <c r="C6" s="34"/>
+      <c r="D6" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="36"/>
-      <c r="F6" s="45" t="s">
+      <c r="E6" s="34"/>
+      <c r="F6" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="36"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="68" t="s">
+      <c r="I6" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="J6" s="36"/>
-      <c r="K6" s="43" t="s">
+      <c r="J6" s="34"/>
+      <c r="K6" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="L6" s="36"/>
-      <c r="M6" s="45" t="s">
+      <c r="L6" s="34"/>
+      <c r="M6" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="N6" s="36"/>
+      <c r="N6" s="34"/>
     </row>
-    <row r="7" spans="2:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="58">
+    <row r="7" spans="2:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="33">
         <v>1962</v>
       </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="53">
+      <c r="C7" s="34"/>
+      <c r="D7" s="54">
         <v>1891</v>
       </c>
-      <c r="E7" s="36"/>
-      <c r="F7" s="67">
+      <c r="E7" s="34"/>
+      <c r="F7" s="35">
         <v>71</v>
       </c>
-      <c r="G7" s="36"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="58">
+      <c r="I7" s="33">
         <v>1962</v>
       </c>
-      <c r="J7" s="36"/>
-      <c r="K7" s="53">
+      <c r="J7" s="34"/>
+      <c r="K7" s="54">
         <v>1865</v>
       </c>
-      <c r="L7" s="36"/>
-      <c r="M7" s="67">
+      <c r="L7" s="34"/>
+      <c r="M7" s="35">
         <v>71</v>
       </c>
-      <c r="N7" s="36"/>
+      <c r="N7" s="34"/>
     </row>
-    <row r="8" spans="2:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:27" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
@@ -2493,30 +3761,30 @@
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
     </row>
-    <row r="9" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="51" t="s">
+    <row r="9" spans="2:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="47" t="s">
+      <c r="I9" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="J9" s="42"/>
-      <c r="K9" s="42"/>
-      <c r="L9" s="42"/>
-      <c r="M9" s="42"/>
-      <c r="N9" s="36"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="48"/>
+      <c r="M9" s="48"/>
+      <c r="N9" s="34"/>
     </row>
-    <row r="10" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="56" t="s">
+    <row r="10" spans="2:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="57"/>
+      <c r="C10" s="59"/>
       <c r="D10" s="5" t="s">
         <v>2</v>
       </c>
@@ -2549,11 +3817,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="37" t="s">
+    <row r="11" spans="2:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="36"/>
+      <c r="C11" s="34"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
@@ -2574,11 +3842,11 @@
         <v>-</v>
       </c>
     </row>
-    <row r="12" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="52" t="s">
+    <row r="12" spans="2:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="36"/>
+      <c r="C12" s="34"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -2599,11 +3867,11 @@
         <v>-</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="37" t="s">
+    <row r="13" spans="2:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="36"/>
+      <c r="C13" s="34"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
@@ -2624,11 +3892,11 @@
         <v>-</v>
       </c>
     </row>
-    <row r="14" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="52" t="s">
+    <row r="14" spans="2:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="36"/>
+      <c r="C14" s="34"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -2649,11 +3917,11 @@
         <v>-</v>
       </c>
     </row>
-    <row r="15" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="37" t="s">
+    <row r="15" spans="2:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="36"/>
+      <c r="C15" s="34"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
@@ -2674,11 +3942,11 @@
         <v>-</v>
       </c>
     </row>
-    <row r="16" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="65" t="s">
+    <row r="16" spans="2:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="66"/>
+      <c r="C16" s="51"/>
       <c r="D16" s="8">
         <f>SUM(D11:D15)</f>
         <v>0</v>
@@ -2756,135 +4024,135 @@
       <c r="N18" s="3"/>
     </row>
     <row r="19" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="41" t="s">
+      <c r="B19" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="36"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="34"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="41" t="s">
+      <c r="I19" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="J19" s="42"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="42"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="36"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="34"/>
     </row>
     <row r="20" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="46" t="s">
+      <c r="B20" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="46" t="s">
+      <c r="C20" s="34"/>
+      <c r="D20" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="36"/>
-      <c r="F20" s="46" t="s">
+      <c r="E20" s="34"/>
+      <c r="F20" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="36"/>
+      <c r="G20" s="34"/>
       <c r="H20" s="3"/>
-      <c r="I20" s="46" t="s">
+      <c r="I20" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="J20" s="36"/>
-      <c r="K20" s="46" t="s">
+      <c r="J20" s="34"/>
+      <c r="K20" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="L20" s="36"/>
-      <c r="M20" s="46" t="s">
+      <c r="L20" s="34"/>
+      <c r="M20" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="N20" s="36"/>
+      <c r="N20" s="34"/>
     </row>
     <row r="21" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="37" t="s">
+      <c r="B21" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="36"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="36"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="34"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="52" t="s">
+      <c r="I21" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="J21" s="36"/>
-      <c r="K21" s="48"/>
-      <c r="L21" s="36"/>
-      <c r="M21" s="59" t="str">
+      <c r="J21" s="34"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="34"/>
+      <c r="M21" s="60" t="str">
         <f>IF(K23=0,"-",K21/K23)</f>
         <v>-</v>
       </c>
-      <c r="N21" s="36"/>
+      <c r="N21" s="34"/>
     </row>
     <row r="22" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="52" t="s">
+      <c r="B22" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="36"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="34"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="37" t="s">
+      <c r="I22" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="J22" s="36"/>
-      <c r="K22" s="44"/>
-      <c r="L22" s="36"/>
-      <c r="M22" s="55" t="str">
+      <c r="J22" s="34"/>
+      <c r="K22" s="40"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="57" t="str">
         <f>IF(K23=0,"-",K22/K23)</f>
         <v>-</v>
       </c>
-      <c r="N22" s="36"/>
+      <c r="N22" s="34"/>
     </row>
     <row r="23" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="37" t="s">
+      <c r="B23" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="36"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="36"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="34"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="35" t="s">
+      <c r="I23" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="J23" s="36"/>
-      <c r="K23" s="40">
+      <c r="J23" s="34"/>
+      <c r="K23" s="66">
         <f>SUM(K21:L22)</f>
         <v>0</v>
       </c>
-      <c r="L23" s="36"/>
-      <c r="M23" s="62" t="str">
+      <c r="L23" s="34"/>
+      <c r="M23" s="39" t="str">
         <f>IF(K23=0,"-",(K21+K22)/K23)</f>
         <v>-</v>
       </c>
-      <c r="N23" s="36"/>
+      <c r="N23" s="34"/>
     </row>
     <row r="24" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="35" t="s">
+      <c r="B24" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="36"/>
-      <c r="D24" s="63">
+      <c r="C24" s="34"/>
+      <c r="D24" s="45">
         <f>SUM(D21:E23)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="64"/>
-      <c r="F24" s="63">
+      <c r="E24" s="46"/>
+      <c r="F24" s="45">
         <f>SUM(F21:G23)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="64"/>
+      <c r="G24" s="46"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2902,23 +4170,23 @@
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
     </row>
-    <row r="26" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="25"/>
-      <c r="B26" s="33" t="s">
+      <c r="B26" s="63" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="34"/>
-      <c r="I26" s="34"/>
-      <c r="J26" s="34"/>
-      <c r="K26" s="34"/>
-      <c r="L26" s="34"/>
-      <c r="M26" s="34"/>
-      <c r="N26" s="34"/>
+      <c r="C26" s="64"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="64"/>
+      <c r="F26" s="64"/>
+      <c r="G26" s="64"/>
+      <c r="H26" s="64"/>
+      <c r="I26" s="64"/>
+      <c r="J26" s="64"/>
+      <c r="K26" s="64"/>
+      <c r="L26" s="64"/>
+      <c r="M26" s="64"/>
+      <c r="N26" s="64"/>
     </row>
     <row r="27" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="25"/>
@@ -3106,13 +4374,38 @@
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="B2:AA2"/>
+    <mergeCell ref="B26:N26"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="I5:N5"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="I9:N9"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="B4:N4"/>
+    <mergeCell ref="K7:L7"/>
     <mergeCell ref="M23:N23"/>
     <mergeCell ref="F21:G21"/>
     <mergeCell ref="B11:C11"/>
@@ -3129,42 +4422,17 @@
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="B4:N4"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="B26:N26"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="I5:N5"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="I9:N9"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="F7:G7"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
-  <drawing r:id="rId1"/>
+  <pageSetup scale="43" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/my_project/templates/template_B.xlsx
+++ b/my_project/templates/template_B.xlsx
@@ -725,100 +725,100 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1256,7 +1256,6 @@
                   <c:showLeaderLines val="0"/>
                   <c:extLst>
                     <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                      <c15:layout/>
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
                         <c:spPr>
@@ -1748,7 +1747,6 @@
                   <c:showLeaderLines val="0"/>
                   <c:extLst>
                     <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                      <c15:layout/>
                       <c15:showLeaderLines val="1"/>
                       <c15:leaderLines>
                         <c:spPr>
@@ -3368,13 +3366,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>291353</xdr:colOff>
+      <xdr:colOff>291352</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>90765</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>336177</xdr:colOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>526675</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>22412</xdr:rowOff>
     </xdr:to>
@@ -3403,8 +3401,8 @@
       <xdr:rowOff>22411</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>358588</xdr:colOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>560294</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>156882</xdr:rowOff>
     </xdr:to>
@@ -3626,125 +3624,125 @@
   <sheetData>
     <row r="1" spans="2:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:27" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52"/>
-      <c r="N2" s="52"/>
-      <c r="O2" s="52"/>
-      <c r="P2" s="52"/>
-      <c r="Q2" s="52"/>
-      <c r="R2" s="52"/>
-      <c r="S2" s="52"/>
-      <c r="T2" s="52"/>
-      <c r="U2" s="52"/>
-      <c r="V2" s="52"/>
-      <c r="W2" s="52"/>
-      <c r="X2" s="52"/>
-      <c r="Y2" s="52"/>
-      <c r="Z2" s="52"/>
-      <c r="AA2" s="52"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
+      <c r="T2" s="33"/>
+      <c r="U2" s="33"/>
+      <c r="V2" s="33"/>
+      <c r="W2" s="33"/>
+      <c r="X2" s="33"/>
+      <c r="Y2" s="33"/>
+      <c r="Z2" s="33"/>
+      <c r="AA2" s="33"/>
     </row>
     <row r="3" spans="2:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
-      <c r="L4" s="62"/>
-      <c r="M4" s="62"/>
-      <c r="N4" s="62"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
+      <c r="L4" s="60"/>
+      <c r="M4" s="60"/>
+      <c r="N4" s="60"/>
     </row>
     <row r="5" spans="2:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="55" t="s">
+      <c r="B5" s="53" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="65" t="s">
+      <c r="I5" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="J5" s="56"/>
-      <c r="K5" s="56"/>
-      <c r="L5" s="56"/>
-      <c r="M5" s="56"/>
-      <c r="N5" s="56"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="40"/>
     </row>
     <row r="6" spans="2:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="38" t="s">
+      <c r="C6" s="37"/>
+      <c r="D6" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="34"/>
-      <c r="F6" s="37" t="s">
+      <c r="E6" s="37"/>
+      <c r="F6" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="34"/>
+      <c r="G6" s="37"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="36" t="s">
+      <c r="I6" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="J6" s="34"/>
-      <c r="K6" s="38" t="s">
+      <c r="J6" s="37"/>
+      <c r="K6" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="L6" s="34"/>
-      <c r="M6" s="37" t="s">
+      <c r="L6" s="37"/>
+      <c r="M6" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="N6" s="34"/>
+      <c r="N6" s="37"/>
     </row>
     <row r="7" spans="2:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="33">
+      <c r="B7" s="57">
         <v>1962</v>
       </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="54">
+      <c r="C7" s="37"/>
+      <c r="D7" s="52">
         <v>1891</v>
       </c>
-      <c r="E7" s="34"/>
-      <c r="F7" s="35">
+      <c r="E7" s="37"/>
+      <c r="F7" s="66">
         <v>71</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="37"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="33">
+      <c r="I7" s="57">
         <v>1962</v>
       </c>
-      <c r="J7" s="34"/>
-      <c r="K7" s="54">
+      <c r="J7" s="37"/>
+      <c r="K7" s="52">
         <v>1865</v>
       </c>
-      <c r="L7" s="34"/>
-      <c r="M7" s="35">
+      <c r="L7" s="37"/>
+      <c r="M7" s="66">
         <v>71</v>
       </c>
-      <c r="N7" s="34"/>
+      <c r="N7" s="37"/>
     </row>
     <row r="8" spans="2:27" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="3"/>
@@ -3762,29 +3760,29 @@
       <c r="N8" s="3"/>
     </row>
     <row r="9" spans="2:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="53" t="s">
+      <c r="B9" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="67" t="s">
+      <c r="I9" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="J9" s="48"/>
-      <c r="K9" s="48"/>
-      <c r="L9" s="48"/>
-      <c r="M9" s="48"/>
-      <c r="N9" s="34"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+      <c r="L9" s="43"/>
+      <c r="M9" s="43"/>
+      <c r="N9" s="37"/>
     </row>
     <row r="10" spans="2:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="58" t="s">
+      <c r="B10" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="59"/>
+      <c r="C10" s="56"/>
       <c r="D10" s="5" t="s">
         <v>2</v>
       </c>
@@ -3818,10 +3816,10 @@
       </c>
     </row>
     <row r="11" spans="2:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="34"/>
+      <c r="C11" s="37"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
@@ -3843,10 +3841,10 @@
       </c>
     </row>
     <row r="12" spans="2:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="44" t="s">
+      <c r="B12" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="34"/>
+      <c r="C12" s="37"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -3868,10 +3866,10 @@
       </c>
     </row>
     <row r="13" spans="2:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="34"/>
+      <c r="C13" s="37"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
@@ -3893,10 +3891,10 @@
       </c>
     </row>
     <row r="14" spans="2:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="44" t="s">
+      <c r="B14" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="34"/>
+      <c r="C14" s="37"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -3918,10 +3916,10 @@
       </c>
     </row>
     <row r="15" spans="2:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="41" t="s">
+      <c r="B15" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="34"/>
+      <c r="C15" s="37"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
@@ -3943,10 +3941,10 @@
       </c>
     </row>
     <row r="16" spans="2:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="50" t="s">
+      <c r="B16" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="51"/>
+      <c r="C16" s="65"/>
       <c r="D16" s="8">
         <f>SUM(D11:D15)</f>
         <v>0</v>
@@ -4024,135 +4022,135 @@
       <c r="N18" s="3"/>
     </row>
     <row r="19" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="47" t="s">
+      <c r="B19" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="34"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="37"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="47" t="s">
+      <c r="I19" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="34"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
+      <c r="L19" s="43"/>
+      <c r="M19" s="43"/>
+      <c r="N19" s="37"/>
     </row>
     <row r="20" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="49" t="s">
+      <c r="B20" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="34"/>
-      <c r="D20" s="49" t="s">
+      <c r="C20" s="37"/>
+      <c r="D20" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="34"/>
-      <c r="F20" s="49" t="s">
+      <c r="E20" s="37"/>
+      <c r="F20" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="34"/>
+      <c r="G20" s="37"/>
       <c r="H20" s="3"/>
-      <c r="I20" s="49" t="s">
+      <c r="I20" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="J20" s="34"/>
-      <c r="K20" s="49" t="s">
+      <c r="J20" s="37"/>
+      <c r="K20" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="L20" s="34"/>
-      <c r="M20" s="49" t="s">
+      <c r="L20" s="37"/>
+      <c r="M20" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="N20" s="34"/>
+      <c r="N20" s="37"/>
     </row>
     <row r="21" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="41" t="s">
+      <c r="B21" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="34"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="34"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="37"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="44" t="s">
+      <c r="I21" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="J21" s="34"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="34"/>
-      <c r="M21" s="60" t="str">
+      <c r="J21" s="37"/>
+      <c r="K21" s="49"/>
+      <c r="L21" s="37"/>
+      <c r="M21" s="58" t="str">
         <f>IF(K23=0,"-",K21/K23)</f>
         <v>-</v>
       </c>
-      <c r="N21" s="34"/>
+      <c r="N21" s="37"/>
     </row>
     <row r="22" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="44" t="s">
+      <c r="B22" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="34"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="34"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="37"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="41" t="s">
+      <c r="I22" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="J22" s="34"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="34"/>
-      <c r="M22" s="57" t="str">
+      <c r="J22" s="37"/>
+      <c r="K22" s="45"/>
+      <c r="L22" s="37"/>
+      <c r="M22" s="54" t="str">
         <f>IF(K23=0,"-",K22/K23)</f>
         <v>-</v>
       </c>
-      <c r="N22" s="34"/>
+      <c r="N22" s="37"/>
     </row>
     <row r="23" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="41" t="s">
+      <c r="B23" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="34"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="34"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="37"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="42" t="s">
+      <c r="I23" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="J23" s="34"/>
-      <c r="K23" s="66">
+      <c r="J23" s="37"/>
+      <c r="K23" s="41">
         <f>SUM(K21:L22)</f>
         <v>0</v>
       </c>
-      <c r="L23" s="34"/>
-      <c r="M23" s="39" t="str">
+      <c r="L23" s="37"/>
+      <c r="M23" s="61" t="str">
         <f>IF(K23=0,"-",(K21+K22)/K23)</f>
         <v>-</v>
       </c>
-      <c r="N23" s="34"/>
+      <c r="N23" s="37"/>
     </row>
     <row r="24" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="34"/>
-      <c r="D24" s="45">
+      <c r="C24" s="37"/>
+      <c r="D24" s="62">
         <f>SUM(D21:E23)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="46"/>
-      <c r="F24" s="45">
+      <c r="E24" s="63"/>
+      <c r="F24" s="62">
         <f>SUM(F21:G23)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="46"/>
+      <c r="G24" s="63"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4172,21 +4170,21 @@
     </row>
     <row r="26" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="25"/>
-      <c r="B26" s="63" t="s">
+      <c r="B26" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="64"/>
-      <c r="D26" s="64"/>
-      <c r="E26" s="64"/>
-      <c r="F26" s="64"/>
-      <c r="G26" s="64"/>
-      <c r="H26" s="64"/>
-      <c r="I26" s="64"/>
-      <c r="J26" s="64"/>
-      <c r="K26" s="64"/>
-      <c r="L26" s="64"/>
-      <c r="M26" s="64"/>
-      <c r="N26" s="64"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="35"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="35"/>
+      <c r="K26" s="35"/>
+      <c r="L26" s="35"/>
+      <c r="M26" s="35"/>
+      <c r="N26" s="35"/>
     </row>
     <row r="27" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="25"/>
@@ -4374,6 +4372,45 @@
     </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="B4:N4"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="I19:N19"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="B2:AA2"/>
     <mergeCell ref="B26:N26"/>
     <mergeCell ref="I23:J23"/>
@@ -4390,45 +4427,6 @@
     <mergeCell ref="I9:N9"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="K20:L20"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="B4:N4"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="I19:N19"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="F7:G7"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/my_project/templates/template_B.xlsx
+++ b/my_project/templates/template_B.xlsx
@@ -725,6 +725,83 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -734,91 +811,14 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="3" fontId="9" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="9" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3607,7 +3607,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AA31"/>
+  <dimension ref="A1:AG31"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="17.25" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -3622,129 +3622,135 @@
     <col min="30" max="16384" width="8.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:27" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="33" t="s">
+    <row r="1" spans="2:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:33" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
-      <c r="T2" s="33"/>
-      <c r="U2" s="33"/>
-      <c r="V2" s="33"/>
-      <c r="W2" s="33"/>
-      <c r="X2" s="33"/>
-      <c r="Y2" s="33"/>
-      <c r="Z2" s="33"/>
-      <c r="AA2" s="33"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="62"/>
+      <c r="M2" s="62"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="62"/>
+      <c r="W2" s="62"/>
+      <c r="X2" s="62"/>
+      <c r="Y2" s="62"/>
+      <c r="Z2" s="62"/>
+      <c r="AA2" s="62"/>
+      <c r="AB2" s="62"/>
+      <c r="AC2" s="62"/>
+      <c r="AD2" s="62"/>
+      <c r="AE2" s="62"/>
+      <c r="AF2" s="62"/>
+      <c r="AG2" s="62"/>
     </row>
-    <row r="3" spans="2:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="2:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="59" t="s">
+    <row r="3" spans="2:33" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="2:33" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="60"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
     </row>
-    <row r="5" spans="2:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="53" t="s">
+    <row r="5" spans="2:33" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="55" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="39" t="s">
+      <c r="I5" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="J5" s="40"/>
-      <c r="K5" s="40"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="40"/>
-      <c r="N5" s="40"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="56"/>
+      <c r="L5" s="56"/>
+      <c r="M5" s="56"/>
+      <c r="N5" s="56"/>
     </row>
-    <row r="6" spans="2:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="67" t="s">
+    <row r="6" spans="2:33" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="44" t="s">
+      <c r="C6" s="34"/>
+      <c r="D6" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="37"/>
-      <c r="F6" s="46" t="s">
+      <c r="E6" s="34"/>
+      <c r="F6" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="37"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="67" t="s">
+      <c r="I6" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="J6" s="37"/>
-      <c r="K6" s="44" t="s">
+      <c r="J6" s="34"/>
+      <c r="K6" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="L6" s="37"/>
-      <c r="M6" s="46" t="s">
+      <c r="L6" s="34"/>
+      <c r="M6" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="N6" s="37"/>
+      <c r="N6" s="34"/>
     </row>
-    <row r="7" spans="2:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="57">
+    <row r="7" spans="2:33" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="50">
         <v>1962</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="52">
+      <c r="C7" s="34"/>
+      <c r="D7" s="42">
         <v>1891</v>
       </c>
-      <c r="E7" s="37"/>
-      <c r="F7" s="66">
+      <c r="E7" s="34"/>
+      <c r="F7" s="51">
         <v>71</v>
       </c>
-      <c r="G7" s="37"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="57">
+      <c r="I7" s="50">
         <v>1962</v>
       </c>
-      <c r="J7" s="37"/>
-      <c r="K7" s="52">
+      <c r="J7" s="34"/>
+      <c r="K7" s="42">
         <v>1865</v>
       </c>
-      <c r="L7" s="37"/>
-      <c r="M7" s="66">
+      <c r="L7" s="34"/>
+      <c r="M7" s="51">
         <v>71</v>
       </c>
-      <c r="N7" s="37"/>
+      <c r="N7" s="34"/>
     </row>
-    <row r="8" spans="2:27" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:33" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
@@ -3759,30 +3765,30 @@
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
     </row>
-    <row r="9" spans="2:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="50" t="s">
+    <row r="9" spans="2:33" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="48" t="s">
+      <c r="I9" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="J9" s="43"/>
-      <c r="K9" s="43"/>
-      <c r="L9" s="43"/>
-      <c r="M9" s="43"/>
-      <c r="N9" s="37"/>
+      <c r="J9" s="46"/>
+      <c r="K9" s="46"/>
+      <c r="L9" s="46"/>
+      <c r="M9" s="46"/>
+      <c r="N9" s="34"/>
     </row>
-    <row r="10" spans="2:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="55" t="s">
+    <row r="10" spans="2:33" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="56"/>
+      <c r="C10" s="59"/>
       <c r="D10" s="5" t="s">
         <v>2</v>
       </c>
@@ -3815,11 +3821,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="2:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="38" t="s">
+    <row r="11" spans="2:33" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="37"/>
+      <c r="C11" s="34"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
@@ -3840,11 +3846,11 @@
         <v>-</v>
       </c>
     </row>
-    <row r="12" spans="2:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="51" t="s">
+    <row r="12" spans="2:33" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="37"/>
+      <c r="C12" s="34"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -3865,11 +3871,11 @@
         <v>-</v>
       </c>
     </row>
-    <row r="13" spans="2:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="38" t="s">
+    <row r="13" spans="2:33" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="37"/>
+      <c r="C13" s="34"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
@@ -3890,11 +3896,11 @@
         <v>-</v>
       </c>
     </row>
-    <row r="14" spans="2:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="51" t="s">
+    <row r="14" spans="2:33" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="37"/>
+      <c r="C14" s="34"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -3915,11 +3921,11 @@
         <v>-</v>
       </c>
     </row>
-    <row r="15" spans="2:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="38" t="s">
+    <row r="15" spans="2:33" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="37"/>
+      <c r="C15" s="34"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
@@ -3940,11 +3946,11 @@
         <v>-</v>
       </c>
     </row>
-    <row r="16" spans="2:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="64" t="s">
+    <row r="16" spans="2:33" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="65"/>
+      <c r="C16" s="49"/>
       <c r="D16" s="8">
         <f>SUM(D11:D15)</f>
         <v>0</v>
@@ -4022,135 +4028,135 @@
       <c r="N18" s="3"/>
     </row>
     <row r="19" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="43"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="37"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="34"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="42" t="s">
+      <c r="I19" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
-      <c r="L19" s="43"/>
-      <c r="M19" s="43"/>
-      <c r="N19" s="37"/>
+      <c r="J19" s="46"/>
+      <c r="K19" s="46"/>
+      <c r="L19" s="46"/>
+      <c r="M19" s="46"/>
+      <c r="N19" s="34"/>
     </row>
     <row r="20" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="37"/>
+      <c r="C20" s="34"/>
       <c r="D20" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="37"/>
+      <c r="E20" s="34"/>
       <c r="F20" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="37"/>
+      <c r="G20" s="34"/>
       <c r="H20" s="3"/>
       <c r="I20" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="J20" s="37"/>
+      <c r="J20" s="34"/>
       <c r="K20" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="L20" s="37"/>
+      <c r="L20" s="34"/>
       <c r="M20" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="N20" s="37"/>
+      <c r="N20" s="34"/>
     </row>
     <row r="21" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="38" t="s">
+      <c r="B21" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="37"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="37"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="34"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="51" t="s">
+      <c r="I21" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="J21" s="37"/>
-      <c r="K21" s="49"/>
-      <c r="L21" s="37"/>
-      <c r="M21" s="58" t="str">
+      <c r="J21" s="34"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="34"/>
+      <c r="M21" s="60" t="str">
         <f>IF(K23=0,"-",K21/K23)</f>
         <v>-</v>
       </c>
-      <c r="N21" s="37"/>
+      <c r="N21" s="34"/>
     </row>
     <row r="22" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="51" t="s">
+      <c r="B22" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="37"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="37"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="34"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="38" t="s">
+      <c r="I22" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="J22" s="37"/>
-      <c r="K22" s="45"/>
-      <c r="L22" s="37"/>
-      <c r="M22" s="54" t="str">
+      <c r="J22" s="34"/>
+      <c r="K22" s="39"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="57" t="str">
         <f>IF(K23=0,"-",K22/K23)</f>
         <v>-</v>
       </c>
-      <c r="N22" s="37"/>
+      <c r="N22" s="34"/>
     </row>
     <row r="23" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="38" t="s">
+      <c r="B23" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="37"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="34"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="36" t="s">
+      <c r="I23" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="J23" s="37"/>
-      <c r="K23" s="41">
+      <c r="J23" s="34"/>
+      <c r="K23" s="66">
         <f>SUM(K21:L22)</f>
         <v>0</v>
       </c>
-      <c r="L23" s="37"/>
-      <c r="M23" s="61" t="str">
+      <c r="L23" s="34"/>
+      <c r="M23" s="43" t="str">
         <f>IF(K23=0,"-",(K21+K22)/K23)</f>
         <v>-</v>
       </c>
-      <c r="N23" s="37"/>
+      <c r="N23" s="34"/>
     </row>
     <row r="24" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="36" t="s">
+      <c r="B24" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="37"/>
-      <c r="D24" s="62">
+      <c r="C24" s="34"/>
+      <c r="D24" s="37">
         <f>SUM(D21:E23)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="63"/>
-      <c r="F24" s="62">
+      <c r="E24" s="38"/>
+      <c r="F24" s="37">
         <f>SUM(F21:G23)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="63"/>
+      <c r="G24" s="38"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4170,21 +4176,21 @@
     </row>
     <row r="26" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="25"/>
-      <c r="B26" s="34" t="s">
+      <c r="B26" s="63" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="35"/>
-      <c r="J26" s="35"/>
-      <c r="K26" s="35"/>
-      <c r="L26" s="35"/>
-      <c r="M26" s="35"/>
-      <c r="N26" s="35"/>
+      <c r="C26" s="64"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="64"/>
+      <c r="F26" s="64"/>
+      <c r="G26" s="64"/>
+      <c r="H26" s="64"/>
+      <c r="I26" s="64"/>
+      <c r="J26" s="64"/>
+      <c r="K26" s="64"/>
+      <c r="L26" s="64"/>
+      <c r="M26" s="64"/>
+      <c r="N26" s="64"/>
     </row>
     <row r="27" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="25"/>
@@ -4372,15 +4378,36 @@
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="B2:AG2"/>
+    <mergeCell ref="B26:N26"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="I5:N5"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="I9:N9"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="B4:N4"/>
     <mergeCell ref="K7:L7"/>
     <mergeCell ref="M23:N23"/>
@@ -4397,36 +4424,15 @@
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="F7:G7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B2:AA2"/>
-    <mergeCell ref="B26:N26"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="I5:N5"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="I9:N9"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
